--- a/xlsx/dre/DRE_06_2026.xlsx
+++ b/xlsx/dre/DRE_06_2026.xlsx
@@ -447,6 +447,21 @@
     <t>R$  178,31</t>
   </si>
   <si>
+    <t>1/5</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>R$  441,79</t>
+  </si>
+  <si>
+    <t>27/02/26</t>
+  </si>
+  <si>
+    <t>Digisac MP 2026</t>
+  </si>
+  <si>
     <t>685/1</t>
   </si>
   <si>
@@ -460,21 +475,6 @@
   </si>
   <si>
     <t>22/06/26</t>
-  </si>
-  <si>
-    <t>1/5</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>R$  441,79</t>
-  </si>
-  <si>
-    <t>27/02/26</t>
-  </si>
-  <si>
-    <t>Digisac MP 2026</t>
   </si>
   <si>
     <t>4 CUSTOS E DESPESAS</t>
@@ -691,6 +691,15 @@
     <t>R$ 1.915,14</t>
   </si>
   <si>
+    <t>64301/1</t>
+  </si>
+  <si>
+    <t>PFR</t>
+  </si>
+  <si>
+    <t>R$  1.622,10</t>
+  </si>
+  <si>
     <t>76601/1</t>
   </si>
   <si>
@@ -699,15 +708,6 @@
   <si>
     <t>Título referente a Frete. 
 Título gerado pela diferença de valor da revisão.</t>
-  </si>
-  <si>
-    <t>64301/1</t>
-  </si>
-  <si>
-    <t>PFR</t>
-  </si>
-  <si>
-    <t>R$  1.622,10</t>
   </si>
   <si>
     <t>4.02.01.01.04 Compra de outras mercadorias</t>
@@ -872,6 +872,15 @@
     <t>R$  7.854,09</t>
   </si>
   <si>
+    <t>85601/0</t>
+  </si>
+  <si>
+    <t>R$  95,00</t>
+  </si>
+  <si>
+    <t>85601KrisdanyVSMC</t>
+  </si>
+  <si>
     <t>83001/2</t>
   </si>
   <si>
@@ -926,6 +935,9 @@
     <t>R$  1.577,95</t>
   </si>
   <si>
+    <t>R$  30,00</t>
+  </si>
+  <si>
     <t>85701/3</t>
   </si>
   <si>
@@ -962,6 +974,12 @@
     <t>85701HelgaBA</t>
   </si>
   <si>
+    <t>81801/2</t>
+  </si>
+  <si>
+    <t>Chapa de MDF cliente Andre Soy Parc 2/3</t>
+  </si>
+  <si>
     <t>84102/3</t>
   </si>
   <si>
@@ -974,24 +992,6 @@
     <t>R$  1.779,72</t>
   </si>
   <si>
-    <t>85601/0</t>
-  </si>
-  <si>
-    <t>R$  95,00</t>
-  </si>
-  <si>
-    <t>85601KrisdanyVSMC</t>
-  </si>
-  <si>
-    <t>R$  30,00</t>
-  </si>
-  <si>
-    <t>81801/2</t>
-  </si>
-  <si>
-    <t>Chapa de MDF cliente Andre Soy Parc 2/3</t>
-  </si>
-  <si>
     <t>R$  75,63</t>
   </si>
   <si>
@@ -1337,12 +1337,12 @@
     <t>DSR jun26/1</t>
   </si>
   <si>
+    <t>R$  2.151,72</t>
+  </si>
+  <si>
     <t>R$  1.207,83</t>
   </si>
   <si>
-    <t>R$  2.151,72</t>
-  </si>
-  <si>
     <t>4.03.02 COMISSÕES E BÔNUS DE TERCEIROS</t>
   </si>
   <si>
@@ -1541,6 +1541,18 @@
     <t>12/6</t>
   </si>
   <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
     <t>Google</t>
   </si>
   <si>
@@ -1562,18 +1574,6 @@
     <t>Webgiga 2026</t>
   </si>
   <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
-  </si>
-  <si>
     <t>1/4</t>
   </si>
   <si>
@@ -1934,48 +1934,48 @@
     <t>4.04.02.05.02 Serviços de limpeza</t>
   </si>
   <si>
+    <t>664/1</t>
+  </si>
+  <si>
+    <t>Claudineuza Santos Machado</t>
+  </si>
+  <si>
+    <t>R$  230,00</t>
+  </si>
+  <si>
+    <t>08/06/26</t>
+  </si>
+  <si>
+    <t>673/1</t>
+  </si>
+  <si>
+    <t>11/06/26</t>
+  </si>
+  <si>
+    <t>Thais Pereira Pires</t>
+  </si>
+  <si>
+    <t>R$  1.600,00</t>
+  </si>
+  <si>
+    <t>Thais Limpeza - 2026</t>
+  </si>
+  <si>
+    <t>683/1</t>
+  </si>
+  <si>
+    <t>Sabrina Barbosa de Medeiros</t>
+  </si>
+  <si>
     <t>675/1</t>
   </si>
   <si>
-    <t>Claudineuza Santos Machado</t>
-  </si>
-  <si>
-    <t>R$  230,00</t>
-  </si>
-  <si>
-    <t>683/1</t>
-  </si>
-  <si>
-    <t>Sabrina Barbosa de Medeiros</t>
-  </si>
-  <si>
-    <t>664/1</t>
-  </si>
-  <si>
-    <t>08/06/26</t>
-  </si>
-  <si>
-    <t>Thais Pereira Pires</t>
-  </si>
-  <si>
-    <t>R$  1.600,00</t>
-  </si>
-  <si>
-    <t>Thais Limpeza - 2026</t>
-  </si>
-  <si>
     <t>663/1</t>
   </si>
   <si>
     <t>R$  220,00</t>
   </si>
   <si>
-    <t>673/1</t>
-  </si>
-  <si>
-    <t>11/06/26</t>
-  </si>
-  <si>
     <t>4.04.02.06 Material de escritório</t>
   </si>
   <si>
@@ -1983,18 +1983,6 @@
   </si>
   <si>
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
-  </si>
-  <si>
-    <t>699/1</t>
-  </si>
-  <si>
-    <t>Pão de Açúcar</t>
-  </si>
-  <si>
-    <t>R$  95,17</t>
-  </si>
-  <si>
-    <t>material limpeza</t>
   </si>
   <si>
     <t>700/1</t>
@@ -2013,6 +2001,18 @@
 </t>
   </si>
   <si>
+    <t>699/1</t>
+  </si>
+  <si>
+    <t>Pão de Açúcar</t>
+  </si>
+  <si>
+    <t>R$  95,17</t>
+  </si>
+  <si>
+    <t>material limpeza</t>
+  </si>
+  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2076,6 +2076,48 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>64/1</t>
+  </si>
+  <si>
+    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  146,67</t>
+  </si>
+  <si>
+    <t>ISO Implantação -Saude ocupacional</t>
+  </si>
+  <si>
+    <t>63/1</t>
+  </si>
+  <si>
+    <t>R$  376,38</t>
+  </si>
+  <si>
+    <t>Promob 2026/4</t>
+  </si>
+  <si>
+    <t>62/1</t>
+  </si>
+  <si>
+    <t>R$  293,11</t>
+  </si>
+  <si>
+    <t>Promob 2026/3</t>
+  </si>
+  <si>
+    <t>3/5</t>
+  </si>
+  <si>
+    <t>R$  1.248,76</t>
+  </si>
+  <si>
+    <t>13/02/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/2</t>
+  </si>
+  <si>
     <t>D4 sign</t>
   </si>
   <si>
@@ -2085,64 +2127,22 @@
     <t>D4 sign 2026</t>
   </si>
   <si>
-    <t>64/1</t>
-  </si>
-  <si>
-    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  146,67</t>
-  </si>
-  <si>
-    <t>ISO Implantação -Saude ocupacional</t>
-  </si>
-  <si>
-    <t>63/1</t>
-  </si>
-  <si>
-    <t>R$  376,38</t>
-  </si>
-  <si>
-    <t>Promob 2026/4</t>
-  </si>
-  <si>
-    <t>62/1</t>
-  </si>
-  <si>
-    <t>R$  293,11</t>
-  </si>
-  <si>
-    <t>Promob 2026/3</t>
-  </si>
-  <si>
-    <t>3/5</t>
-  </si>
-  <si>
-    <t>R$  1.248,76</t>
-  </si>
-  <si>
-    <t>13/02/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/2</t>
+    <t>61/2</t>
+  </si>
+  <si>
+    <t>Pipefy</t>
+  </si>
+  <si>
+    <t>R$  95,96</t>
+  </si>
+  <si>
+    <t>21/05/26</t>
   </si>
   <si>
     <t>R$  599,00</t>
   </si>
   <si>
     <t>Promob 2026</t>
-  </si>
-  <si>
-    <t>61/2</t>
-  </si>
-  <si>
-    <t>Pipefy</t>
-  </si>
-  <si>
-    <t>R$  95,96</t>
-  </si>
-  <si>
-    <t>21/05/26</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -4505,25 +4505,25 @@
         <v>144</v>
       </c>
       <c r="F46" t="s">
+        <v>48</v>
+      </c>
+      <c r="G46" t="s">
+        <v>41</v>
+      </c>
+      <c r="H46" t="s">
         <v>145</v>
       </c>
-      <c r="G46" t="s">
-        <v>41</v>
-      </c>
-      <c r="H46" t="s">
+      <c r="I46" t="s">
         <v>146</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>147</v>
       </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
+        <v>91</v>
+      </c>
+      <c r="L46" t="s">
         <v>148</v>
-      </c>
-      <c r="K46" t="s">
-        <v>57</v>
-      </c>
-      <c r="L46" t="s">
-        <v>34</v>
       </c>
       <c r="M46" t="s">
         <v>133</v>
@@ -4535,7 +4535,7 @@
         <v>140</v>
       </c>
       <c r="P46" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q46" t="s">
         <v>45</v>
@@ -4561,25 +4561,25 @@
         <v>149</v>
       </c>
       <c r="F47" t="s">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="G47" t="s">
         <v>41</v>
       </c>
       <c r="H47" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J47" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K47" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="L47" t="s">
-        <v>153</v>
+        <v>34</v>
       </c>
       <c r="M47" t="s">
         <v>133</v>
@@ -4591,7 +4591,7 @@
         <v>140</v>
       </c>
       <c r="P47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q47" t="s">
         <v>45</v>
@@ -4838,7 +4838,7 @@
         <v>33</v>
       </c>
       <c r="E52" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F52" t="s">
         <v>162</v>
@@ -5177,13 +5177,13 @@
         <v>190</v>
       </c>
       <c r="F58" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G58" t="s">
         <v>41</v>
       </c>
       <c r="H58" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I58" t="s">
         <v>191</v>
@@ -5513,7 +5513,7 @@
         <v>62</v>
       </c>
       <c r="F64" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G64" t="s">
         <v>41</v>
@@ -5569,13 +5569,13 @@
         <v>207</v>
       </c>
       <c r="F65" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G65" t="s">
         <v>41</v>
       </c>
       <c r="H65" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I65" t="s">
         <v>191</v>
@@ -5961,25 +5961,25 @@
         <v>225</v>
       </c>
       <c r="F72" t="s">
-        <v>48</v>
+        <v>226</v>
       </c>
       <c r="G72" t="s">
         <v>41</v>
       </c>
       <c r="H72" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="I72" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J72" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="K72" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="L72" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="M72" t="s">
         <v>223</v>
@@ -6017,25 +6017,25 @@
         <v>228</v>
       </c>
       <c r="F73" t="s">
+        <v>48</v>
+      </c>
+      <c r="G73" t="s">
+        <v>41</v>
+      </c>
+      <c r="H73" t="s">
+        <v>203</v>
+      </c>
+      <c r="I73" t="s">
         <v>229</v>
       </c>
-      <c r="G73" t="s">
-        <v>41</v>
-      </c>
-      <c r="H73" t="s">
-        <v>188</v>
-      </c>
-      <c r="I73" t="s">
+      <c r="J73" t="s">
+        <v>138</v>
+      </c>
+      <c r="K73" t="s">
+        <v>138</v>
+      </c>
+      <c r="L73" t="s">
         <v>230</v>
-      </c>
-      <c r="J73" t="s">
-        <v>87</v>
-      </c>
-      <c r="K73" t="s">
-        <v>87</v>
-      </c>
-      <c r="L73" t="s">
-        <v>212</v>
       </c>
       <c r="M73" t="s">
         <v>223</v>
@@ -6073,7 +6073,7 @@
         <v>233</v>
       </c>
       <c r="F74" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G74" t="s">
         <v>41</v>
@@ -6185,7 +6185,7 @@
         <v>242</v>
       </c>
       <c r="F76" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G76" t="s">
         <v>41</v>
@@ -6241,7 +6241,7 @@
         <v>245</v>
       </c>
       <c r="F77" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G77" t="s">
         <v>41</v>
@@ -6297,13 +6297,13 @@
         <v>249</v>
       </c>
       <c r="F78" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G78" t="s">
         <v>41</v>
       </c>
       <c r="H78" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I78" t="s">
         <v>250</v>
@@ -6353,13 +6353,13 @@
         <v>251</v>
       </c>
       <c r="F79" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G79" t="s">
         <v>41</v>
       </c>
       <c r="H79" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I79" t="s">
         <v>252</v>
@@ -6409,7 +6409,7 @@
         <v>253</v>
       </c>
       <c r="F80" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G80" t="s">
         <v>41</v>
@@ -6465,7 +6465,7 @@
         <v>257</v>
       </c>
       <c r="F81" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G81" t="s">
         <v>41</v>
@@ -6527,7 +6527,7 @@
         <v>41</v>
       </c>
       <c r="H82" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I82" t="s">
         <v>263</v>
@@ -6577,7 +6577,7 @@
         <v>265</v>
       </c>
       <c r="F83" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G83" t="s">
         <v>41</v>
@@ -6969,7 +6969,7 @@
         <v>282</v>
       </c>
       <c r="F90" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="G90" t="s">
         <v>41</v>
@@ -6981,13 +6981,13 @@
         <v>283</v>
       </c>
       <c r="J90" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="K90" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="L90" t="s">
-        <v>274</v>
+        <v>34</v>
       </c>
       <c r="M90" t="s">
         <v>271</v>
@@ -6996,7 +6996,7 @@
         <v>45</v>
       </c>
       <c r="O90" t="s">
-        <v>66</v>
+        <v>284</v>
       </c>
       <c r="P90" t="s">
         <v>283</v>
@@ -7022,7 +7022,7 @@
         <v>34</v>
       </c>
       <c r="E91" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F91" t="s">
         <v>187</v>
@@ -7031,16 +7031,16 @@
         <v>41</v>
       </c>
       <c r="H91" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="I91" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J91" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="K91" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="L91" t="s">
         <v>274</v>
@@ -7052,10 +7052,10 @@
         <v>45</v>
       </c>
       <c r="O91" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="P91" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q91" t="s">
         <v>45</v>
@@ -7078,7 +7078,7 @@
         <v>34</v>
       </c>
       <c r="E92" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F92" t="s">
         <v>187</v>
@@ -7087,10 +7087,10 @@
         <v>41</v>
       </c>
       <c r="H92" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="I92" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J92" t="s">
         <v>44</v>
@@ -7111,7 +7111,7 @@
         <v>46</v>
       </c>
       <c r="P92" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q92" t="s">
         <v>45</v>
@@ -7134,7 +7134,7 @@
         <v>34</v>
       </c>
       <c r="E93" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F93" t="s">
         <v>187</v>
@@ -7146,13 +7146,13 @@
         <v>272</v>
       </c>
       <c r="I93" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J93" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="K93" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L93" t="s">
         <v>274</v>
@@ -7164,10 +7164,10 @@
         <v>45</v>
       </c>
       <c r="O93" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="P93" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q93" t="s">
         <v>45</v>
@@ -7190,7 +7190,7 @@
         <v>34</v>
       </c>
       <c r="E94" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F94" t="s">
         <v>187</v>
@@ -7199,10 +7199,10 @@
         <v>41</v>
       </c>
       <c r="H94" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="I94" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J94" t="s">
         <v>52</v>
@@ -7223,7 +7223,7 @@
         <v>61</v>
       </c>
       <c r="P94" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q94" t="s">
         <v>45</v>
@@ -7246,7 +7246,7 @@
         <v>34</v>
       </c>
       <c r="E95" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F95" t="s">
         <v>187</v>
@@ -7258,13 +7258,13 @@
         <v>276</v>
       </c>
       <c r="I95" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J95" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="K95" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="L95" t="s">
         <v>274</v>
@@ -7276,10 +7276,10 @@
         <v>45</v>
       </c>
       <c r="O95" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="P95" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q95" t="s">
         <v>45</v>
@@ -7302,7 +7302,7 @@
         <v>34</v>
       </c>
       <c r="E96" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F96" t="s">
         <v>187</v>
@@ -7314,13 +7314,13 @@
         <v>276</v>
       </c>
       <c r="I96" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J96" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="K96" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="L96" t="s">
         <v>274</v>
@@ -7332,10 +7332,10 @@
         <v>45</v>
       </c>
       <c r="O96" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="P96" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q96" t="s">
         <v>45</v>
@@ -7358,7 +7358,7 @@
         <v>34</v>
       </c>
       <c r="E97" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F97" t="s">
         <v>187</v>
@@ -7367,10 +7367,10 @@
         <v>41</v>
       </c>
       <c r="H97" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="I97" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J97" t="s">
         <v>98</v>
@@ -7391,7 +7391,7 @@
         <v>99</v>
       </c>
       <c r="P97" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q97" t="s">
         <v>45</v>
@@ -7414,7 +7414,7 @@
         <v>34</v>
       </c>
       <c r="E98" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F98" t="s">
         <v>187</v>
@@ -7423,16 +7423,16 @@
         <v>41</v>
       </c>
       <c r="H98" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="I98" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J98" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="K98" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="L98" t="s">
         <v>274</v>
@@ -7444,10 +7444,10 @@
         <v>45</v>
       </c>
       <c r="O98" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="P98" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q98" t="s">
         <v>45</v>
@@ -7470,7 +7470,7 @@
         <v>34</v>
       </c>
       <c r="E99" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F99" t="s">
         <v>187</v>
@@ -7482,13 +7482,13 @@
         <v>276</v>
       </c>
       <c r="I99" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J99" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K99" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L99" t="s">
         <v>274</v>
@@ -7500,10 +7500,10 @@
         <v>45</v>
       </c>
       <c r="O99" t="s">
+        <v>81</v>
+      </c>
+      <c r="P99" t="s">
         <v>302</v>
-      </c>
-      <c r="P99" t="s">
-        <v>301</v>
       </c>
       <c r="Q99" t="s">
         <v>45</v>
@@ -7526,28 +7526,28 @@
         <v>34</v>
       </c>
       <c r="E100" t="s">
+        <v>39</v>
+      </c>
+      <c r="F100" t="s">
+        <v>150</v>
+      </c>
+      <c r="G100" t="s">
+        <v>41</v>
+      </c>
+      <c r="H100" t="s">
+        <v>272</v>
+      </c>
+      <c r="I100" t="s">
         <v>303</v>
       </c>
-      <c r="F100" t="s">
-        <v>187</v>
-      </c>
-      <c r="G100" t="s">
-        <v>41</v>
-      </c>
-      <c r="H100" t="s">
-        <v>276</v>
-      </c>
-      <c r="I100" t="s">
-        <v>304</v>
-      </c>
       <c r="J100" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="K100" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="L100" t="s">
-        <v>274</v>
+        <v>34</v>
       </c>
       <c r="M100" t="s">
         <v>271</v>
@@ -7556,10 +7556,10 @@
         <v>45</v>
       </c>
       <c r="O100" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="P100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q100" t="s">
         <v>45</v>
@@ -7582,7 +7582,7 @@
         <v>34</v>
       </c>
       <c r="E101" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F101" t="s">
         <v>187</v>
@@ -7591,16 +7591,16 @@
         <v>41</v>
       </c>
       <c r="H101" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="I101" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J101" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="K101" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="L101" t="s">
         <v>274</v>
@@ -7612,10 +7612,10 @@
         <v>45</v>
       </c>
       <c r="O101" t="s">
-        <v>81</v>
+        <v>306</v>
       </c>
       <c r="P101" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q101" t="s">
         <v>45</v>
@@ -7647,7 +7647,7 @@
         <v>41</v>
       </c>
       <c r="H102" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="I102" t="s">
         <v>308</v>
@@ -7709,10 +7709,10 @@
         <v>310</v>
       </c>
       <c r="J103" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K103" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L103" t="s">
         <v>274</v>
@@ -7724,7 +7724,7 @@
         <v>45</v>
       </c>
       <c r="O103" t="s">
-        <v>311</v>
+        <v>81</v>
       </c>
       <c r="P103" t="s">
         <v>310</v>
@@ -7750,7 +7750,7 @@
         <v>34</v>
       </c>
       <c r="E104" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F104" t="s">
         <v>187</v>
@@ -7759,16 +7759,16 @@
         <v>41</v>
       </c>
       <c r="H104" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="I104" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J104" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="K104" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="L104" t="s">
         <v>274</v>
@@ -7780,10 +7780,10 @@
         <v>45</v>
       </c>
       <c r="O104" t="s">
-        <v>58</v>
+        <v>121</v>
       </c>
       <c r="P104" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q104" t="s">
         <v>45</v>
@@ -7806,7 +7806,7 @@
         <v>34</v>
       </c>
       <c r="E105" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F105" t="s">
         <v>187</v>
@@ -7818,13 +7818,13 @@
         <v>272</v>
       </c>
       <c r="I105" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J105" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="K105" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="L105" t="s">
         <v>274</v>
@@ -7836,10 +7836,10 @@
         <v>45</v>
       </c>
       <c r="O105" t="s">
-        <v>58</v>
+        <v>315</v>
       </c>
       <c r="P105" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q105" t="s">
         <v>45</v>
@@ -7865,25 +7865,25 @@
         <v>316</v>
       </c>
       <c r="F106" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G106" t="s">
         <v>41</v>
       </c>
       <c r="H106" t="s">
-        <v>272</v>
+        <v>151</v>
       </c>
       <c r="I106" t="s">
+        <v>191</v>
+      </c>
+      <c r="J106" t="s">
+        <v>44</v>
+      </c>
+      <c r="K106" t="s">
+        <v>44</v>
+      </c>
+      <c r="L106" t="s">
         <v>317</v>
-      </c>
-      <c r="J106" t="s">
-        <v>57</v>
-      </c>
-      <c r="K106" t="s">
-        <v>57</v>
-      </c>
-      <c r="L106" t="s">
-        <v>34</v>
       </c>
       <c r="M106" t="s">
         <v>271</v>
@@ -7892,10 +7892,10 @@
         <v>45</v>
       </c>
       <c r="O106" t="s">
-        <v>318</v>
+        <v>192</v>
       </c>
       <c r="P106" t="s">
-        <v>317</v>
+        <v>191</v>
       </c>
       <c r="Q106" t="s">
         <v>45</v>
@@ -7918,28 +7918,28 @@
         <v>34</v>
       </c>
       <c r="E107" t="s">
-        <v>39</v>
+        <v>318</v>
       </c>
       <c r="F107" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="G107" t="s">
         <v>41</v>
       </c>
       <c r="H107" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="I107" t="s">
         <v>319</v>
       </c>
       <c r="J107" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="K107" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="L107" t="s">
-        <v>34</v>
+        <v>274</v>
       </c>
       <c r="M107" t="s">
         <v>271</v>
@@ -7948,7 +7948,7 @@
         <v>45</v>
       </c>
       <c r="O107" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="P107" t="s">
         <v>319</v>
@@ -7977,25 +7977,25 @@
         <v>320</v>
       </c>
       <c r="F108" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="G108" t="s">
         <v>41</v>
       </c>
       <c r="H108" t="s">
-        <v>146</v>
+        <v>272</v>
       </c>
       <c r="I108" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="J108" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="K108" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="L108" t="s">
-        <v>321</v>
+        <v>274</v>
       </c>
       <c r="M108" t="s">
         <v>271</v>
@@ -8004,10 +8004,10 @@
         <v>45</v>
       </c>
       <c r="O108" t="s">
-        <v>192</v>
+        <v>58</v>
       </c>
       <c r="P108" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="Q108" t="s">
         <v>45</v>
@@ -8033,7 +8033,7 @@
         <v>95</v>
       </c>
       <c r="F109" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G109" t="s">
         <v>41</v>
@@ -8089,7 +8089,7 @@
         <v>62</v>
       </c>
       <c r="F110" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G110" t="s">
         <v>41</v>
@@ -8098,7 +8098,7 @@
         <v>272</v>
       </c>
       <c r="I110" t="s">
-        <v>317</v>
+        <v>283</v>
       </c>
       <c r="J110" t="s">
         <v>65</v>
@@ -8119,7 +8119,7 @@
         <v>66</v>
       </c>
       <c r="P110" t="s">
-        <v>317</v>
+        <v>283</v>
       </c>
       <c r="Q110" t="s">
         <v>45</v>
@@ -8396,7 +8396,7 @@
         <v>45</v>
       </c>
       <c r="O115" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="P115" t="s">
         <v>332</v>
@@ -9012,7 +9012,7 @@
         <v>45</v>
       </c>
       <c r="O126" t="s">
-        <v>318</v>
+        <v>284</v>
       </c>
       <c r="P126" t="s">
         <v>347</v>
@@ -10188,7 +10188,7 @@
         <v>45</v>
       </c>
       <c r="O147" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="P147" t="s">
         <v>373</v>
@@ -10300,7 +10300,7 @@
         <v>45</v>
       </c>
       <c r="O149" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="P149" t="s">
         <v>375</v>
@@ -10860,7 +10860,7 @@
         <v>45</v>
       </c>
       <c r="O159" t="s">
-        <v>318</v>
+        <v>284</v>
       </c>
       <c r="P159" t="s">
         <v>378</v>
@@ -10916,7 +10916,7 @@
         <v>45</v>
       </c>
       <c r="O160" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="P160" t="s">
         <v>332</v>
@@ -11140,7 +11140,7 @@
         <v>45</v>
       </c>
       <c r="O164" t="s">
-        <v>318</v>
+        <v>284</v>
       </c>
       <c r="P164" t="s">
         <v>382</v>
@@ -11588,7 +11588,7 @@
         <v>45</v>
       </c>
       <c r="O172" t="s">
-        <v>318</v>
+        <v>284</v>
       </c>
       <c r="P172" t="s">
         <v>378</v>
@@ -11617,7 +11617,7 @@
         <v>215</v>
       </c>
       <c r="F173" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G173" t="s">
         <v>41</v>
@@ -11644,7 +11644,7 @@
         <v>45</v>
       </c>
       <c r="O173" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="P173" t="s">
         <v>332</v>
@@ -12513,7 +12513,7 @@
         <v>54</v>
       </c>
       <c r="F189" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G189" t="s">
         <v>41</v>
@@ -12625,7 +12625,7 @@
         <v>119</v>
       </c>
       <c r="F191" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G191" t="s">
         <v>41</v>
@@ -12681,7 +12681,7 @@
         <v>95</v>
       </c>
       <c r="F192" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G192" t="s">
         <v>41</v>
@@ -12737,7 +12737,7 @@
         <v>428</v>
       </c>
       <c r="F193" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G193" t="s">
         <v>41</v>
@@ -12764,7 +12764,7 @@
         <v>45</v>
       </c>
       <c r="O193" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="P193" t="s">
         <v>430</v>
@@ -12793,7 +12793,7 @@
         <v>59</v>
       </c>
       <c r="F194" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G194" t="s">
         <v>41</v>
@@ -12849,7 +12849,7 @@
         <v>62</v>
       </c>
       <c r="F195" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G195" t="s">
         <v>41</v>
@@ -12905,7 +12905,7 @@
         <v>88</v>
       </c>
       <c r="F196" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G196" t="s">
         <v>41</v>
@@ -12961,13 +12961,13 @@
         <v>436</v>
       </c>
       <c r="F197" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G197" t="s">
         <v>41</v>
       </c>
       <c r="H197" t="s">
-        <v>331</v>
+        <v>369</v>
       </c>
       <c r="I197" t="s">
         <v>437</v>
@@ -13017,13 +13017,13 @@
         <v>436</v>
       </c>
       <c r="F198" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G198" t="s">
         <v>41</v>
       </c>
       <c r="H198" t="s">
-        <v>369</v>
+        <v>331</v>
       </c>
       <c r="I198" t="s">
         <v>438</v>
@@ -13185,7 +13185,7 @@
         <v>186</v>
       </c>
       <c r="F201" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G201" t="s">
         <v>41</v>
@@ -13353,7 +13353,7 @@
         <v>95</v>
       </c>
       <c r="F204" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G204" t="s">
         <v>41</v>
@@ -13409,7 +13409,7 @@
         <v>452</v>
       </c>
       <c r="F205" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G205" t="s">
         <v>41</v>
@@ -13465,7 +13465,7 @@
         <v>455</v>
       </c>
       <c r="F206" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G206" t="s">
         <v>41</v>
@@ -13521,7 +13521,7 @@
         <v>59</v>
       </c>
       <c r="F207" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G207" t="s">
         <v>41</v>
@@ -13577,7 +13577,7 @@
         <v>54</v>
       </c>
       <c r="F208" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G208" t="s">
         <v>41</v>
@@ -13633,7 +13633,7 @@
         <v>460</v>
       </c>
       <c r="F209" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G209" t="s">
         <v>41</v>
@@ -13689,7 +13689,7 @@
         <v>464</v>
       </c>
       <c r="F210" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G210" t="s">
         <v>41</v>
@@ -13745,7 +13745,7 @@
         <v>345</v>
       </c>
       <c r="F211" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G211" t="s">
         <v>41</v>
@@ -13772,7 +13772,7 @@
         <v>45</v>
       </c>
       <c r="O211" t="s">
-        <v>318</v>
+        <v>284</v>
       </c>
       <c r="P211" t="s">
         <v>468</v>
@@ -13801,7 +13801,7 @@
         <v>469</v>
       </c>
       <c r="F212" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G212" t="s">
         <v>41</v>
@@ -13857,7 +13857,7 @@
         <v>472</v>
       </c>
       <c r="F213" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G213" t="s">
         <v>41</v>
@@ -13913,7 +13913,7 @@
         <v>474</v>
       </c>
       <c r="F214" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G214" t="s">
         <v>41</v>
@@ -13969,7 +13969,7 @@
         <v>477</v>
       </c>
       <c r="F215" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G215" t="s">
         <v>41</v>
@@ -14025,7 +14025,7 @@
         <v>480</v>
       </c>
       <c r="F216" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G216" t="s">
         <v>41</v>
@@ -14081,7 +14081,7 @@
         <v>483</v>
       </c>
       <c r="F217" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G217" t="s">
         <v>41</v>
@@ -14137,7 +14137,7 @@
         <v>485</v>
       </c>
       <c r="F218" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G218" t="s">
         <v>41</v>
@@ -14193,7 +14193,7 @@
         <v>488</v>
       </c>
       <c r="F219" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G219" t="s">
         <v>41</v>
@@ -14249,7 +14249,7 @@
         <v>491</v>
       </c>
       <c r="F220" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G220" t="s">
         <v>41</v>
@@ -14414,7 +14414,7 @@
         <v>33</v>
       </c>
       <c r="E223" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F223" t="s">
         <v>162</v>
@@ -14429,10 +14429,10 @@
         <v>499</v>
       </c>
       <c r="J223" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="K223" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="L223" t="s">
         <v>34</v>
@@ -14444,7 +14444,7 @@
         <v>45</v>
       </c>
       <c r="O223" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P223" t="s">
         <v>499</v>
@@ -14470,7 +14470,7 @@
         <v>34</v>
       </c>
       <c r="E224" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="F224" t="s">
         <v>162</v>
@@ -14485,10 +14485,10 @@
         <v>499</v>
       </c>
       <c r="J224" t="s">
-        <v>148</v>
+        <v>72</v>
       </c>
       <c r="K224" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="L224" t="s">
         <v>34</v>
@@ -14500,7 +14500,7 @@
         <v>45</v>
       </c>
       <c r="O224" t="s">
-        <v>81</v>
+        <v>306</v>
       </c>
       <c r="P224" t="s">
         <v>499</v>
@@ -14526,7 +14526,7 @@
         <v>34</v>
       </c>
       <c r="E225" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="F225" t="s">
         <v>162</v>
@@ -14541,10 +14541,10 @@
         <v>499</v>
       </c>
       <c r="J225" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K225" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="L225" t="s">
         <v>34</v>
@@ -14556,7 +14556,7 @@
         <v>45</v>
       </c>
       <c r="O225" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="P225" t="s">
         <v>499</v>
@@ -14582,7 +14582,7 @@
         <v>34</v>
       </c>
       <c r="E226" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="F226" t="s">
         <v>162</v>
@@ -14597,10 +14597,10 @@
         <v>499</v>
       </c>
       <c r="J226" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="K226" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="L226" t="s">
         <v>34</v>
@@ -14612,7 +14612,7 @@
         <v>45</v>
       </c>
       <c r="O226" t="s">
-        <v>302</v>
+        <v>92</v>
       </c>
       <c r="P226" t="s">
         <v>499</v>
@@ -14638,7 +14638,7 @@
         <v>34</v>
       </c>
       <c r="E227" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F227" t="s">
         <v>162</v>
@@ -14653,10 +14653,10 @@
         <v>499</v>
       </c>
       <c r="J227" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="K227" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="L227" t="s">
         <v>34</v>
@@ -14668,7 +14668,7 @@
         <v>45</v>
       </c>
       <c r="O227" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="P227" t="s">
         <v>499</v>
@@ -14694,7 +14694,7 @@
         <v>34</v>
       </c>
       <c r="E228" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="F228" t="s">
         <v>162</v>
@@ -14709,10 +14709,10 @@
         <v>499</v>
       </c>
       <c r="J228" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="K228" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="L228" t="s">
         <v>34</v>
@@ -14724,7 +14724,7 @@
         <v>45</v>
       </c>
       <c r="O228" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="P228" t="s">
         <v>499</v>
@@ -14750,7 +14750,7 @@
         <v>34</v>
       </c>
       <c r="E229" t="s">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="F229" t="s">
         <v>162</v>
@@ -14765,10 +14765,10 @@
         <v>499</v>
       </c>
       <c r="J229" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="K229" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="L229" t="s">
         <v>34</v>
@@ -14780,7 +14780,7 @@
         <v>45</v>
       </c>
       <c r="O229" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="P229" t="s">
         <v>499</v>
@@ -15045,13 +15045,13 @@
         <v>506</v>
       </c>
       <c r="J234" t="s">
-        <v>240</v>
+        <v>507</v>
       </c>
       <c r="K234" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="L234" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M234" t="s">
         <v>503</v>
@@ -15086,7 +15086,7 @@
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>149</v>
+        <v>504</v>
       </c>
       <c r="F235" t="s">
         <v>162</v>
@@ -15095,16 +15095,16 @@
         <v>41</v>
       </c>
       <c r="H235" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I235" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J235" t="s">
-        <v>510</v>
+        <v>240</v>
       </c>
       <c r="K235" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="L235" t="s">
         <v>511</v>
@@ -15119,7 +15119,7 @@
         <v>140</v>
       </c>
       <c r="P235" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Q235" t="s">
         <v>45</v>
@@ -15142,7 +15142,7 @@
         <v>34</v>
       </c>
       <c r="E236" t="s">
-        <v>504</v>
+        <v>144</v>
       </c>
       <c r="F236" t="s">
         <v>162</v>
@@ -15160,7 +15160,7 @@
         <v>514</v>
       </c>
       <c r="K236" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="L236" t="s">
         <v>515</v>
@@ -15437,7 +15437,7 @@
         <v>527</v>
       </c>
       <c r="J241" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="K241" t="s">
         <v>44</v>
@@ -15605,7 +15605,7 @@
         <v>535</v>
       </c>
       <c r="J244" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="K244" t="s">
         <v>44</v>
@@ -15649,7 +15649,7 @@
         <v>537</v>
       </c>
       <c r="F245" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G245" t="s">
         <v>41</v>
@@ -15717,7 +15717,7 @@
         <v>541</v>
       </c>
       <c r="J246" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="K246" t="s">
         <v>44</v>
@@ -15773,7 +15773,7 @@
         <v>543</v>
       </c>
       <c r="J247" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="K247" t="s">
         <v>44</v>
@@ -15829,7 +15829,7 @@
         <v>546</v>
       </c>
       <c r="J248" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="K248" t="s">
         <v>44</v>
@@ -15873,7 +15873,7 @@
         <v>548</v>
       </c>
       <c r="F249" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G249" t="s">
         <v>41</v>
@@ -15941,7 +15941,7 @@
         <v>527</v>
       </c>
       <c r="J250" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="K250" t="s">
         <v>44</v>
@@ -16041,7 +16041,7 @@
         <v>548</v>
       </c>
       <c r="F252" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G252" t="s">
         <v>41</v>
@@ -16094,7 +16094,7 @@
         <v>34</v>
       </c>
       <c r="E253" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F253" t="s">
         <v>162</v>
@@ -16150,7 +16150,7 @@
         <v>34</v>
       </c>
       <c r="E254" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F254" t="s">
         <v>162</v>
@@ -16277,7 +16277,7 @@
         <v>566</v>
       </c>
       <c r="J256" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="K256" t="s">
         <v>44</v>
@@ -16881,7 +16881,7 @@
         <v>590</v>
       </c>
       <c r="F267" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G267" t="s">
         <v>41</v>
@@ -16937,7 +16937,7 @@
         <v>590</v>
       </c>
       <c r="F268" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G268" t="s">
         <v>41</v>
@@ -17117,7 +17117,7 @@
         <v>601</v>
       </c>
       <c r="J271" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="K271" t="s">
         <v>138</v>
@@ -17161,7 +17161,7 @@
         <v>605</v>
       </c>
       <c r="F272" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G272" t="s">
         <v>41</v>
@@ -17397,7 +17397,7 @@
         <v>619</v>
       </c>
       <c r="J276" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="K276" t="s">
         <v>44</v>
@@ -17565,7 +17565,7 @@
         <v>631</v>
       </c>
       <c r="J279" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="K279" t="s">
         <v>550</v>
@@ -17665,7 +17665,7 @@
         <v>636</v>
       </c>
       <c r="F281" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G281" t="s">
         <v>41</v>
@@ -17677,10 +17677,10 @@
         <v>638</v>
       </c>
       <c r="J281" t="s">
-        <v>51</v>
+        <v>639</v>
       </c>
       <c r="K281" t="s">
-        <v>51</v>
+        <v>260</v>
       </c>
       <c r="L281" t="s">
         <v>34</v>
@@ -17718,25 +17718,25 @@
         <v>34</v>
       </c>
       <c r="E282" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F282" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G282" t="s">
         <v>41</v>
       </c>
       <c r="H282" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="I282" t="s">
         <v>638</v>
       </c>
       <c r="J282" t="s">
-        <v>91</v>
+        <v>641</v>
       </c>
       <c r="K282" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="L282" t="s">
         <v>34</v>
@@ -17774,28 +17774,28 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>641</v>
+        <v>599</v>
       </c>
       <c r="F283" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="G283" t="s">
         <v>41</v>
       </c>
       <c r="H283" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="I283" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="J283" t="s">
-        <v>642</v>
+        <v>507</v>
       </c>
       <c r="K283" t="s">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c r="L283" t="s">
-        <v>34</v>
+        <v>644</v>
       </c>
       <c r="M283" t="s">
         <v>635</v>
@@ -17807,7 +17807,7 @@
         <v>140</v>
       </c>
       <c r="P283" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="Q283" t="s">
         <v>45</v>
@@ -17830,28 +17830,28 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>599</v>
+        <v>645</v>
       </c>
       <c r="F284" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G284" t="s">
         <v>41</v>
       </c>
       <c r="H284" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="I284" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="J284" t="s">
-        <v>514</v>
+        <v>91</v>
       </c>
       <c r="K284" t="s">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="L284" t="s">
-        <v>645</v>
+        <v>34</v>
       </c>
       <c r="M284" t="s">
         <v>635</v>
@@ -17863,7 +17863,7 @@
         <v>140</v>
       </c>
       <c r="P284" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="Q284" t="s">
         <v>45</v>
@@ -17886,10 +17886,10 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F285" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G285" t="s">
         <v>41</v>
@@ -17898,13 +17898,13 @@
         <v>637</v>
       </c>
       <c r="I285" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="J285" t="s">
-        <v>550</v>
+        <v>51</v>
       </c>
       <c r="K285" t="s">
-        <v>550</v>
+        <v>51</v>
       </c>
       <c r="L285" t="s">
         <v>34</v>
@@ -17919,7 +17919,7 @@
         <v>140</v>
       </c>
       <c r="P285" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="Q285" t="s">
         <v>45</v>
@@ -17945,7 +17945,7 @@
         <v>648</v>
       </c>
       <c r="F286" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G286" t="s">
         <v>41</v>
@@ -17954,13 +17954,13 @@
         <v>637</v>
       </c>
       <c r="I286" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="J286" t="s">
-        <v>649</v>
+        <v>550</v>
       </c>
       <c r="K286" t="s">
-        <v>51</v>
+        <v>550</v>
       </c>
       <c r="L286" t="s">
         <v>34</v>
@@ -17975,7 +17975,7 @@
         <v>140</v>
       </c>
       <c r="P286" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="Q286" t="s">
         <v>45</v>
@@ -18057,7 +18057,7 @@
         <v>653</v>
       </c>
       <c r="F288" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G288" t="s">
         <v>41</v>
@@ -18072,7 +18072,7 @@
         <v>247</v>
       </c>
       <c r="K288" t="s">
-        <v>550</v>
+        <v>51</v>
       </c>
       <c r="L288" t="s">
         <v>656</v>
@@ -18113,7 +18113,7 @@
         <v>657</v>
       </c>
       <c r="F289" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G289" t="s">
         <v>41</v>
@@ -18128,7 +18128,7 @@
         <v>247</v>
       </c>
       <c r="K289" t="s">
-        <v>51</v>
+        <v>550</v>
       </c>
       <c r="L289" t="s">
         <v>660</v>
@@ -18237,7 +18237,7 @@
         <v>666</v>
       </c>
       <c r="J291" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="K291" t="s">
         <v>44</v>
@@ -18446,7 +18446,7 @@
         <v>33</v>
       </c>
       <c r="E295" t="s">
-        <v>504</v>
+        <v>682</v>
       </c>
       <c r="F295" t="s">
         <v>162</v>
@@ -18455,19 +18455,19 @@
         <v>41</v>
       </c>
       <c r="H295" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I295" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="J295" t="s">
-        <v>240</v>
+        <v>57</v>
       </c>
       <c r="K295" t="s">
-        <v>44</v>
+        <v>153</v>
       </c>
       <c r="L295" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M295" t="s">
         <v>681</v>
@@ -18479,7 +18479,7 @@
         <v>140</v>
       </c>
       <c r="P295" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="Q295" t="s">
         <v>45</v>
@@ -18502,7 +18502,7 @@
         <v>34</v>
       </c>
       <c r="E296" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F296" t="s">
         <v>162</v>
@@ -18511,16 +18511,16 @@
         <v>41</v>
       </c>
       <c r="H296" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="I296" t="s">
         <v>687</v>
       </c>
       <c r="J296" t="s">
-        <v>57</v>
+        <v>641</v>
       </c>
       <c r="K296" t="s">
-        <v>148</v>
+        <v>44</v>
       </c>
       <c r="L296" t="s">
         <v>688</v>
@@ -18573,7 +18573,7 @@
         <v>690</v>
       </c>
       <c r="J297" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="K297" t="s">
         <v>44</v>
@@ -18629,13 +18629,13 @@
         <v>693</v>
       </c>
       <c r="J298" t="s">
-        <v>649</v>
+        <v>694</v>
       </c>
       <c r="K298" t="s">
         <v>44</v>
       </c>
       <c r="L298" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M298" t="s">
         <v>681</v>
@@ -18670,7 +18670,7 @@
         <v>34</v>
       </c>
       <c r="E299" t="s">
-        <v>695</v>
+        <v>504</v>
       </c>
       <c r="F299" t="s">
         <v>162</v>
@@ -18679,13 +18679,13 @@
         <v>41</v>
       </c>
       <c r="H299" t="s">
-        <v>676</v>
+        <v>696</v>
       </c>
       <c r="I299" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="J299" t="s">
-        <v>697</v>
+        <v>240</v>
       </c>
       <c r="K299" t="s">
         <v>44</v>
@@ -18703,7 +18703,7 @@
         <v>140</v>
       </c>
       <c r="P299" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="Q299" t="s">
         <v>45</v>
@@ -18726,7 +18726,7 @@
         <v>34</v>
       </c>
       <c r="E300" t="s">
-        <v>504</v>
+        <v>699</v>
       </c>
       <c r="F300" t="s">
         <v>162</v>
@@ -18735,16 +18735,16 @@
         <v>41</v>
       </c>
       <c r="H300" t="s">
-        <v>676</v>
+        <v>700</v>
       </c>
       <c r="I300" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="J300" t="s">
-        <v>240</v>
+        <v>702</v>
       </c>
       <c r="K300" t="s">
-        <v>642</v>
+        <v>44</v>
       </c>
       <c r="L300" t="s">
         <v>700</v>
@@ -18759,7 +18759,7 @@
         <v>140</v>
       </c>
       <c r="P300" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="Q300" t="s">
         <v>45</v>
@@ -18782,7 +18782,7 @@
         <v>34</v>
       </c>
       <c r="E301" t="s">
-        <v>701</v>
+        <v>504</v>
       </c>
       <c r="F301" t="s">
         <v>162</v>
@@ -18791,19 +18791,19 @@
         <v>41</v>
       </c>
       <c r="H301" t="s">
-        <v>702</v>
+        <v>676</v>
       </c>
       <c r="I301" t="s">
         <v>703</v>
       </c>
       <c r="J301" t="s">
+        <v>240</v>
+      </c>
+      <c r="K301" t="s">
+        <v>639</v>
+      </c>
+      <c r="L301" t="s">
         <v>704</v>
-      </c>
-      <c r="K301" t="s">
-        <v>44</v>
-      </c>
-      <c r="L301" t="s">
-        <v>702</v>
       </c>
       <c r="M301" t="s">
         <v>681</v>
@@ -18909,7 +18909,7 @@
         <v>709</v>
       </c>
       <c r="J303" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="K303" t="s">
         <v>44</v>
@@ -19009,7 +19009,7 @@
         <v>715</v>
       </c>
       <c r="F305" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G305" t="s">
         <v>41</v>
@@ -19077,7 +19077,7 @@
         <v>722</v>
       </c>
       <c r="J306" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="K306" t="s">
         <v>44</v>
@@ -19121,7 +19121,7 @@
         <v>726</v>
       </c>
       <c r="F307" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G307" t="s">
         <v>41</v>
@@ -19289,7 +19289,7 @@
         <v>739</v>
       </c>
       <c r="F310" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G310" t="s">
         <v>41</v>
@@ -19357,7 +19357,7 @@
         <v>745</v>
       </c>
       <c r="J311" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="K311" t="s">
         <v>44</v>
@@ -19413,7 +19413,7 @@
         <v>748</v>
       </c>
       <c r="J312" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K312" t="s">
         <v>91</v>
@@ -19454,7 +19454,7 @@
         <v>33</v>
       </c>
       <c r="E313" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F313" t="s">
         <v>162</v>
@@ -19469,7 +19469,7 @@
         <v>753</v>
       </c>
       <c r="J313" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="K313" t="s">
         <v>44</v>
@@ -19681,7 +19681,7 @@
         <v>760</v>
       </c>
       <c r="F317" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G317" t="s">
         <v>41</v>

--- a/xlsx/dre/DRE_06_2026.xlsx
+++ b/xlsx/dre/DRE_06_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7060" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7060" uniqueCount="873">
   <si>
     <t>Movimentações Financeiras</t>
   </si>
@@ -1214,28 +1214,43 @@
     <t>R$ 7.548,44</t>
   </si>
   <si>
+    <t>R$  1.149,31</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA LEMOS</t>
+  </si>
+  <si>
+    <t>82201/1</t>
+  </si>
+  <si>
+    <t>R$  12,29</t>
+  </si>
+  <si>
+    <t>82201RuanCGS</t>
+  </si>
+  <si>
+    <t>79202/2</t>
+  </si>
+  <si>
+    <t>PPC</t>
+  </si>
+  <si>
+    <t>84601/2</t>
+  </si>
+  <si>
+    <t>R$  2,40</t>
+  </si>
+  <si>
     <t>Jose Carlos de Carvalho</t>
   </si>
   <si>
     <t>R$  1.229,74</t>
   </si>
   <si>
-    <t>RAYSSA BARBOSA LEMOS</t>
-  </si>
-  <si>
-    <t>82201/1</t>
-  </si>
-  <si>
-    <t>R$  12,29</t>
-  </si>
-  <si>
-    <t>82201RuanCGS</t>
-  </si>
-  <si>
-    <t>79202/2</t>
-  </si>
-  <si>
-    <t>PPC</t>
+    <t>82201/2</t>
+  </si>
+  <si>
+    <t>03/06/26</t>
   </si>
   <si>
     <t>R$  4.535,18</t>
@@ -1244,21 +1259,6 @@
     <t>85601/2</t>
   </si>
   <si>
-    <t>84601/2</t>
-  </si>
-  <si>
-    <t>R$  2,40</t>
-  </si>
-  <si>
-    <t>82201/2</t>
-  </si>
-  <si>
-    <t>03/06/26</t>
-  </si>
-  <si>
-    <t>R$  1.149,31</t>
-  </si>
-  <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
   </si>
   <si>
@@ -1628,6 +1628,48 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>Fixo jun26/1</t>
+  </si>
+  <si>
+    <t>EFRAIM RIBEIRO</t>
+  </si>
+  <si>
+    <t>R$  1.060,00</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>R$  2.365,00</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  4.687,39</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
     <t>GUTEMBERG DIAS GOMES</t>
   </si>
   <si>
@@ -1646,79 +1688,40 @@
     <t>R$  1.268,00</t>
   </si>
   <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  4.687,39</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>R$  2.365,00</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Fixo jun26/1</t>
+    <t>R$  1.679,77</t>
+  </si>
+  <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>R$  1.419,85</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
+  </si>
+  <si>
+    <t>R$  1.024,58</t>
+  </si>
+  <si>
+    <t>Rubens - Pagamento 2026</t>
   </si>
   <si>
     <t>R$  2.536,00</t>
   </si>
   <si>
+    <t>19/02/26</t>
+  </si>
+  <si>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
     <t>02/06/26</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
-    <t>R$  1.024,58</t>
-  </si>
-  <si>
-    <t>Rubens - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>EFRAIM RIBEIRO</t>
-  </si>
-  <si>
-    <t>R$  1.060,00</t>
-  </si>
-  <si>
-    <t>R$  1.679,77</t>
-  </si>
-  <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
-    <t>19/02/26</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
-    <t>R$  1.419,85</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
   </si>
   <si>
     <t>Denny Lucas do Carmo Pereira</t>
@@ -11446,7 +11449,7 @@
         <v>33</v>
       </c>
       <c r="E170" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F170" t="s">
         <v>187</v>
@@ -11455,16 +11458,16 @@
         <v>41</v>
       </c>
       <c r="H170" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="I170" t="s">
-        <v>338</v>
+        <v>396</v>
       </c>
       <c r="J170" t="s">
-        <v>388</v>
+        <v>103</v>
       </c>
       <c r="K170" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="L170" t="s">
         <v>34</v>
@@ -11476,10 +11479,10 @@
         <v>45</v>
       </c>
       <c r="O170" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="P170" t="s">
-        <v>338</v>
+        <v>396</v>
       </c>
       <c r="Q170" t="s">
         <v>45</v>
@@ -11502,25 +11505,25 @@
         <v>34</v>
       </c>
       <c r="E171" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="F171" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="G171" t="s">
         <v>41</v>
       </c>
       <c r="H171" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I171" t="s">
-        <v>397</v>
+        <v>332</v>
       </c>
       <c r="J171" t="s">
-        <v>388</v>
+        <v>44</v>
       </c>
       <c r="K171" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="L171" t="s">
         <v>34</v>
@@ -11532,10 +11535,10 @@
         <v>45</v>
       </c>
       <c r="O171" t="s">
-        <v>81</v>
+        <v>306</v>
       </c>
       <c r="P171" t="s">
-        <v>397</v>
+        <v>332</v>
       </c>
       <c r="Q171" t="s">
         <v>45</v>
@@ -11558,7 +11561,7 @@
         <v>34</v>
       </c>
       <c r="E172" t="s">
-        <v>345</v>
+        <v>197</v>
       </c>
       <c r="F172" t="s">
         <v>187</v>
@@ -11567,16 +11570,16 @@
         <v>41</v>
       </c>
       <c r="H172" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="I172" t="s">
-        <v>378</v>
+        <v>338</v>
       </c>
       <c r="J172" t="s">
-        <v>103</v>
+        <v>388</v>
       </c>
       <c r="K172" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="L172" t="s">
         <v>34</v>
@@ -11588,10 +11591,10 @@
         <v>45</v>
       </c>
       <c r="O172" t="s">
-        <v>284</v>
+        <v>66</v>
       </c>
       <c r="P172" t="s">
-        <v>378</v>
+        <v>338</v>
       </c>
       <c r="Q172" t="s">
         <v>45</v>
@@ -11614,22 +11617,22 @@
         <v>34</v>
       </c>
       <c r="E173" t="s">
-        <v>215</v>
+        <v>398</v>
       </c>
       <c r="F173" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="G173" t="s">
         <v>41</v>
       </c>
       <c r="H173" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="I173" t="s">
-        <v>332</v>
+        <v>399</v>
       </c>
       <c r="J173" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="K173" t="s">
         <v>44</v>
@@ -11644,10 +11647,10 @@
         <v>45</v>
       </c>
       <c r="O173" t="s">
-        <v>306</v>
+        <v>400</v>
       </c>
       <c r="P173" t="s">
-        <v>332</v>
+        <v>399</v>
       </c>
       <c r="Q173" t="s">
         <v>45</v>
@@ -11670,25 +11673,25 @@
         <v>34</v>
       </c>
       <c r="E174" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F174" t="s">
-        <v>187</v>
+        <v>402</v>
       </c>
       <c r="G174" t="s">
         <v>41</v>
       </c>
       <c r="H174" t="s">
-        <v>389</v>
+        <v>203</v>
       </c>
       <c r="I174" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
       <c r="J174" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K174" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="L174" t="s">
         <v>34</v>
@@ -11700,13 +11703,13 @@
         <v>45</v>
       </c>
       <c r="O174" t="s">
-        <v>401</v>
+        <v>34</v>
       </c>
       <c r="P174" t="s">
-        <v>400</v>
+        <v>34</v>
       </c>
       <c r="Q174" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R174" t="s">
         <v>34</v>
@@ -11782,10 +11785,10 @@
         <v>34</v>
       </c>
       <c r="E176" t="s">
+        <v>403</v>
+      </c>
+      <c r="F176" t="s">
         <v>402</v>
-      </c>
-      <c r="F176" t="s">
-        <v>403</v>
       </c>
       <c r="G176" t="s">
         <v>41</v>
@@ -11794,13 +11797,13 @@
         <v>203</v>
       </c>
       <c r="I176" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="J176" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="K176" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="L176" t="s">
         <v>34</v>
@@ -11838,25 +11841,25 @@
         <v>34</v>
       </c>
       <c r="E177" t="s">
-        <v>278</v>
+        <v>186</v>
       </c>
       <c r="F177" t="s">
-        <v>403</v>
+        <v>187</v>
       </c>
       <c r="G177" t="s">
         <v>41</v>
       </c>
       <c r="H177" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="I177" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J177" t="s">
-        <v>117</v>
+        <v>388</v>
       </c>
       <c r="K177" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="L177" t="s">
         <v>34</v>
@@ -11868,13 +11871,13 @@
         <v>45</v>
       </c>
       <c r="O177" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="P177" t="s">
-        <v>34</v>
+        <v>406</v>
       </c>
       <c r="Q177" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R177" t="s">
         <v>34</v>
@@ -11894,10 +11897,10 @@
         <v>34</v>
       </c>
       <c r="E178" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F178" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G178" t="s">
         <v>41</v>
@@ -11906,13 +11909,13 @@
         <v>203</v>
       </c>
       <c r="I178" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="J178" t="s">
-        <v>57</v>
+        <v>408</v>
       </c>
       <c r="K178" t="s">
-        <v>57</v>
+        <v>408</v>
       </c>
       <c r="L178" t="s">
         <v>34</v>
@@ -11950,25 +11953,25 @@
         <v>34</v>
       </c>
       <c r="E179" t="s">
-        <v>406</v>
+        <v>278</v>
       </c>
       <c r="F179" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G179" t="s">
         <v>41</v>
       </c>
       <c r="H179" t="s">
-        <v>203</v>
+        <v>405</v>
       </c>
       <c r="I179" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J179" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="K179" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="L179" t="s">
         <v>34</v>
@@ -12006,10 +12009,10 @@
         <v>34</v>
       </c>
       <c r="E180" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F180" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G180" t="s">
         <v>41</v>
@@ -12018,13 +12021,13 @@
         <v>203</v>
       </c>
       <c r="I180" t="s">
-        <v>400</v>
+        <v>378</v>
       </c>
       <c r="J180" t="s">
-        <v>409</v>
+        <v>57</v>
       </c>
       <c r="K180" t="s">
-        <v>409</v>
+        <v>57</v>
       </c>
       <c r="L180" t="s">
         <v>34</v>
@@ -12062,7 +12065,7 @@
         <v>34</v>
       </c>
       <c r="E181" t="s">
-        <v>195</v>
+        <v>345</v>
       </c>
       <c r="F181" t="s">
         <v>187</v>
@@ -12074,13 +12077,13 @@
         <v>389</v>
       </c>
       <c r="I181" t="s">
-        <v>410</v>
+        <v>378</v>
       </c>
       <c r="J181" t="s">
         <v>103</v>
       </c>
       <c r="K181" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L181" t="s">
         <v>34</v>
@@ -12092,10 +12095,10 @@
         <v>45</v>
       </c>
       <c r="O181" t="s">
-        <v>61</v>
+        <v>284</v>
       </c>
       <c r="P181" t="s">
-        <v>410</v>
+        <v>378</v>
       </c>
       <c r="Q181" t="s">
         <v>45</v>
@@ -12118,10 +12121,10 @@
         <v>33</v>
       </c>
       <c r="E182" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F182" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G182" t="s">
         <v>41</v>
@@ -12133,10 +12136,10 @@
         <v>413</v>
       </c>
       <c r="J182" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K182" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="L182" t="s">
         <v>34</v>
@@ -12177,7 +12180,7 @@
         <v>199</v>
       </c>
       <c r="F183" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G183" t="s">
         <v>41</v>
@@ -12233,7 +12236,7 @@
         <v>415</v>
       </c>
       <c r="F184" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G184" t="s">
         <v>41</v>
@@ -12289,7 +12292,7 @@
         <v>186</v>
       </c>
       <c r="F185" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G185" t="s">
         <v>41</v>
@@ -12345,7 +12348,7 @@
         <v>345</v>
       </c>
       <c r="F186" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G186" t="s">
         <v>41</v>
@@ -12401,7 +12404,7 @@
         <v>221</v>
       </c>
       <c r="F187" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G187" t="s">
         <v>41</v>
@@ -12457,7 +12460,7 @@
         <v>358</v>
       </c>
       <c r="F188" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G188" t="s">
         <v>41</v>
@@ -12569,7 +12572,7 @@
         <v>107</v>
       </c>
       <c r="F190" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G190" t="s">
         <v>41</v>
@@ -12805,7 +12808,7 @@
         <v>431</v>
       </c>
       <c r="J194" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K194" t="s">
         <v>52</v>
@@ -15590,28 +15593,28 @@
         <v>33</v>
       </c>
       <c r="E244" t="s">
-        <v>504</v>
+        <v>534</v>
       </c>
       <c r="F244" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G244" t="s">
         <v>41</v>
       </c>
       <c r="H244" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I244" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J244" t="s">
-        <v>507</v>
+        <v>138</v>
       </c>
       <c r="K244" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="L244" t="s">
-        <v>536</v>
+        <v>34</v>
       </c>
       <c r="M244" t="s">
         <v>533</v>
@@ -15623,7 +15626,7 @@
         <v>140</v>
       </c>
       <c r="P244" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="Q244" t="s">
         <v>45</v>
@@ -15646,28 +15649,28 @@
         <v>34</v>
       </c>
       <c r="E245" t="s">
+        <v>504</v>
+      </c>
+      <c r="F245" t="s">
+        <v>162</v>
+      </c>
+      <c r="G245" t="s">
+        <v>41</v>
+      </c>
+      <c r="H245" t="s">
         <v>537</v>
       </c>
-      <c r="F245" t="s">
-        <v>150</v>
-      </c>
-      <c r="G245" t="s">
-        <v>41</v>
-      </c>
-      <c r="H245" t="s">
+      <c r="I245" t="s">
         <v>538</v>
       </c>
-      <c r="I245" t="s">
+      <c r="J245" t="s">
+        <v>507</v>
+      </c>
+      <c r="K245" t="s">
+        <v>44</v>
+      </c>
+      <c r="L245" t="s">
         <v>539</v>
-      </c>
-      <c r="J245" t="s">
-        <v>138</v>
-      </c>
-      <c r="K245" t="s">
-        <v>138</v>
-      </c>
-      <c r="L245" t="s">
-        <v>34</v>
       </c>
       <c r="M245" t="s">
         <v>533</v>
@@ -15679,7 +15682,7 @@
         <v>140</v>
       </c>
       <c r="P245" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="Q245" t="s">
         <v>45</v>
@@ -15767,10 +15770,10 @@
         <v>41</v>
       </c>
       <c r="H247" t="s">
-        <v>381</v>
+        <v>543</v>
       </c>
       <c r="I247" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="J247" t="s">
         <v>507</v>
@@ -15791,7 +15794,7 @@
         <v>140</v>
       </c>
       <c r="P247" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="Q247" t="s">
         <v>45</v>
@@ -15870,28 +15873,28 @@
         <v>34</v>
       </c>
       <c r="E249" t="s">
+        <v>504</v>
+      </c>
+      <c r="F249" t="s">
+        <v>162</v>
+      </c>
+      <c r="G249" t="s">
+        <v>41</v>
+      </c>
+      <c r="H249" t="s">
         <v>548</v>
-      </c>
-      <c r="F249" t="s">
-        <v>150</v>
-      </c>
-      <c r="G249" t="s">
-        <v>41</v>
-      </c>
-      <c r="H249" t="s">
-        <v>354</v>
       </c>
       <c r="I249" t="s">
         <v>549</v>
       </c>
       <c r="J249" t="s">
-        <v>177</v>
+        <v>507</v>
       </c>
       <c r="K249" t="s">
+        <v>44</v>
+      </c>
+      <c r="L249" t="s">
         <v>550</v>
-      </c>
-      <c r="L249" t="s">
-        <v>34</v>
       </c>
       <c r="M249" t="s">
         <v>533</v>
@@ -15926,28 +15929,28 @@
         <v>34</v>
       </c>
       <c r="E250" t="s">
-        <v>504</v>
+        <v>551</v>
       </c>
       <c r="F250" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G250" t="s">
         <v>41</v>
       </c>
       <c r="H250" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I250" t="s">
-        <v>527</v>
+        <v>553</v>
       </c>
       <c r="J250" t="s">
-        <v>507</v>
+        <v>138</v>
       </c>
       <c r="K250" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="L250" t="s">
-        <v>552</v>
+        <v>34</v>
       </c>
       <c r="M250" t="s">
         <v>533</v>
@@ -15959,7 +15962,7 @@
         <v>140</v>
       </c>
       <c r="P250" t="s">
-        <v>527</v>
+        <v>553</v>
       </c>
       <c r="Q250" t="s">
         <v>45</v>
@@ -15982,7 +15985,7 @@
         <v>34</v>
       </c>
       <c r="E251" t="s">
-        <v>504</v>
+        <v>144</v>
       </c>
       <c r="F251" t="s">
         <v>162</v>
@@ -15991,19 +15994,19 @@
         <v>41</v>
       </c>
       <c r="H251" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="I251" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="J251" t="s">
-        <v>240</v>
+        <v>555</v>
       </c>
       <c r="K251" t="s">
         <v>44</v>
       </c>
       <c r="L251" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="M251" t="s">
         <v>533</v>
@@ -16015,7 +16018,7 @@
         <v>140</v>
       </c>
       <c r="P251" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="Q251" t="s">
         <v>45</v>
@@ -16038,28 +16041,28 @@
         <v>34</v>
       </c>
       <c r="E252" t="s">
-        <v>548</v>
+        <v>516</v>
       </c>
       <c r="F252" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="G252" t="s">
         <v>41</v>
       </c>
       <c r="H252" t="s">
-        <v>555</v>
+        <v>331</v>
       </c>
       <c r="I252" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="J252" t="s">
-        <v>138</v>
+        <v>558</v>
       </c>
       <c r="K252" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="L252" t="s">
-        <v>34</v>
+        <v>559</v>
       </c>
       <c r="M252" t="s">
         <v>533</v>
@@ -16071,7 +16074,7 @@
         <v>140</v>
       </c>
       <c r="P252" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Q252" t="s">
         <v>45</v>
@@ -16094,7 +16097,7 @@
         <v>34</v>
       </c>
       <c r="E253" t="s">
-        <v>144</v>
+        <v>504</v>
       </c>
       <c r="F253" t="s">
         <v>162</v>
@@ -16103,19 +16106,19 @@
         <v>41</v>
       </c>
       <c r="H253" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="I253" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="J253" t="s">
-        <v>558</v>
+        <v>240</v>
       </c>
       <c r="K253" t="s">
         <v>44</v>
       </c>
       <c r="L253" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="M253" t="s">
         <v>533</v>
@@ -16127,7 +16130,7 @@
         <v>140</v>
       </c>
       <c r="P253" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="Q253" t="s">
         <v>45</v>
@@ -16162,16 +16165,16 @@
         <v>348</v>
       </c>
       <c r="I254" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="J254" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K254" t="s">
         <v>44</v>
       </c>
       <c r="L254" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="M254" t="s">
         <v>533</v>
@@ -16183,7 +16186,7 @@
         <v>140</v>
       </c>
       <c r="P254" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="Q254" t="s">
         <v>45</v>
@@ -16206,28 +16209,28 @@
         <v>34</v>
       </c>
       <c r="E255" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="F255" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G255" t="s">
         <v>41</v>
       </c>
       <c r="H255" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="I255" t="s">
         <v>562</v>
       </c>
       <c r="J255" t="s">
-        <v>563</v>
+        <v>177</v>
       </c>
       <c r="K255" t="s">
-        <v>44</v>
+        <v>565</v>
       </c>
       <c r="L255" t="s">
-        <v>564</v>
+        <v>34</v>
       </c>
       <c r="M255" t="s">
         <v>533</v>
@@ -16271,10 +16274,10 @@
         <v>41</v>
       </c>
       <c r="H256" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="I256" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="J256" t="s">
         <v>507</v>
@@ -16283,7 +16286,7 @@
         <v>44</v>
       </c>
       <c r="L256" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M256" t="s">
         <v>533</v>
@@ -16295,7 +16298,7 @@
         <v>140</v>
       </c>
       <c r="P256" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="Q256" t="s">
         <v>45</v>
@@ -16306,13 +16309,13 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="1">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B257" t="s" s="1">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C257" t="s" s="1">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D257" t="s" s="1">
         <v>33</v>
@@ -16362,13 +16365,13 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
+        <v>571</v>
+      </c>
+      <c r="B258" t="s">
         <v>570</v>
       </c>
-      <c r="B258" t="s">
-        <v>569</v>
-      </c>
       <c r="C258" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D258" t="s">
         <v>33</v>
@@ -16395,10 +16398,10 @@
         <v>80</v>
       </c>
       <c r="L258" t="s">
+        <v>572</v>
+      </c>
+      <c r="M258" t="s">
         <v>571</v>
-      </c>
-      <c r="M258" t="s">
-        <v>570</v>
       </c>
       <c r="N258" t="s">
         <v>45</v>
@@ -16418,13 +16421,13 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="1">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B259" t="s" s="1">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C259" t="s" s="1">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D259" t="s" s="1">
         <v>33</v>
@@ -16474,13 +16477,13 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
+        <v>575</v>
+      </c>
+      <c r="B260" t="s">
         <v>574</v>
       </c>
-      <c r="B260" t="s">
-        <v>573</v>
-      </c>
       <c r="C260" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D260" t="s">
         <v>33</v>
@@ -16507,10 +16510,10 @@
         <v>80</v>
       </c>
       <c r="L260" t="s">
+        <v>576</v>
+      </c>
+      <c r="M260" t="s">
         <v>575</v>
-      </c>
-      <c r="M260" t="s">
-        <v>574</v>
       </c>
       <c r="N260" t="s">
         <v>45</v>
@@ -16530,13 +16533,13 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="1">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B261" t="s" s="1">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C261" t="s" s="1">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D261" t="s" s="1">
         <v>33</v>
@@ -16586,13 +16589,13 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
+        <v>579</v>
+      </c>
+      <c r="B262" t="s">
         <v>578</v>
       </c>
-      <c r="B262" t="s">
-        <v>577</v>
-      </c>
       <c r="C262" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D262" t="s">
         <v>33</v>
@@ -16607,10 +16610,10 @@
         <v>41</v>
       </c>
       <c r="H262" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="I262" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="J262" t="s">
         <v>165</v>
@@ -16619,10 +16622,10 @@
         <v>80</v>
       </c>
       <c r="L262" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M262" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N262" t="s">
         <v>45</v>
@@ -16631,7 +16634,7 @@
         <v>140</v>
       </c>
       <c r="P262" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Q262" t="s">
         <v>45</v>
@@ -16642,13 +16645,13 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="1">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B263" t="s" s="1">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C263" t="s" s="1">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D263" t="s" s="1">
         <v>33</v>
@@ -16698,13 +16701,13 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
+        <v>585</v>
+      </c>
+      <c r="B264" t="s">
         <v>584</v>
       </c>
-      <c r="B264" t="s">
-        <v>583</v>
-      </c>
       <c r="C264" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D264" t="s">
         <v>33</v>
@@ -16722,7 +16725,7 @@
         <v>203</v>
       </c>
       <c r="I264" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="J264" t="s">
         <v>165</v>
@@ -16734,7 +16737,7 @@
         <v>34</v>
       </c>
       <c r="M264" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N264" t="s">
         <v>45</v>
@@ -16754,13 +16757,13 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="1">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B265" t="s" s="1">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C265" t="s" s="1">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D265" t="s" s="1">
         <v>33</v>
@@ -16810,13 +16813,13 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="1">
+        <v>589</v>
+      </c>
+      <c r="B266" t="s" s="1">
         <v>588</v>
       </c>
-      <c r="B266" t="s" s="1">
-        <v>587</v>
-      </c>
       <c r="C266" t="s" s="1">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D266" t="s" s="1">
         <v>33</v>
@@ -16866,19 +16869,19 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B267" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C267" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D267" t="s">
         <v>33</v>
       </c>
       <c r="E267" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F267" t="s">
         <v>150</v>
@@ -16890,7 +16893,7 @@
         <v>369</v>
       </c>
       <c r="I267" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="J267" t="s">
         <v>138</v>
@@ -16902,7 +16905,7 @@
         <v>34</v>
       </c>
       <c r="M267" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N267" t="s">
         <v>45</v>
@@ -16911,7 +16914,7 @@
         <v>140</v>
       </c>
       <c r="P267" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Q267" t="s">
         <v>45</v>
@@ -16922,7 +16925,7 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B268" t="s">
         <v>34</v>
@@ -16934,7 +16937,7 @@
         <v>34</v>
       </c>
       <c r="E268" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F268" t="s">
         <v>150</v>
@@ -16946,7 +16949,7 @@
         <v>331</v>
       </c>
       <c r="I268" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J268" t="s">
         <v>138</v>
@@ -16958,7 +16961,7 @@
         <v>34</v>
       </c>
       <c r="M268" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N268" t="s">
         <v>45</v>
@@ -16967,7 +16970,7 @@
         <v>140</v>
       </c>
       <c r="P268" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Q268" t="s">
         <v>45</v>
@@ -16978,13 +16981,13 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="1">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B269" t="s" s="1">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C269" t="s" s="1">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D269" t="s" s="1">
         <v>33</v>
@@ -17034,13 +17037,13 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="1">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B270" t="s" s="1">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C270" t="s" s="1">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D270" t="s" s="1">
         <v>33</v>
@@ -17090,19 +17093,19 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B271" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C271" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D271" t="s">
         <v>33</v>
       </c>
       <c r="E271" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F271" t="s">
         <v>162</v>
@@ -17111,10 +17114,10 @@
         <v>41</v>
       </c>
       <c r="H271" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I271" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="J271" t="s">
         <v>507</v>
@@ -17123,10 +17126,10 @@
         <v>138</v>
       </c>
       <c r="L271" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M271" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N271" t="s">
         <v>45</v>
@@ -17135,7 +17138,7 @@
         <v>140</v>
       </c>
       <c r="P271" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="Q271" t="s">
         <v>45</v>
@@ -17146,19 +17149,19 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B272" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C272" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D272" t="s">
         <v>33</v>
       </c>
       <c r="E272" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F272" t="s">
         <v>150</v>
@@ -17170,7 +17173,7 @@
         <v>142</v>
       </c>
       <c r="I272" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="J272" t="s">
         <v>138</v>
@@ -17182,7 +17185,7 @@
         <v>34</v>
       </c>
       <c r="M272" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N272" t="s">
         <v>45</v>
@@ -17191,7 +17194,7 @@
         <v>140</v>
       </c>
       <c r="P272" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Q272" t="s">
         <v>45</v>
@@ -17202,13 +17205,13 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="1">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B273" t="s" s="1">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C273" t="s" s="1">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D273" t="s" s="1">
         <v>33</v>
@@ -17258,19 +17261,19 @@
     </row>
     <row r="274">
       <c r="A274" t="s">
+        <v>610</v>
+      </c>
+      <c r="B274" t="s">
         <v>609</v>
       </c>
-      <c r="B274" t="s">
-        <v>608</v>
-      </c>
       <c r="C274" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D274" t="s">
         <v>33</v>
       </c>
       <c r="E274" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F274" t="s">
         <v>162</v>
@@ -17279,22 +17282,22 @@
         <v>41</v>
       </c>
       <c r="H274" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I274" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="J274" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="K274" t="s">
         <v>65</v>
       </c>
       <c r="L274" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M274" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N274" t="s">
         <v>45</v>
@@ -17303,7 +17306,7 @@
         <v>140</v>
       </c>
       <c r="P274" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="Q274" t="s">
         <v>45</v>
@@ -17314,13 +17317,13 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="1">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B275" t="s" s="1">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C275" t="s" s="1">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D275" t="s" s="1">
         <v>33</v>
@@ -17370,13 +17373,13 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
+        <v>618</v>
+      </c>
+      <c r="B276" t="s">
         <v>617</v>
       </c>
-      <c r="B276" t="s">
-        <v>616</v>
-      </c>
       <c r="C276" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D276" t="s">
         <v>33</v>
@@ -17391,10 +17394,10 @@
         <v>41</v>
       </c>
       <c r="H276" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I276" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="J276" t="s">
         <v>507</v>
@@ -17403,10 +17406,10 @@
         <v>44</v>
       </c>
       <c r="L276" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M276" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N276" t="s">
         <v>45</v>
@@ -17415,7 +17418,7 @@
         <v>140</v>
       </c>
       <c r="P276" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Q276" t="s">
         <v>45</v>
@@ -17426,13 +17429,13 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="1">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B277" t="s" s="1">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C277" t="s" s="1">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D277" t="s" s="1">
         <v>33</v>
@@ -17482,19 +17485,19 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B278" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C278" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D278" t="s">
         <v>33</v>
       </c>
       <c r="E278" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F278" t="s">
         <v>162</v>
@@ -17503,22 +17506,22 @@
         <v>41</v>
       </c>
       <c r="H278" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="I278" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="J278" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="K278" t="s">
         <v>110</v>
       </c>
       <c r="L278" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M278" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N278" t="s">
         <v>45</v>
@@ -17527,7 +17530,7 @@
         <v>140</v>
       </c>
       <c r="P278" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="Q278" t="s">
         <v>45</v>
@@ -17538,13 +17541,13 @@
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B279" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C279" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D279" t="s">
         <v>33</v>
@@ -17559,22 +17562,22 @@
         <v>41</v>
       </c>
       <c r="H279" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="I279" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="J279" t="s">
         <v>507</v>
       </c>
       <c r="K279" t="s">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="L279" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M279" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N279" t="s">
         <v>45</v>
@@ -17583,7 +17586,7 @@
         <v>140</v>
       </c>
       <c r="P279" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="Q279" t="s">
         <v>45</v>
@@ -17594,13 +17597,13 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="1">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B280" t="s" s="1">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C280" t="s" s="1">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D280" t="s" s="1">
         <v>33</v>
@@ -17650,19 +17653,19 @@
     </row>
     <row r="281">
       <c r="A281" t="s">
+        <v>636</v>
+      </c>
+      <c r="B281" t="s">
         <v>635</v>
       </c>
-      <c r="B281" t="s">
-        <v>634</v>
-      </c>
       <c r="C281" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D281" t="s">
         <v>33</v>
       </c>
       <c r="E281" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F281" t="s">
         <v>150</v>
@@ -17671,13 +17674,13 @@
         <v>41</v>
       </c>
       <c r="H281" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I281" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="J281" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="K281" t="s">
         <v>260</v>
@@ -17686,7 +17689,7 @@
         <v>34</v>
       </c>
       <c r="M281" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N281" t="s">
         <v>45</v>
@@ -17695,7 +17698,7 @@
         <v>140</v>
       </c>
       <c r="P281" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="Q281" t="s">
         <v>45</v>
@@ -17706,7 +17709,7 @@
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B282" t="s">
         <v>34</v>
@@ -17718,7 +17721,7 @@
         <v>34</v>
       </c>
       <c r="E282" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F282" t="s">
         <v>150</v>
@@ -17727,13 +17730,13 @@
         <v>41</v>
       </c>
       <c r="H282" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I282" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="J282" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K282" t="s">
         <v>51</v>
@@ -17742,7 +17745,7 @@
         <v>34</v>
       </c>
       <c r="M282" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N282" t="s">
         <v>45</v>
@@ -17751,7 +17754,7 @@
         <v>140</v>
       </c>
       <c r="P282" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="Q282" t="s">
         <v>45</v>
@@ -17762,7 +17765,7 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B283" t="s">
         <v>34</v>
@@ -17774,7 +17777,7 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F283" t="s">
         <v>162</v>
@@ -17783,10 +17786,10 @@
         <v>41</v>
       </c>
       <c r="H283" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="I283" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="J283" t="s">
         <v>507</v>
@@ -17795,10 +17798,10 @@
         <v>138</v>
       </c>
       <c r="L283" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M283" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N283" t="s">
         <v>45</v>
@@ -17807,7 +17810,7 @@
         <v>140</v>
       </c>
       <c r="P283" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Q283" t="s">
         <v>45</v>
@@ -17818,7 +17821,7 @@
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B284" t="s">
         <v>34</v>
@@ -17830,7 +17833,7 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F284" t="s">
         <v>150</v>
@@ -17839,10 +17842,10 @@
         <v>41</v>
       </c>
       <c r="H284" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="I284" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="J284" t="s">
         <v>91</v>
@@ -17854,7 +17857,7 @@
         <v>34</v>
       </c>
       <c r="M284" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N284" t="s">
         <v>45</v>
@@ -17863,7 +17866,7 @@
         <v>140</v>
       </c>
       <c r="P284" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="Q284" t="s">
         <v>45</v>
@@ -17874,7 +17877,7 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B285" t="s">
         <v>34</v>
@@ -17886,7 +17889,7 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F285" t="s">
         <v>150</v>
@@ -17895,10 +17898,10 @@
         <v>41</v>
       </c>
       <c r="H285" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I285" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="J285" t="s">
         <v>51</v>
@@ -17910,7 +17913,7 @@
         <v>34</v>
       </c>
       <c r="M285" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N285" t="s">
         <v>45</v>
@@ -17919,7 +17922,7 @@
         <v>140</v>
       </c>
       <c r="P285" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="Q285" t="s">
         <v>45</v>
@@ -17930,7 +17933,7 @@
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B286" t="s">
         <v>34</v>
@@ -17942,7 +17945,7 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F286" t="s">
         <v>150</v>
@@ -17951,22 +17954,22 @@
         <v>41</v>
       </c>
       <c r="H286" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I286" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="J286" t="s">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="K286" t="s">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="L286" t="s">
         <v>34</v>
       </c>
       <c r="M286" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N286" t="s">
         <v>45</v>
@@ -17975,7 +17978,7 @@
         <v>140</v>
       </c>
       <c r="P286" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="Q286" t="s">
         <v>45</v>
@@ -17986,13 +17989,13 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="1">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B287" t="s" s="1">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C287" t="s" s="1">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D287" t="s" s="1">
         <v>33</v>
@@ -18042,19 +18045,19 @@
     </row>
     <row r="288">
       <c r="A288" t="s">
+        <v>653</v>
+      </c>
+      <c r="B288" t="s">
         <v>652</v>
       </c>
-      <c r="B288" t="s">
-        <v>651</v>
-      </c>
       <c r="C288" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D288" t="s">
         <v>33</v>
       </c>
       <c r="E288" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F288" t="s">
         <v>150</v>
@@ -18063,10 +18066,10 @@
         <v>41</v>
       </c>
       <c r="H288" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="I288" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="J288" t="s">
         <v>247</v>
@@ -18075,10 +18078,10 @@
         <v>51</v>
       </c>
       <c r="L288" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M288" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N288" t="s">
         <v>45</v>
@@ -18087,7 +18090,7 @@
         <v>140</v>
       </c>
       <c r="P288" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="Q288" t="s">
         <v>45</v>
@@ -18098,7 +18101,7 @@
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B289" t="s">
         <v>34</v>
@@ -18110,7 +18113,7 @@
         <v>34</v>
       </c>
       <c r="E289" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F289" t="s">
         <v>150</v>
@@ -18119,22 +18122,22 @@
         <v>41</v>
       </c>
       <c r="H289" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="I289" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J289" t="s">
         <v>247</v>
       </c>
       <c r="K289" t="s">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="L289" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M289" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N289" t="s">
         <v>45</v>
@@ -18143,7 +18146,7 @@
         <v>140</v>
       </c>
       <c r="P289" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="Q289" t="s">
         <v>45</v>
@@ -18154,13 +18157,13 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="1">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B290" t="s" s="1">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C290" t="s" s="1">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D290" t="s" s="1">
         <v>33</v>
@@ -18210,13 +18213,13 @@
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B291" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C291" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D291" t="s">
         <v>33</v>
@@ -18231,10 +18234,10 @@
         <v>41</v>
       </c>
       <c r="H291" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="I291" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="J291" t="s">
         <v>507</v>
@@ -18243,10 +18246,10 @@
         <v>44</v>
       </c>
       <c r="L291" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M291" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N291" t="s">
         <v>45</v>
@@ -18255,7 +18258,7 @@
         <v>140</v>
       </c>
       <c r="P291" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="Q291" t="s">
         <v>45</v>
@@ -18266,19 +18269,19 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B292" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C292" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D292" t="s">
         <v>33</v>
       </c>
       <c r="E292" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F292" t="s">
         <v>162</v>
@@ -18287,22 +18290,22 @@
         <v>41</v>
       </c>
       <c r="H292" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="I292" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="J292" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="K292" t="s">
         <v>72</v>
       </c>
       <c r="L292" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M292" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N292" t="s">
         <v>45</v>
@@ -18311,7 +18314,7 @@
         <v>140</v>
       </c>
       <c r="P292" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="Q292" t="s">
         <v>45</v>
@@ -18322,19 +18325,19 @@
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B293" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C293" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D293" t="s">
         <v>33</v>
       </c>
       <c r="E293" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F293" t="s">
         <v>162</v>
@@ -18343,22 +18346,22 @@
         <v>41</v>
       </c>
       <c r="H293" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I293" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J293" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="K293" t="s">
         <v>44</v>
       </c>
       <c r="L293" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M293" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N293" t="s">
         <v>45</v>
@@ -18367,7 +18370,7 @@
         <v>140</v>
       </c>
       <c r="P293" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="Q293" t="s">
         <v>45</v>
@@ -18378,13 +18381,13 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="1">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B294" t="s" s="1">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C294" t="s" s="1">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D294" t="s" s="1">
         <v>33</v>
@@ -18434,19 +18437,19 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
+        <v>682</v>
+      </c>
+      <c r="B295" t="s">
         <v>681</v>
       </c>
-      <c r="B295" t="s">
-        <v>680</v>
-      </c>
       <c r="C295" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D295" t="s">
         <v>33</v>
       </c>
       <c r="E295" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F295" t="s">
         <v>162</v>
@@ -18455,10 +18458,10 @@
         <v>41</v>
       </c>
       <c r="H295" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="I295" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="J295" t="s">
         <v>57</v>
@@ -18467,10 +18470,10 @@
         <v>153</v>
       </c>
       <c r="L295" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="M295" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N295" t="s">
         <v>45</v>
@@ -18479,7 +18482,7 @@
         <v>140</v>
       </c>
       <c r="P295" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="Q295" t="s">
         <v>45</v>
@@ -18490,7 +18493,7 @@
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B296" t="s">
         <v>34</v>
@@ -18502,7 +18505,7 @@
         <v>34</v>
       </c>
       <c r="E296" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F296" t="s">
         <v>162</v>
@@ -18511,22 +18514,22 @@
         <v>41</v>
       </c>
       <c r="H296" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I296" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J296" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K296" t="s">
         <v>44</v>
       </c>
       <c r="L296" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M296" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N296" t="s">
         <v>45</v>
@@ -18535,7 +18538,7 @@
         <v>140</v>
       </c>
       <c r="P296" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="Q296" t="s">
         <v>45</v>
@@ -18546,7 +18549,7 @@
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B297" t="s">
         <v>34</v>
@@ -18558,7 +18561,7 @@
         <v>34</v>
       </c>
       <c r="E297" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="F297" t="s">
         <v>162</v>
@@ -18567,22 +18570,22 @@
         <v>41</v>
       </c>
       <c r="H297" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I297" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="J297" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K297" t="s">
         <v>44</v>
       </c>
       <c r="L297" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M297" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N297" t="s">
         <v>45</v>
@@ -18591,7 +18594,7 @@
         <v>140</v>
       </c>
       <c r="P297" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="Q297" t="s">
         <v>45</v>
@@ -18602,7 +18605,7 @@
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B298" t="s">
         <v>34</v>
@@ -18614,7 +18617,7 @@
         <v>34</v>
       </c>
       <c r="E298" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F298" t="s">
         <v>162</v>
@@ -18623,22 +18626,22 @@
         <v>41</v>
       </c>
       <c r="H298" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I298" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="J298" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K298" t="s">
         <v>44</v>
       </c>
       <c r="L298" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M298" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N298" t="s">
         <v>45</v>
@@ -18647,7 +18650,7 @@
         <v>140</v>
       </c>
       <c r="P298" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="Q298" t="s">
         <v>45</v>
@@ -18658,7 +18661,7 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B299" t="s">
         <v>34</v>
@@ -18679,10 +18682,10 @@
         <v>41</v>
       </c>
       <c r="H299" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="I299" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J299" t="s">
         <v>240</v>
@@ -18691,10 +18694,10 @@
         <v>44</v>
       </c>
       <c r="L299" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M299" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N299" t="s">
         <v>45</v>
@@ -18703,7 +18706,7 @@
         <v>140</v>
       </c>
       <c r="P299" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="Q299" t="s">
         <v>45</v>
@@ -18714,7 +18717,7 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B300" t="s">
         <v>34</v>
@@ -18726,7 +18729,7 @@
         <v>34</v>
       </c>
       <c r="E300" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F300" t="s">
         <v>162</v>
@@ -18735,22 +18738,22 @@
         <v>41</v>
       </c>
       <c r="H300" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="I300" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="J300" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="K300" t="s">
         <v>44</v>
       </c>
       <c r="L300" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M300" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N300" t="s">
         <v>45</v>
@@ -18759,7 +18762,7 @@
         <v>140</v>
       </c>
       <c r="P300" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="Q300" t="s">
         <v>45</v>
@@ -18770,7 +18773,7 @@
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B301" t="s">
         <v>34</v>
@@ -18791,22 +18794,22 @@
         <v>41</v>
       </c>
       <c r="H301" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I301" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="J301" t="s">
         <v>240</v>
       </c>
       <c r="K301" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L301" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M301" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N301" t="s">
         <v>45</v>
@@ -18815,7 +18818,7 @@
         <v>140</v>
       </c>
       <c r="P301" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="Q301" t="s">
         <v>45</v>
@@ -18826,13 +18829,13 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="1">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B302" t="s" s="1">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C302" t="s" s="1">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D302" t="s" s="1">
         <v>33</v>
@@ -18882,19 +18885,19 @@
     </row>
     <row r="303">
       <c r="A303" t="s">
+        <v>708</v>
+      </c>
+      <c r="B303" t="s">
         <v>707</v>
       </c>
-      <c r="B303" t="s">
-        <v>706</v>
-      </c>
       <c r="C303" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D303" t="s">
         <v>33</v>
       </c>
       <c r="E303" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="F303" t="s">
         <v>162</v>
@@ -18906,19 +18909,19 @@
         <v>348</v>
       </c>
       <c r="I303" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="J303" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="K303" t="s">
         <v>44</v>
       </c>
       <c r="L303" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M303" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N303" t="s">
         <v>45</v>
@@ -18927,7 +18930,7 @@
         <v>140</v>
       </c>
       <c r="P303" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="Q303" t="s">
         <v>45</v>
@@ -18938,13 +18941,13 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="1">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B304" t="s" s="1">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C304" t="s" s="1">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D304" t="s" s="1">
         <v>33</v>
@@ -18994,19 +18997,19 @@
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B305" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C305" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D305" t="s">
         <v>33</v>
       </c>
       <c r="E305" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F305" t="s">
         <v>150</v>
@@ -19015,13 +19018,13 @@
         <v>41</v>
       </c>
       <c r="H305" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I305" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="J305" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="K305" t="s">
         <v>260</v>
@@ -19030,7 +19033,7 @@
         <v>34</v>
       </c>
       <c r="M305" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N305" t="s">
         <v>45</v>
@@ -19039,7 +19042,7 @@
         <v>140</v>
       </c>
       <c r="P305" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="Q305" t="s">
         <v>45</v>
@@ -19050,13 +19053,13 @@
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B306" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C306" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D306" t="s">
         <v>33</v>
@@ -19071,10 +19074,10 @@
         <v>41</v>
       </c>
       <c r="H306" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="I306" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="J306" t="s">
         <v>507</v>
@@ -19083,10 +19086,10 @@
         <v>44</v>
       </c>
       <c r="L306" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M306" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N306" t="s">
         <v>45</v>
@@ -19095,7 +19098,7 @@
         <v>140</v>
       </c>
       <c r="P306" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="Q306" t="s">
         <v>45</v>
@@ -19106,19 +19109,19 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B307" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C307" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D307" t="s">
         <v>33</v>
       </c>
       <c r="E307" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F307" t="s">
         <v>150</v>
@@ -19127,10 +19130,10 @@
         <v>41</v>
       </c>
       <c r="H307" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="I307" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="J307" t="s">
         <v>75</v>
@@ -19139,10 +19142,10 @@
         <v>57</v>
       </c>
       <c r="L307" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M307" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N307" t="s">
         <v>45</v>
@@ -19151,7 +19154,7 @@
         <v>140</v>
       </c>
       <c r="P307" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="Q307" t="s">
         <v>45</v>
@@ -19162,13 +19165,13 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="1">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B308" t="s" s="1">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C308" t="s" s="1">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D308" t="s" s="1">
         <v>33</v>
@@ -19218,13 +19221,13 @@
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B309" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C309" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D309" t="s">
         <v>33</v>
@@ -19239,10 +19242,10 @@
         <v>41</v>
       </c>
       <c r="H309" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="I309" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="J309" t="s">
         <v>165</v>
@@ -19251,10 +19254,10 @@
         <v>177</v>
       </c>
       <c r="L309" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M309" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N309" t="s">
         <v>45</v>
@@ -19263,7 +19266,7 @@
         <v>140</v>
       </c>
       <c r="P309" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="Q309" t="s">
         <v>45</v>
@@ -19274,19 +19277,19 @@
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B310" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C310" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D310" t="s">
         <v>33</v>
       </c>
       <c r="E310" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F310" t="s">
         <v>150</v>
@@ -19295,10 +19298,10 @@
         <v>41</v>
       </c>
       <c r="H310" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="I310" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="J310" t="s">
         <v>117</v>
@@ -19310,7 +19313,7 @@
         <v>34</v>
       </c>
       <c r="M310" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N310" t="s">
         <v>45</v>
@@ -19319,7 +19322,7 @@
         <v>140</v>
       </c>
       <c r="P310" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="Q310" t="s">
         <v>45</v>
@@ -19330,13 +19333,13 @@
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B311" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C311" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D311" t="s">
         <v>33</v>
@@ -19351,10 +19354,10 @@
         <v>41</v>
       </c>
       <c r="H311" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="I311" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="J311" t="s">
         <v>507</v>
@@ -19363,10 +19366,10 @@
         <v>44</v>
       </c>
       <c r="L311" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M311" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N311" t="s">
         <v>45</v>
@@ -19375,7 +19378,7 @@
         <v>140</v>
       </c>
       <c r="P311" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="Q311" t="s">
         <v>45</v>
@@ -19386,7 +19389,7 @@
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B312" t="s">
         <v>34</v>
@@ -19398,7 +19401,7 @@
         <v>34</v>
       </c>
       <c r="E312" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F312" t="s">
         <v>162</v>
@@ -19407,10 +19410,10 @@
         <v>41</v>
       </c>
       <c r="H312" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="I312" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="J312" t="s">
         <v>514</v>
@@ -19419,10 +19422,10 @@
         <v>91</v>
       </c>
       <c r="L312" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="M312" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N312" t="s">
         <v>45</v>
@@ -19431,7 +19434,7 @@
         <v>140</v>
       </c>
       <c r="P312" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="Q312" t="s">
         <v>45</v>
@@ -19442,13 +19445,13 @@
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B313" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C313" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D313" t="s">
         <v>33</v>
@@ -19463,22 +19466,22 @@
         <v>41</v>
       </c>
       <c r="H313" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="I313" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="J313" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K313" t="s">
         <v>44</v>
       </c>
       <c r="L313" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="M313" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N313" t="s">
         <v>45</v>
@@ -19487,7 +19490,7 @@
         <v>140</v>
       </c>
       <c r="P313" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="Q313" t="s">
         <v>45</v>
@@ -19498,13 +19501,13 @@
     </row>
     <row r="314">
       <c r="A314" t="s" s="1">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B314" t="s" s="1">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C314" t="s" s="1">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D314" t="s" s="1">
         <v>33</v>
@@ -19554,13 +19557,13 @@
     </row>
     <row r="315">
       <c r="A315" t="s" s="1">
+        <v>758</v>
+      </c>
+      <c r="B315" t="s" s="1">
         <v>757</v>
       </c>
-      <c r="B315" t="s" s="1">
-        <v>756</v>
-      </c>
       <c r="C315" t="s" s="1">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D315" t="s" s="1">
         <v>33</v>
@@ -19610,13 +19613,13 @@
     </row>
     <row r="316">
       <c r="A316" t="s" s="1">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B316" t="s" s="1">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C316" t="s" s="1">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D316" t="s" s="1">
         <v>33</v>
@@ -19666,19 +19669,19 @@
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B317" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C317" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D317" t="s">
         <v>33</v>
       </c>
       <c r="E317" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="F317" t="s">
         <v>150</v>
@@ -19687,10 +19690,10 @@
         <v>41</v>
       </c>
       <c r="H317" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="I317" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="J317" t="s">
         <v>247</v>
@@ -19702,7 +19705,7 @@
         <v>34</v>
       </c>
       <c r="M317" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N317" t="s">
         <v>45</v>
@@ -19711,7 +19714,7 @@
         <v>140</v>
       </c>
       <c r="P317" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="Q317" t="s">
         <v>45</v>
@@ -19722,13 +19725,13 @@
     </row>
     <row r="318">
       <c r="A318" t="s" s="1">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B318" t="s" s="1">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C318" t="s" s="1">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D318" t="s" s="1">
         <v>33</v>
@@ -19778,13 +19781,13 @@
     </row>
     <row r="319">
       <c r="A319" t="s" s="1">
+        <v>766</v>
+      </c>
+      <c r="B319" t="s" s="1">
         <v>765</v>
       </c>
-      <c r="B319" t="s" s="1">
-        <v>764</v>
-      </c>
       <c r="C319" t="s" s="1">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D319" t="s" s="1">
         <v>33</v>
@@ -19834,13 +19837,13 @@
     </row>
     <row r="320">
       <c r="A320" t="s" s="1">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B320" t="s" s="1">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C320" t="s" s="1">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D320" t="s" s="1">
         <v>33</v>
@@ -19890,13 +19893,13 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B321" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C321" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D321" t="s">
         <v>33</v>
@@ -19911,10 +19914,10 @@
         <v>41</v>
       </c>
       <c r="H321" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I321" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="J321" t="s">
         <v>52</v>
@@ -19923,10 +19926,10 @@
         <v>52</v>
       </c>
       <c r="L321" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M321" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N321" t="s">
         <v>45</v>
@@ -19946,7 +19949,7 @@
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B322" t="s">
         <v>34</v>
@@ -19967,10 +19970,10 @@
         <v>41</v>
       </c>
       <c r="H322" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="I322" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="J322" t="s">
         <v>57</v>
@@ -19979,10 +19982,10 @@
         <v>57</v>
       </c>
       <c r="L322" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M322" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N322" t="s">
         <v>45</v>
@@ -20002,7 +20005,7 @@
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B323" t="s">
         <v>34</v>
@@ -20023,10 +20026,10 @@
         <v>41</v>
       </c>
       <c r="H323" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I323" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="J323" t="s">
         <v>80</v>
@@ -20035,10 +20038,10 @@
         <v>80</v>
       </c>
       <c r="L323" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M323" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N323" t="s">
         <v>45</v>
@@ -20058,7 +20061,7 @@
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B324" t="s">
         <v>34</v>
@@ -20079,10 +20082,10 @@
         <v>41</v>
       </c>
       <c r="H324" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I324" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="J324" t="s">
         <v>65</v>
@@ -20091,10 +20094,10 @@
         <v>65</v>
       </c>
       <c r="L324" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M324" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N324" t="s">
         <v>45</v>
@@ -20114,7 +20117,7 @@
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B325" t="s">
         <v>34</v>
@@ -20135,10 +20138,10 @@
         <v>41</v>
       </c>
       <c r="H325" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I325" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="J325" t="s">
         <v>110</v>
@@ -20147,10 +20150,10 @@
         <v>110</v>
       </c>
       <c r="L325" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M325" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N325" t="s">
         <v>45</v>
@@ -20170,7 +20173,7 @@
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B326" t="s">
         <v>34</v>
@@ -20191,10 +20194,10 @@
         <v>41</v>
       </c>
       <c r="H326" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I326" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="J326" t="s">
         <v>117</v>
@@ -20203,10 +20206,10 @@
         <v>117</v>
       </c>
       <c r="L326" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M326" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N326" t="s">
         <v>45</v>
@@ -20226,7 +20229,7 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B327" t="s">
         <v>34</v>
@@ -20247,10 +20250,10 @@
         <v>41</v>
       </c>
       <c r="H327" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I327" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="J327" t="s">
         <v>91</v>
@@ -20259,10 +20262,10 @@
         <v>91</v>
       </c>
       <c r="L327" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M327" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N327" t="s">
         <v>45</v>
@@ -20271,7 +20274,7 @@
         <v>92</v>
       </c>
       <c r="P327" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="Q327" t="s">
         <v>45</v>
@@ -20282,7 +20285,7 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B328" t="s">
         <v>34</v>
@@ -20303,10 +20306,10 @@
         <v>41</v>
       </c>
       <c r="H328" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I328" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J328" t="s">
         <v>104</v>
@@ -20315,10 +20318,10 @@
         <v>104</v>
       </c>
       <c r="L328" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M328" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N328" t="s">
         <v>45</v>
@@ -20338,7 +20341,7 @@
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B329" t="s">
         <v>34</v>
@@ -20359,10 +20362,10 @@
         <v>41</v>
       </c>
       <c r="H329" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I329" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="J329" t="s">
         <v>98</v>
@@ -20371,10 +20374,10 @@
         <v>98</v>
       </c>
       <c r="L329" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M329" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N329" t="s">
         <v>45</v>
@@ -20394,7 +20397,7 @@
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B330" t="s">
         <v>34</v>
@@ -20415,10 +20418,10 @@
         <v>41</v>
       </c>
       <c r="H330" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I330" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="J330" t="s">
         <v>57</v>
@@ -20427,10 +20430,10 @@
         <v>57</v>
       </c>
       <c r="L330" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M330" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N330" t="s">
         <v>45</v>
@@ -20450,7 +20453,7 @@
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B331" t="s">
         <v>34</v>
@@ -20471,10 +20474,10 @@
         <v>41</v>
       </c>
       <c r="H331" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I331" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="J331" t="s">
         <v>104</v>
@@ -20483,10 +20486,10 @@
         <v>104</v>
       </c>
       <c r="L331" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M331" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N331" t="s">
         <v>45</v>
@@ -20506,7 +20509,7 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B332" t="s">
         <v>34</v>
@@ -20527,10 +20530,10 @@
         <v>41</v>
       </c>
       <c r="H332" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I332" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="J332" t="s">
         <v>72</v>
@@ -20539,10 +20542,10 @@
         <v>72</v>
       </c>
       <c r="L332" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M332" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N332" t="s">
         <v>45</v>
@@ -20562,7 +20565,7 @@
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B333" t="s">
         <v>34</v>
@@ -20574,7 +20577,7 @@
         <v>34</v>
       </c>
       <c r="E333" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F333" t="s">
         <v>202</v>
@@ -20583,22 +20586,22 @@
         <v>41</v>
       </c>
       <c r="H333" t="s">
+        <v>769</v>
+      </c>
+      <c r="I333" t="s">
+        <v>784</v>
+      </c>
+      <c r="J333" t="s">
+        <v>408</v>
+      </c>
+      <c r="K333" t="s">
+        <v>408</v>
+      </c>
+      <c r="L333" t="s">
+        <v>771</v>
+      </c>
+      <c r="M333" t="s">
         <v>768</v>
-      </c>
-      <c r="I333" t="s">
-        <v>783</v>
-      </c>
-      <c r="J333" t="s">
-        <v>409</v>
-      </c>
-      <c r="K333" t="s">
-        <v>409</v>
-      </c>
-      <c r="L333" t="s">
-        <v>770</v>
-      </c>
-      <c r="M333" t="s">
-        <v>767</v>
       </c>
       <c r="N333" t="s">
         <v>45</v>
@@ -20618,7 +20621,7 @@
     </row>
     <row r="334">
       <c r="A334" t="s" s="1">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B334" t="s" s="1">
         <v>32</v>
@@ -20674,7 +20677,7 @@
     </row>
     <row r="335">
       <c r="A335" t="s" s="1">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B335" t="s" s="1">
         <v>32</v>
@@ -20730,7 +20733,7 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B336" t="s">
         <v>32</v>
@@ -20786,7 +20789,7 @@
     </row>
     <row r="337">
       <c r="A337" t="s" s="1">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B337" t="s" s="1">
         <v>157</v>
@@ -20842,7 +20845,7 @@
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B338" t="s">
         <v>157</v>
@@ -20898,13 +20901,13 @@
     </row>
     <row r="339">
       <c r="A339" t="s" s="1">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B339" t="s" s="1">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C339" t="s" s="1">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D339" t="s" s="1">
         <v>33</v>
@@ -20954,7 +20957,7 @@
     </row>
     <row r="340">
       <c r="A340" t="s" s="1">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B340" t="s" s="1">
         <v>180</v>
@@ -21010,7 +21013,7 @@
     </row>
     <row r="341">
       <c r="A341" t="s" s="1">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B341" t="s" s="1">
         <v>182</v>
@@ -21066,7 +21069,7 @@
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B342" t="s">
         <v>182</v>
@@ -21122,7 +21125,7 @@
     </row>
     <row r="343">
       <c r="A343" t="s" s="1">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B343" t="s" s="1">
         <v>269</v>
@@ -21178,7 +21181,7 @@
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B344" t="s">
         <v>269</v>
@@ -21234,13 +21237,13 @@
     </row>
     <row r="345">
       <c r="A345" t="s" s="1">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B345" t="s" s="1">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C345" t="s" s="1">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D345" t="s" s="1">
         <v>33</v>
@@ -21290,13 +21293,13 @@
     </row>
     <row r="346">
       <c r="A346" t="s" s="1">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B346" t="s" s="1">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C346" t="s" s="1">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D346" t="s" s="1">
         <v>33</v>
@@ -21346,7 +21349,7 @@
     </row>
     <row r="347">
       <c r="A347" t="s" s="1">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B347" t="s" s="1">
         <v>324</v>
@@ -21402,7 +21405,7 @@
     </row>
     <row r="348">
       <c r="A348" t="s" s="1">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B348" t="s" s="1">
         <v>326</v>
@@ -21458,7 +21461,7 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B349" t="s">
         <v>326</v>
@@ -21514,7 +21517,7 @@
     </row>
     <row r="350">
       <c r="A350" t="s" s="1">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B350" t="s" s="1">
         <v>440</v>
@@ -21570,7 +21573,7 @@
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B351" t="s">
         <v>440</v>
@@ -21626,7 +21629,7 @@
     </row>
     <row r="352">
       <c r="A352" t="s" s="1">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B352" t="s" s="1">
         <v>446</v>
@@ -21682,7 +21685,7 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B353" t="s">
         <v>448</v>
@@ -21738,7 +21741,7 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B354" t="s">
         <v>495</v>
@@ -21794,7 +21797,7 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B355" t="s">
         <v>502</v>
@@ -21850,7 +21853,7 @@
     </row>
     <row r="356">
       <c r="A356" t="s" s="1">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B356" t="s" s="1">
         <v>521</v>
@@ -21906,7 +21909,7 @@
     </row>
     <row r="357">
       <c r="A357" t="s" s="1">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B357" t="s" s="1">
         <v>523</v>
@@ -21962,7 +21965,7 @@
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B358" t="s">
         <v>525</v>
@@ -22018,7 +22021,7 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B359" t="s">
         <v>530</v>
@@ -22074,13 +22077,13 @@
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B360" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C360" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D360" t="s">
         <v>33</v>
@@ -22130,13 +22133,13 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B361" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C361" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D361" t="s">
         <v>33</v>
@@ -22186,13 +22189,13 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B362" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C362" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D362" t="s">
         <v>33</v>
@@ -22242,13 +22245,13 @@
     </row>
     <row r="363">
       <c r="A363" t="s" s="1">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B363" t="s" s="1">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C363" t="s" s="1">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D363" t="s" s="1">
         <v>33</v>
@@ -22298,13 +22301,13 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B364" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C364" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D364" t="s">
         <v>33</v>
@@ -22354,13 +22357,13 @@
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B365" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C365" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D365" t="s">
         <v>33</v>
@@ -22410,13 +22413,13 @@
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B366" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C366" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D366" t="s">
         <v>33</v>
@@ -22466,13 +22469,13 @@
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B367" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C367" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D367" t="s">
         <v>33</v>
@@ -22522,13 +22525,13 @@
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B368" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C368" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D368" t="s">
         <v>33</v>
@@ -22578,13 +22581,13 @@
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B369" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C369" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D369" t="s">
         <v>33</v>
@@ -22634,13 +22637,13 @@
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B370" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C370" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D370" t="s">
         <v>33</v>
@@ -22690,13 +22693,13 @@
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B371" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C371" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D371" t="s">
         <v>33</v>
@@ -22746,13 +22749,13 @@
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B372" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C372" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D372" t="s">
         <v>33</v>
@@ -22802,13 +22805,13 @@
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B373" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C373" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D373" t="s">
         <v>33</v>
@@ -22858,13 +22861,13 @@
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B374" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C374" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D374" t="s">
         <v>33</v>
@@ -22914,13 +22917,13 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="1">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B375" t="s" s="1">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C375" t="s" s="1">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D375" t="s" s="1">
         <v>33</v>
@@ -22970,13 +22973,13 @@
     </row>
     <row r="376">
       <c r="A376" t="s" s="1">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B376" t="s" s="1">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C376" t="s" s="1">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D376" t="s" s="1">
         <v>33</v>
@@ -23026,13 +23029,13 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="1">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B377" t="s" s="1">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C377" t="s" s="1">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D377" t="s" s="1">
         <v>33</v>
@@ -23082,13 +23085,13 @@
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B378" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C378" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D378" t="s">
         <v>33</v>
@@ -23138,13 +23141,13 @@
     </row>
     <row r="379">
       <c r="A379" t="s" s="1">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B379" t="s" s="1">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C379" t="s" s="1">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D379" t="s" s="1">
         <v>33</v>
@@ -23194,13 +23197,13 @@
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B380" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C380" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D380" t="s">
         <v>33</v>
@@ -23250,13 +23253,13 @@
     </row>
     <row r="381">
       <c r="A381" t="s" s="1">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B381" t="s" s="1">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C381" t="s" s="1">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D381" t="s" s="1">
         <v>33</v>
@@ -23306,13 +23309,13 @@
     </row>
     <row r="382">
       <c r="A382" t="s" s="1">
+        <v>839</v>
+      </c>
+      <c r="B382" t="s" s="1">
         <v>838</v>
       </c>
-      <c r="B382" t="s" s="1">
-        <v>837</v>
-      </c>
       <c r="C382" t="s" s="1">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D382" t="s" s="1">
         <v>33</v>
@@ -23362,13 +23365,13 @@
     </row>
     <row r="383">
       <c r="A383" t="s" s="1">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B383" t="s" s="1">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C383" t="s" s="1">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D383" t="s" s="1">
         <v>33</v>
@@ -23418,7 +23421,7 @@
     </row>
     <row r="384">
       <c r="A384" t="s" s="1">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B384" t="s" s="1">
         <v>32</v>
@@ -23474,13 +23477,13 @@
     </row>
     <row r="385">
       <c r="A385" t="s" s="1">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B385" t="s" s="1">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C385" t="s" s="1">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D385" t="s" s="1">
         <v>33</v>
@@ -23530,7 +23533,7 @@
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B386" t="s">
         <v>157</v>
@@ -23586,7 +23589,7 @@
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B387" t="s">
         <v>180</v>
@@ -23642,7 +23645,7 @@
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B388" t="s">
         <v>324</v>
@@ -23698,13 +23701,13 @@
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B389" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C389" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D389" t="s">
         <v>33</v>
@@ -23754,13 +23757,13 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="1">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B390" t="s" s="1">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C390" t="s" s="1">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D390" t="s" s="1">
         <v>33</v>
@@ -23810,7 +23813,7 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B391" t="s">
         <v>521</v>
@@ -23866,13 +23869,13 @@
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B392" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C392" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D392" t="s">
         <v>33</v>
@@ -23922,7 +23925,7 @@
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B393" t="s">
         <v>32</v>
@@ -23978,13 +23981,13 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B394" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C394" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D394" t="s">
         <v>33</v>
@@ -24034,13 +24037,13 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B395" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C395" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D395" t="s">
         <v>33</v>
@@ -24090,7 +24093,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B396" t="s">
         <v>182</v>
@@ -24146,7 +24149,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B397" t="s">
         <v>326</v>
@@ -24202,7 +24205,7 @@
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B398" t="s">
         <v>523</v>
@@ -24258,13 +24261,13 @@
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B399" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C399" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D399" t="s">
         <v>33</v>
@@ -24314,7 +24317,7 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B400" t="s">
         <v>157</v>
@@ -24370,13 +24373,13 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B401" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C401" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D401" t="s">
         <v>33</v>
@@ -24426,13 +24429,13 @@
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B402" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C402" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D402" t="s">
         <v>33</v>
@@ -24482,13 +24485,13 @@
     </row>
     <row r="403">
       <c r="A403" t="s" s="1">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B403" t="s" s="1">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C403" t="s" s="1">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D403" t="s" s="1">
         <v>33</v>
@@ -24538,16 +24541,16 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="1">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B404" t="s" s="1">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C404" t="s" s="1">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D404" t="s" s="1">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E404" t="s" s="1">
         <v>34</v>
@@ -24594,16 +24597,16 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="1">
+        <v>869</v>
+      </c>
+      <c r="B405" t="s" s="1">
+        <v>870</v>
+      </c>
+      <c r="C405" t="s" s="1">
+        <v>870</v>
+      </c>
+      <c r="D405" t="s" s="1">
         <v>868</v>
-      </c>
-      <c r="B405" t="s" s="1">
-        <v>869</v>
-      </c>
-      <c r="C405" t="s" s="1">
-        <v>869</v>
-      </c>
-      <c r="D405" t="s" s="1">
-        <v>867</v>
       </c>
       <c r="E405" t="s" s="1">
         <v>34</v>
@@ -24650,16 +24653,16 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="1">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B406" t="s" s="1">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C406" t="s" s="1">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D406" t="s" s="1">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E406" t="s" s="1">
         <v>34</v>

--- a/xlsx/dre/DRE_06_2026.xlsx
+++ b/xlsx/dre/DRE_06_2026.xlsx
@@ -480,7 +480,7 @@
     <t>4 CUSTOS E DESPESAS</t>
   </si>
   <si>
-    <t>R$ 644.023,76</t>
+    <t>R$ 645.556,14</t>
   </si>
   <si>
     <t>4.01 DEDUÇÕES DE RECEITA</t>
@@ -555,7 +555,7 @@
     <t>4.02 CUSTOS</t>
   </si>
   <si>
-    <t>R$ 319.904,88</t>
+    <t>R$ 321.437,26</t>
   </si>
   <si>
     <t>4.02.01 CUSTO DAS MERCADORIAS VENDIDAS e SERVIÇOS</t>
@@ -833,7 +833,7 @@
     <t>4.02.02 CUSTO DE TRANSPORTE</t>
   </si>
   <si>
-    <t>R$ 45.126,60</t>
+    <t>R$ 46.658,98</t>
   </si>
   <si>
     <t>4.02.02.01 Fretes sobre compras</t>
@@ -863,13 +863,13 @@
     <t>83201/2</t>
   </si>
   <si>
-    <t>R$  7.708,12</t>
+    <t>R$  8.466,66</t>
   </si>
   <si>
     <t>83201/3</t>
   </si>
   <si>
-    <t>R$  7.854,09</t>
+    <t>R$  8.627,93</t>
   </si>
   <si>
     <t>85601/0</t>
@@ -2424,7 +2424,7 @@
     <t>7.05 = RESULTADO BRUTO</t>
   </si>
   <si>
-    <t>R$ 395.519,45</t>
+    <t>R$ 393.987,07</t>
   </si>
   <si>
     <t>7.06 (-) DESPESAS REGULARES</t>
@@ -2520,7 +2520,7 @@
     <t>7.07 = RESULTADO ANTES DAS DESPESAS E RECEITAS FINANCEIRAS</t>
   </si>
   <si>
-    <t>R$ 140.770,45</t>
+    <t>R$ 139.238,07</t>
   </si>
   <si>
     <t>7.08 (-) DESPESAS E RECEITAS FINANCEIRAS</t>
@@ -2544,7 +2544,7 @@
     <t>7.09 = RESULTADO OPERACIONAL</t>
   </si>
   <si>
-    <t>R$ 96.295,78</t>
+    <t>R$ 94.763,40</t>
   </si>
   <si>
     <t>7.11 = RESULTADO LÍQUIDO DO EXERCÍCIO</t>
@@ -2559,7 +2559,7 @@
     <t>7.50.02 TOTAL DOS CUSTOS VARIÁVEIS</t>
   </si>
   <si>
-    <t>R$ 561.020,71</t>
+    <t>R$ 562.553,09</t>
   </si>
   <si>
     <t>7.50.02.01 Deduções de receita</t>
@@ -2625,7 +2625,7 @@
     <t>7.70 BREAK-EVEN POINT</t>
   </si>
   <si>
-    <t>R$ 342.717,13</t>
+    <t>R$ 345.671,41</t>
   </si>
   <si>
     <t>7.80.01 Mark Up Negociado</t>

--- a/xlsx/dre/DRE_06_2026.xlsx
+++ b/xlsx/dre/DRE_06_2026.xlsx
@@ -447,6 +447,21 @@
     <t>R$  178,31</t>
   </si>
   <si>
+    <t>685/1</t>
+  </si>
+  <si>
+    <t>DMP</t>
+  </si>
+  <si>
+    <t>Leo Madeiras</t>
+  </si>
+  <si>
+    <t>R$  37,80</t>
+  </si>
+  <si>
+    <t>22/06/26</t>
+  </si>
+  <si>
     <t>1/5</t>
   </si>
   <si>
@@ -460,21 +475,6 @@
   </si>
   <si>
     <t>Digisac MP 2026</t>
-  </si>
-  <si>
-    <t>685/1</t>
-  </si>
-  <si>
-    <t>DMP</t>
-  </si>
-  <si>
-    <t>Leo Madeiras</t>
-  </si>
-  <si>
-    <t>R$  37,80</t>
-  </si>
-  <si>
-    <t>22/06/26</t>
   </si>
   <si>
     <t>4 CUSTOS E DESPESAS</t>
@@ -1343,12 +1343,12 @@
     <t>DSR jun26/1</t>
   </si>
   <si>
+    <t>R$  1.207,83</t>
+  </si>
+  <si>
     <t>R$  2.151,72</t>
   </si>
   <si>
-    <t>R$  1.207,83</t>
-  </si>
-  <si>
     <t>4.03.02 COMISSÕES E BÔNUS DE TERCEIROS</t>
   </si>
   <si>
@@ -1385,15 +1385,126 @@
     <t>Uber</t>
   </si>
   <si>
+    <t>R$  79,10</t>
+  </si>
+  <si>
+    <t>46201UBER/0</t>
+  </si>
+  <si>
+    <t>R$  26,52</t>
+  </si>
+  <si>
+    <t>46201ANGELASC</t>
+  </si>
+  <si>
+    <t>37801/0</t>
+  </si>
+  <si>
+    <t>R$  13,74</t>
+  </si>
+  <si>
+    <t>37801fabiotp</t>
+  </si>
+  <si>
+    <t>R$  33,27</t>
+  </si>
+  <si>
     <t>R$  11,21</t>
   </si>
   <si>
+    <t>13301U/0</t>
+  </si>
+  <si>
+    <t>R$  60,17</t>
+  </si>
+  <si>
+    <t>30/06/25</t>
+  </si>
+  <si>
+    <t>FlaviaCM0013301</t>
+  </si>
+  <si>
+    <t>51301UBER/0</t>
+  </si>
+  <si>
+    <t>R$  30,35</t>
+  </si>
+  <si>
+    <t>51301ElisangelaTSO</t>
+  </si>
+  <si>
     <t>Lalamove</t>
   </si>
   <si>
     <t>R$  100,00</t>
   </si>
   <si>
+    <t>52001/0</t>
+  </si>
+  <si>
+    <t>R$  43,42</t>
+  </si>
+  <si>
+    <t>52001LucianaXM</t>
+  </si>
+  <si>
+    <t>81902UB/0</t>
+  </si>
+  <si>
+    <t>R$  13,37</t>
+  </si>
+  <si>
+    <t>29901UBER/0</t>
+  </si>
+  <si>
+    <t>R$  14,48</t>
+  </si>
+  <si>
+    <t>29901FL8</t>
+  </si>
+  <si>
+    <t>30901/0</t>
+  </si>
+  <si>
+    <t>R$  25,15</t>
+  </si>
+  <si>
+    <t>30901RobertoP</t>
+  </si>
+  <si>
+    <t>40901/0</t>
+  </si>
+  <si>
+    <t>R$  11,73</t>
+  </si>
+  <si>
+    <t>40901DOUGLASJOS</t>
+  </si>
+  <si>
+    <t>ADM-UBER/0</t>
+  </si>
+  <si>
+    <t>R$  269,33</t>
+  </si>
+  <si>
+    <t>47101UBER/0</t>
+  </si>
+  <si>
+    <t>R$  12,69</t>
+  </si>
+  <si>
+    <t>47101MarciaOA</t>
+  </si>
+  <si>
+    <t>23801/0</t>
+  </si>
+  <si>
+    <t>R$  1,74</t>
+  </si>
+  <si>
+    <t>DiegoSB0023801</t>
+  </si>
+  <si>
     <t>42001/0</t>
   </si>
   <si>
@@ -1403,117 +1514,6 @@
     <t>42001LaysSB</t>
   </si>
   <si>
-    <t>R$  79,10</t>
-  </si>
-  <si>
-    <t>51301UBER/0</t>
-  </si>
-  <si>
-    <t>R$  30,35</t>
-  </si>
-  <si>
-    <t>51301ElisangelaTSO</t>
-  </si>
-  <si>
-    <t>46201UBER/0</t>
-  </si>
-  <si>
-    <t>R$  26,52</t>
-  </si>
-  <si>
-    <t>46201ANGELASC</t>
-  </si>
-  <si>
-    <t>R$  33,27</t>
-  </si>
-  <si>
-    <t>37801/0</t>
-  </si>
-  <si>
-    <t>R$  13,74</t>
-  </si>
-  <si>
-    <t>37801fabiotp</t>
-  </si>
-  <si>
-    <t>30901/0</t>
-  </si>
-  <si>
-    <t>R$  25,15</t>
-  </si>
-  <si>
-    <t>30901RobertoP</t>
-  </si>
-  <si>
-    <t>47101UBER/0</t>
-  </si>
-  <si>
-    <t>R$  12,69</t>
-  </si>
-  <si>
-    <t>47101MarciaOA</t>
-  </si>
-  <si>
-    <t>52001/0</t>
-  </si>
-  <si>
-    <t>R$  43,42</t>
-  </si>
-  <si>
-    <t>52001LucianaXM</t>
-  </si>
-  <si>
-    <t>23801/0</t>
-  </si>
-  <si>
-    <t>R$  1,74</t>
-  </si>
-  <si>
-    <t>DiegoSB0023801</t>
-  </si>
-  <si>
-    <t>29901UBER/0</t>
-  </si>
-  <si>
-    <t>R$  14,48</t>
-  </si>
-  <si>
-    <t>29901FL8</t>
-  </si>
-  <si>
-    <t>40901/0</t>
-  </si>
-  <si>
-    <t>R$  11,73</t>
-  </si>
-  <si>
-    <t>40901DOUGLASJOS</t>
-  </si>
-  <si>
-    <t>ADM-UBER/0</t>
-  </si>
-  <si>
-    <t>R$  269,33</t>
-  </si>
-  <si>
-    <t>13301U/0</t>
-  </si>
-  <si>
-    <t>R$  60,17</t>
-  </si>
-  <si>
-    <t>30/06/25</t>
-  </si>
-  <si>
-    <t>FlaviaCM0013301</t>
-  </si>
-  <si>
-    <t>81902UB/0</t>
-  </si>
-  <si>
-    <t>R$  13,37</t>
-  </si>
-  <si>
     <t>4.03.03.02 Agregados e outros gastos de montagens</t>
   </si>
   <si>
@@ -1547,6 +1547,27 @@
     <t>12/6</t>
   </si>
   <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>R$  14,99</t>
+  </si>
+  <si>
+    <t>Google 2026</t>
+  </si>
+  <si>
+    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
+  </si>
+  <si>
+    <t>R$  4.588,50</t>
+  </si>
+  <si>
+    <t>18/02/26</t>
+  </si>
+  <si>
+    <t>Webgiga 2026</t>
+  </si>
+  <si>
     <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
   </si>
   <si>
@@ -1559,27 +1580,6 @@
     <t>MHM - Honorários 2026</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>R$  14,99</t>
-  </si>
-  <si>
-    <t>Google 2026</t>
-  </si>
-  <si>
-    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
-  </si>
-  <si>
-    <t>R$  4.588,50</t>
-  </si>
-  <si>
-    <t>18/02/26</t>
-  </si>
-  <si>
-    <t>Webgiga 2026</t>
-  </si>
-  <si>
     <t>1/4</t>
   </si>
   <si>
@@ -1943,48 +1943,48 @@
     <t>4.04.02.05.02 Serviços de limpeza</t>
   </si>
   <si>
+    <t>675/1</t>
+  </si>
+  <si>
+    <t>Claudineuza Santos Machado</t>
+  </si>
+  <si>
+    <t>R$  230,00</t>
+  </si>
+  <si>
+    <t>683/1</t>
+  </si>
+  <si>
+    <t>Sabrina Barbosa de Medeiros</t>
+  </si>
+  <si>
     <t>664/1</t>
   </si>
   <si>
-    <t>Claudineuza Santos Machado</t>
-  </si>
-  <si>
-    <t>R$  230,00</t>
-  </si>
-  <si>
     <t>08/06/26</t>
   </si>
   <si>
+    <t>Thais Pereira Pires</t>
+  </si>
+  <si>
+    <t>R$  1.600,00</t>
+  </si>
+  <si>
+    <t>Thais Limpeza - 2026</t>
+  </si>
+  <si>
+    <t>663/1</t>
+  </si>
+  <si>
+    <t>R$  220,00</t>
+  </si>
+  <si>
     <t>673/1</t>
   </si>
   <si>
     <t>11/06/26</t>
   </si>
   <si>
-    <t>Thais Pereira Pires</t>
-  </si>
-  <si>
-    <t>R$  1.600,00</t>
-  </si>
-  <si>
-    <t>Thais Limpeza - 2026</t>
-  </si>
-  <si>
-    <t>683/1</t>
-  </si>
-  <si>
-    <t>Sabrina Barbosa de Medeiros</t>
-  </si>
-  <si>
-    <t>675/1</t>
-  </si>
-  <si>
-    <t>663/1</t>
-  </si>
-  <si>
-    <t>R$  220,00</t>
-  </si>
-  <si>
     <t>4.04.02.06 Material de escritório</t>
   </si>
   <si>
@@ -1992,6 +1992,18 @@
   </si>
   <si>
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
+  </si>
+  <si>
+    <t>699/1</t>
+  </si>
+  <si>
+    <t>Pão de Açúcar</t>
+  </si>
+  <si>
+    <t>R$  95,17</t>
+  </si>
+  <si>
+    <t>material limpeza</t>
   </si>
   <si>
     <t>700/1</t>
@@ -2010,18 +2022,6 @@
 </t>
   </si>
   <si>
-    <t>699/1</t>
-  </si>
-  <si>
-    <t>Pão de Açúcar</t>
-  </si>
-  <si>
-    <t>R$  95,17</t>
-  </si>
-  <si>
-    <t>material limpeza</t>
-  </si>
-  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2085,6 +2085,15 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4 sign 2026</t>
+  </si>
+  <si>
     <t>64/1</t>
   </si>
   <si>
@@ -2127,13 +2136,10 @@
     <t>Promob 2026/2</t>
   </si>
   <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4 sign 2026</t>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
   </si>
   <si>
     <t>61/2</t>
@@ -2146,12 +2152,6 @@
   </si>
   <si>
     <t>21/05/26</t>
-  </si>
-  <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -4514,25 +4514,25 @@
         <v>144</v>
       </c>
       <c r="F46" t="s">
-        <v>48</v>
+        <v>145</v>
       </c>
       <c r="G46" t="s">
         <v>41</v>
       </c>
       <c r="H46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I46" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J46" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K46" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="L46" t="s">
-        <v>148</v>
+        <v>34</v>
       </c>
       <c r="M46" t="s">
         <v>133</v>
@@ -4544,7 +4544,7 @@
         <v>140</v>
       </c>
       <c r="P46" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q46" t="s">
         <v>45</v>
@@ -4570,25 +4570,25 @@
         <v>149</v>
       </c>
       <c r="F47" t="s">
+        <v>48</v>
+      </c>
+      <c r="G47" t="s">
+        <v>41</v>
+      </c>
+      <c r="H47" t="s">
         <v>150</v>
       </c>
-      <c r="G47" t="s">
-        <v>41</v>
-      </c>
-      <c r="H47" t="s">
+      <c r="I47" t="s">
         <v>151</v>
       </c>
-      <c r="I47" t="s">
+      <c r="J47" t="s">
         <v>152</v>
       </c>
-      <c r="J47" t="s">
+      <c r="K47" t="s">
+        <v>91</v>
+      </c>
+      <c r="L47" t="s">
         <v>153</v>
-      </c>
-      <c r="K47" t="s">
-        <v>57</v>
-      </c>
-      <c r="L47" t="s">
-        <v>34</v>
       </c>
       <c r="M47" t="s">
         <v>133</v>
@@ -4600,7 +4600,7 @@
         <v>140</v>
       </c>
       <c r="P47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q47" t="s">
         <v>45</v>
@@ -4847,7 +4847,7 @@
         <v>33</v>
       </c>
       <c r="E52" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F52" t="s">
         <v>162</v>
@@ -5186,7 +5186,7 @@
         <v>190</v>
       </c>
       <c r="F58" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G58" t="s">
         <v>41</v>
@@ -5522,13 +5522,13 @@
         <v>205</v>
       </c>
       <c r="F64" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G64" t="s">
         <v>41</v>
       </c>
       <c r="H64" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I64" t="s">
         <v>206</v>
@@ -5578,7 +5578,7 @@
         <v>62</v>
       </c>
       <c r="F65" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G65" t="s">
         <v>41</v>
@@ -5634,13 +5634,13 @@
         <v>210</v>
       </c>
       <c r="F66" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G66" t="s">
         <v>41</v>
       </c>
       <c r="H66" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I66" t="s">
         <v>206</v>
@@ -6138,13 +6138,13 @@
         <v>235</v>
       </c>
       <c r="F75" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G75" t="s">
         <v>41</v>
       </c>
       <c r="H75" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I75" t="s">
         <v>236</v>
@@ -6200,7 +6200,7 @@
         <v>41</v>
       </c>
       <c r="H76" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I76" t="s">
         <v>239</v>
@@ -6250,7 +6250,7 @@
         <v>241</v>
       </c>
       <c r="F77" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G77" t="s">
         <v>41</v>
@@ -6306,7 +6306,7 @@
         <v>245</v>
       </c>
       <c r="F78" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G78" t="s">
         <v>41</v>
@@ -6362,7 +6362,7 @@
         <v>249</v>
       </c>
       <c r="F79" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G79" t="s">
         <v>41</v>
@@ -6418,7 +6418,7 @@
         <v>252</v>
       </c>
       <c r="F80" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G80" t="s">
         <v>41</v>
@@ -6530,7 +6530,7 @@
         <v>259</v>
       </c>
       <c r="F82" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G82" t="s">
         <v>41</v>
@@ -6586,13 +6586,13 @@
         <v>264</v>
       </c>
       <c r="F83" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G83" t="s">
         <v>41</v>
       </c>
       <c r="H83" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I83" t="s">
         <v>265</v>
@@ -6642,7 +6642,7 @@
         <v>266</v>
       </c>
       <c r="F84" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G84" t="s">
         <v>41</v>
@@ -7930,7 +7930,7 @@
         <v>318</v>
       </c>
       <c r="F107" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G107" t="s">
         <v>41</v>
@@ -7986,7 +7986,7 @@
         <v>39</v>
       </c>
       <c r="F108" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G108" t="s">
         <v>41</v>
@@ -8042,13 +8042,13 @@
         <v>322</v>
       </c>
       <c r="F109" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G109" t="s">
         <v>41</v>
       </c>
       <c r="H109" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I109" t="s">
         <v>206</v>
@@ -8098,7 +8098,7 @@
         <v>95</v>
       </c>
       <c r="F110" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G110" t="s">
         <v>41</v>
@@ -8154,7 +8154,7 @@
         <v>62</v>
       </c>
       <c r="F111" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G111" t="s">
         <v>41</v>
@@ -12074,7 +12074,7 @@
         <v>218</v>
       </c>
       <c r="F181" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G181" t="s">
         <v>41</v>
@@ -12578,7 +12578,7 @@
         <v>54</v>
       </c>
       <c r="F190" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G190" t="s">
         <v>41</v>
@@ -12690,7 +12690,7 @@
         <v>119</v>
       </c>
       <c r="F192" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G192" t="s">
         <v>41</v>
@@ -12746,7 +12746,7 @@
         <v>95</v>
       </c>
       <c r="F193" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G193" t="s">
         <v>41</v>
@@ -12802,7 +12802,7 @@
         <v>430</v>
       </c>
       <c r="F194" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G194" t="s">
         <v>41</v>
@@ -12858,7 +12858,7 @@
         <v>59</v>
       </c>
       <c r="F195" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G195" t="s">
         <v>41</v>
@@ -12914,7 +12914,7 @@
         <v>62</v>
       </c>
       <c r="F196" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G196" t="s">
         <v>41</v>
@@ -12970,7 +12970,7 @@
         <v>88</v>
       </c>
       <c r="F197" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G197" t="s">
         <v>41</v>
@@ -13026,13 +13026,13 @@
         <v>438</v>
       </c>
       <c r="F198" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G198" t="s">
         <v>41</v>
       </c>
       <c r="H198" t="s">
-        <v>371</v>
+        <v>333</v>
       </c>
       <c r="I198" t="s">
         <v>439</v>
@@ -13082,13 +13082,13 @@
         <v>438</v>
       </c>
       <c r="F199" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G199" t="s">
         <v>41</v>
       </c>
       <c r="H199" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="I199" t="s">
         <v>440</v>
@@ -13250,7 +13250,7 @@
         <v>186</v>
       </c>
       <c r="F202" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G202" t="s">
         <v>41</v>
@@ -13415,10 +13415,10 @@
         <v>33</v>
       </c>
       <c r="E205" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="F205" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G205" t="s">
         <v>41</v>
@@ -13430,10 +13430,10 @@
         <v>453</v>
       </c>
       <c r="J205" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="K205" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="L205" t="s">
         <v>34</v>
@@ -13445,7 +13445,7 @@
         <v>45</v>
       </c>
       <c r="O205" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="P205" t="s">
         <v>453</v>
@@ -13471,25 +13471,25 @@
         <v>34</v>
       </c>
       <c r="E206" t="s">
-        <v>347</v>
+        <v>454</v>
       </c>
       <c r="F206" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G206" t="s">
         <v>41</v>
       </c>
       <c r="H206" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I206" t="s">
         <v>455</v>
       </c>
       <c r="J206" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="K206" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="L206" t="s">
         <v>34</v>
@@ -13501,7 +13501,7 @@
         <v>45</v>
       </c>
       <c r="O206" t="s">
-        <v>320</v>
+        <v>456</v>
       </c>
       <c r="P206" t="s">
         <v>455</v>
@@ -13527,10 +13527,10 @@
         <v>34</v>
       </c>
       <c r="E207" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F207" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G207" t="s">
         <v>41</v>
@@ -13539,7 +13539,7 @@
         <v>452</v>
       </c>
       <c r="I207" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J207" t="s">
         <v>51</v>
@@ -13557,10 +13557,10 @@
         <v>45</v>
       </c>
       <c r="O207" t="s">
+        <v>459</v>
+      </c>
+      <c r="P207" t="s">
         <v>458</v>
-      </c>
-      <c r="P207" t="s">
-        <v>457</v>
       </c>
       <c r="Q207" t="s">
         <v>45</v>
@@ -13583,10 +13583,10 @@
         <v>34</v>
       </c>
       <c r="E208" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="F208" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G208" t="s">
         <v>41</v>
@@ -13595,13 +13595,13 @@
         <v>452</v>
       </c>
       <c r="I208" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J208" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="K208" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="L208" t="s">
         <v>34</v>
@@ -13613,10 +13613,10 @@
         <v>45</v>
       </c>
       <c r="O208" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="P208" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q208" t="s">
         <v>45</v>
@@ -13639,10 +13639,10 @@
         <v>34</v>
       </c>
       <c r="E209" t="s">
-        <v>460</v>
+        <v>54</v>
       </c>
       <c r="F209" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G209" t="s">
         <v>41</v>
@@ -13654,10 +13654,10 @@
         <v>461</v>
       </c>
       <c r="J209" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K209" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L209" t="s">
         <v>34</v>
@@ -13669,7 +13669,7 @@
         <v>45</v>
       </c>
       <c r="O209" t="s">
-        <v>462</v>
+        <v>58</v>
       </c>
       <c r="P209" t="s">
         <v>461</v>
@@ -13695,10 +13695,10 @@
         <v>34</v>
       </c>
       <c r="E210" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F210" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G210" t="s">
         <v>41</v>
@@ -13707,13 +13707,13 @@
         <v>452</v>
       </c>
       <c r="I210" t="s">
+        <v>463</v>
+      </c>
+      <c r="J210" t="s">
         <v>464</v>
       </c>
-      <c r="J210" t="s">
-        <v>51</v>
-      </c>
       <c r="K210" t="s">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="L210" t="s">
         <v>34</v>
@@ -13728,7 +13728,7 @@
         <v>465</v>
       </c>
       <c r="P210" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="Q210" t="s">
         <v>45</v>
@@ -13751,10 +13751,10 @@
         <v>34</v>
       </c>
       <c r="E211" t="s">
-        <v>59</v>
+        <v>466</v>
       </c>
       <c r="F211" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G211" t="s">
         <v>41</v>
@@ -13763,13 +13763,13 @@
         <v>452</v>
       </c>
       <c r="I211" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J211" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K211" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L211" t="s">
         <v>34</v>
@@ -13781,10 +13781,10 @@
         <v>45</v>
       </c>
       <c r="O211" t="s">
-        <v>61</v>
+        <v>468</v>
       </c>
       <c r="P211" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Q211" t="s">
         <v>45</v>
@@ -13807,25 +13807,25 @@
         <v>34</v>
       </c>
       <c r="E212" t="s">
-        <v>467</v>
+        <v>347</v>
       </c>
       <c r="F212" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G212" t="s">
         <v>41</v>
       </c>
       <c r="H212" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="I212" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J212" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K212" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L212" t="s">
         <v>34</v>
@@ -13837,10 +13837,10 @@
         <v>45</v>
       </c>
       <c r="O212" t="s">
-        <v>469</v>
+        <v>320</v>
       </c>
       <c r="P212" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="Q212" t="s">
         <v>45</v>
@@ -13863,10 +13863,10 @@
         <v>34</v>
       </c>
       <c r="E213" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F213" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G213" t="s">
         <v>41</v>
@@ -13875,7 +13875,7 @@
         <v>452</v>
       </c>
       <c r="I213" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J213" t="s">
         <v>51</v>
@@ -13893,10 +13893,10 @@
         <v>45</v>
       </c>
       <c r="O213" t="s">
+        <v>473</v>
+      </c>
+      <c r="P213" t="s">
         <v>472</v>
-      </c>
-      <c r="P213" t="s">
-        <v>471</v>
       </c>
       <c r="Q213" t="s">
         <v>45</v>
@@ -13919,10 +13919,10 @@
         <v>34</v>
       </c>
       <c r="E214" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F214" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G214" t="s">
         <v>41</v>
@@ -13931,13 +13931,13 @@
         <v>452</v>
       </c>
       <c r="I214" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J214" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K214" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L214" t="s">
         <v>34</v>
@@ -13949,10 +13949,10 @@
         <v>45</v>
       </c>
       <c r="O214" t="s">
+        <v>61</v>
+      </c>
+      <c r="P214" t="s">
         <v>475</v>
-      </c>
-      <c r="P214" t="s">
-        <v>474</v>
       </c>
       <c r="Q214" t="s">
         <v>45</v>
@@ -13978,7 +13978,7 @@
         <v>476</v>
       </c>
       <c r="F215" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G215" t="s">
         <v>41</v>
@@ -14034,7 +14034,7 @@
         <v>479</v>
       </c>
       <c r="F216" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G216" t="s">
         <v>41</v>
@@ -14090,7 +14090,7 @@
         <v>482</v>
       </c>
       <c r="F217" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G217" t="s">
         <v>41</v>
@@ -14146,7 +14146,7 @@
         <v>485</v>
       </c>
       <c r="F218" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G218" t="s">
         <v>41</v>
@@ -14173,7 +14173,7 @@
         <v>45</v>
       </c>
       <c r="O218" t="s">
-        <v>487</v>
+        <v>140</v>
       </c>
       <c r="P218" t="s">
         <v>486</v>
@@ -14199,10 +14199,10 @@
         <v>34</v>
       </c>
       <c r="E219" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F219" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G219" t="s">
         <v>41</v>
@@ -14211,7 +14211,7 @@
         <v>452</v>
       </c>
       <c r="I219" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J219" t="s">
         <v>51</v>
@@ -14229,10 +14229,10 @@
         <v>45</v>
       </c>
       <c r="O219" t="s">
-        <v>140</v>
+        <v>489</v>
       </c>
       <c r="P219" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q219" t="s">
         <v>45</v>
@@ -14258,7 +14258,7 @@
         <v>490</v>
       </c>
       <c r="F220" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G220" t="s">
         <v>41</v>
@@ -14270,10 +14270,10 @@
         <v>491</v>
       </c>
       <c r="J220" t="s">
-        <v>492</v>
+        <v>51</v>
       </c>
       <c r="K220" t="s">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="L220" t="s">
         <v>34</v>
@@ -14285,7 +14285,7 @@
         <v>45</v>
       </c>
       <c r="O220" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="P220" t="s">
         <v>491</v>
@@ -14311,10 +14311,10 @@
         <v>34</v>
       </c>
       <c r="E221" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F221" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G221" t="s">
         <v>41</v>
@@ -14323,13 +14323,13 @@
         <v>452</v>
       </c>
       <c r="I221" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J221" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K221" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L221" t="s">
         <v>34</v>
@@ -14341,10 +14341,10 @@
         <v>45</v>
       </c>
       <c r="O221" t="s">
-        <v>61</v>
+        <v>495</v>
       </c>
       <c r="P221" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q221" t="s">
         <v>45</v>
@@ -14479,7 +14479,7 @@
         <v>33</v>
       </c>
       <c r="E224" t="s">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="F224" t="s">
         <v>162</v>
@@ -14494,10 +14494,10 @@
         <v>501</v>
       </c>
       <c r="J224" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="K224" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="L224" t="s">
         <v>34</v>
@@ -14509,7 +14509,7 @@
         <v>45</v>
       </c>
       <c r="O224" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="P224" t="s">
         <v>501</v>
@@ -14535,7 +14535,7 @@
         <v>34</v>
       </c>
       <c r="E225" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="F225" t="s">
         <v>162</v>
@@ -14550,10 +14550,10 @@
         <v>501</v>
       </c>
       <c r="J225" t="s">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="K225" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L225" t="s">
         <v>34</v>
@@ -14565,7 +14565,7 @@
         <v>45</v>
       </c>
       <c r="O225" t="s">
-        <v>304</v>
+        <v>81</v>
       </c>
       <c r="P225" t="s">
         <v>501</v>
@@ -14591,7 +14591,7 @@
         <v>34</v>
       </c>
       <c r="E226" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="F226" t="s">
         <v>162</v>
@@ -14606,10 +14606,10 @@
         <v>501</v>
       </c>
       <c r="J226" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="K226" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L226" t="s">
         <v>34</v>
@@ -14621,7 +14621,7 @@
         <v>45</v>
       </c>
       <c r="O226" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="P226" t="s">
         <v>501</v>
@@ -14647,7 +14647,7 @@
         <v>34</v>
       </c>
       <c r="E227" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="F227" t="s">
         <v>162</v>
@@ -14662,10 +14662,10 @@
         <v>501</v>
       </c>
       <c r="J227" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="K227" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="L227" t="s">
         <v>34</v>
@@ -14677,7 +14677,7 @@
         <v>45</v>
       </c>
       <c r="O227" t="s">
-        <v>92</v>
+        <v>304</v>
       </c>
       <c r="P227" t="s">
         <v>501</v>
@@ -14703,7 +14703,7 @@
         <v>34</v>
       </c>
       <c r="E228" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="F228" t="s">
         <v>162</v>
@@ -14718,10 +14718,10 @@
         <v>501</v>
       </c>
       <c r="J228" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="K228" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="L228" t="s">
         <v>34</v>
@@ -14733,7 +14733,7 @@
         <v>45</v>
       </c>
       <c r="O228" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P228" t="s">
         <v>501</v>
@@ -14759,7 +14759,7 @@
         <v>34</v>
       </c>
       <c r="E229" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F229" t="s">
         <v>162</v>
@@ -14774,10 +14774,10 @@
         <v>501</v>
       </c>
       <c r="J229" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="K229" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="L229" t="s">
         <v>34</v>
@@ -14789,7 +14789,7 @@
         <v>45</v>
       </c>
       <c r="O229" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="P229" t="s">
         <v>501</v>
@@ -14815,7 +14815,7 @@
         <v>34</v>
       </c>
       <c r="E230" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="F230" t="s">
         <v>162</v>
@@ -14830,10 +14830,10 @@
         <v>501</v>
       </c>
       <c r="J230" t="s">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="K230" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="L230" t="s">
         <v>34</v>
@@ -14845,7 +14845,7 @@
         <v>45</v>
       </c>
       <c r="O230" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="P230" t="s">
         <v>501</v>
@@ -15110,13 +15110,13 @@
         <v>508</v>
       </c>
       <c r="J235" t="s">
+        <v>257</v>
+      </c>
+      <c r="K235" t="s">
+        <v>44</v>
+      </c>
+      <c r="L235" t="s">
         <v>509</v>
-      </c>
-      <c r="K235" t="s">
-        <v>138</v>
-      </c>
-      <c r="L235" t="s">
-        <v>510</v>
       </c>
       <c r="M235" t="s">
         <v>505</v>
@@ -15151,7 +15151,7 @@
         <v>34</v>
       </c>
       <c r="E236" t="s">
-        <v>506</v>
+        <v>149</v>
       </c>
       <c r="F236" t="s">
         <v>162</v>
@@ -15160,16 +15160,16 @@
         <v>41</v>
       </c>
       <c r="H236" t="s">
+        <v>510</v>
+      </c>
+      <c r="I236" t="s">
         <v>511</v>
       </c>
-      <c r="I236" t="s">
+      <c r="J236" t="s">
         <v>512</v>
       </c>
-      <c r="J236" t="s">
-        <v>257</v>
-      </c>
       <c r="K236" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="L236" t="s">
         <v>513</v>
@@ -15184,7 +15184,7 @@
         <v>140</v>
       </c>
       <c r="P236" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="Q236" t="s">
         <v>45</v>
@@ -15207,7 +15207,7 @@
         <v>34</v>
       </c>
       <c r="E237" t="s">
-        <v>144</v>
+        <v>506</v>
       </c>
       <c r="F237" t="s">
         <v>162</v>
@@ -15225,7 +15225,7 @@
         <v>516</v>
       </c>
       <c r="K237" t="s">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="L237" t="s">
         <v>517</v>
@@ -15502,7 +15502,7 @@
         <v>529</v>
       </c>
       <c r="J242" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="K242" t="s">
         <v>44</v>
@@ -15658,7 +15658,7 @@
         <v>536</v>
       </c>
       <c r="F245" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G245" t="s">
         <v>41</v>
@@ -15726,7 +15726,7 @@
         <v>540</v>
       </c>
       <c r="J246" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="K246" t="s">
         <v>44</v>
@@ -15782,7 +15782,7 @@
         <v>543</v>
       </c>
       <c r="J247" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="K247" t="s">
         <v>44</v>
@@ -15894,7 +15894,7 @@
         <v>529</v>
       </c>
       <c r="J249" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="K249" t="s">
         <v>44</v>
@@ -15994,7 +15994,7 @@
         <v>552</v>
       </c>
       <c r="F251" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G251" t="s">
         <v>41</v>
@@ -16047,7 +16047,7 @@
         <v>34</v>
       </c>
       <c r="E252" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F252" t="s">
         <v>162</v>
@@ -16118,7 +16118,7 @@
         <v>559</v>
       </c>
       <c r="J253" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="K253" t="s">
         <v>44</v>
@@ -16162,7 +16162,7 @@
         <v>552</v>
       </c>
       <c r="F254" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G254" t="s">
         <v>41</v>
@@ -16230,7 +16230,7 @@
         <v>564</v>
       </c>
       <c r="J255" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="K255" t="s">
         <v>44</v>
@@ -16271,7 +16271,7 @@
         <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F256" t="s">
         <v>162</v>
@@ -16342,7 +16342,7 @@
         <v>569</v>
       </c>
       <c r="J257" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="K257" t="s">
         <v>44</v>
@@ -16946,7 +16946,7 @@
         <v>593</v>
       </c>
       <c r="F268" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G268" t="s">
         <v>41</v>
@@ -17002,7 +17002,7 @@
         <v>593</v>
       </c>
       <c r="F269" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G269" t="s">
         <v>41</v>
@@ -17182,7 +17182,7 @@
         <v>604</v>
       </c>
       <c r="J272" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="K272" t="s">
         <v>138</v>
@@ -17226,7 +17226,7 @@
         <v>608</v>
       </c>
       <c r="F273" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G273" t="s">
         <v>41</v>
@@ -17462,7 +17462,7 @@
         <v>622</v>
       </c>
       <c r="J277" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="K277" t="s">
         <v>44</v>
@@ -17630,7 +17630,7 @@
         <v>634</v>
       </c>
       <c r="J280" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="K280" t="s">
         <v>554</v>
@@ -17730,7 +17730,7 @@
         <v>639</v>
       </c>
       <c r="F282" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G282" t="s">
         <v>41</v>
@@ -17742,10 +17742,10 @@
         <v>641</v>
       </c>
       <c r="J282" t="s">
-        <v>642</v>
+        <v>51</v>
       </c>
       <c r="K282" t="s">
-        <v>262</v>
+        <v>51</v>
       </c>
       <c r="L282" t="s">
         <v>34</v>
@@ -17783,25 +17783,25 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
+        <v>642</v>
+      </c>
+      <c r="F283" t="s">
+        <v>145</v>
+      </c>
+      <c r="G283" t="s">
+        <v>41</v>
+      </c>
+      <c r="H283" t="s">
         <v>643</v>
-      </c>
-      <c r="F283" t="s">
-        <v>150</v>
-      </c>
-      <c r="G283" t="s">
-        <v>41</v>
-      </c>
-      <c r="H283" t="s">
-        <v>640</v>
       </c>
       <c r="I283" t="s">
         <v>641</v>
       </c>
       <c r="J283" t="s">
-        <v>644</v>
+        <v>91</v>
       </c>
       <c r="K283" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="L283" t="s">
         <v>34</v>
@@ -17839,28 +17839,28 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>602</v>
+        <v>644</v>
       </c>
       <c r="F284" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="G284" t="s">
         <v>41</v>
       </c>
       <c r="H284" t="s">
+        <v>640</v>
+      </c>
+      <c r="I284" t="s">
+        <v>641</v>
+      </c>
+      <c r="J284" t="s">
         <v>645</v>
       </c>
-      <c r="I284" t="s">
-        <v>646</v>
-      </c>
-      <c r="J284" t="s">
-        <v>509</v>
-      </c>
       <c r="K284" t="s">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="L284" t="s">
-        <v>647</v>
+        <v>34</v>
       </c>
       <c r="M284" t="s">
         <v>638</v>
@@ -17872,7 +17872,7 @@
         <v>140</v>
       </c>
       <c r="P284" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="Q284" t="s">
         <v>45</v>
@@ -17895,28 +17895,28 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
+        <v>602</v>
+      </c>
+      <c r="F285" t="s">
+        <v>162</v>
+      </c>
+      <c r="G285" t="s">
+        <v>41</v>
+      </c>
+      <c r="H285" t="s">
+        <v>646</v>
+      </c>
+      <c r="I285" t="s">
+        <v>647</v>
+      </c>
+      <c r="J285" t="s">
+        <v>516</v>
+      </c>
+      <c r="K285" t="s">
+        <v>138</v>
+      </c>
+      <c r="L285" t="s">
         <v>648</v>
-      </c>
-      <c r="F285" t="s">
-        <v>150</v>
-      </c>
-      <c r="G285" t="s">
-        <v>41</v>
-      </c>
-      <c r="H285" t="s">
-        <v>649</v>
-      </c>
-      <c r="I285" t="s">
-        <v>641</v>
-      </c>
-      <c r="J285" t="s">
-        <v>91</v>
-      </c>
-      <c r="K285" t="s">
-        <v>75</v>
-      </c>
-      <c r="L285" t="s">
-        <v>34</v>
       </c>
       <c r="M285" t="s">
         <v>638</v>
@@ -17928,7 +17928,7 @@
         <v>140</v>
       </c>
       <c r="P285" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="Q285" t="s">
         <v>45</v>
@@ -17951,10 +17951,10 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F286" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G286" t="s">
         <v>41</v>
@@ -17963,13 +17963,13 @@
         <v>640</v>
       </c>
       <c r="I286" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="J286" t="s">
-        <v>51</v>
+        <v>554</v>
       </c>
       <c r="K286" t="s">
-        <v>51</v>
+        <v>554</v>
       </c>
       <c r="L286" t="s">
         <v>34</v>
@@ -17984,7 +17984,7 @@
         <v>140</v>
       </c>
       <c r="P286" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="Q286" t="s">
         <v>45</v>
@@ -18010,7 +18010,7 @@
         <v>651</v>
       </c>
       <c r="F287" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G287" t="s">
         <v>41</v>
@@ -18019,13 +18019,13 @@
         <v>640</v>
       </c>
       <c r="I287" t="s">
+        <v>641</v>
+      </c>
+      <c r="J287" t="s">
         <v>652</v>
       </c>
-      <c r="J287" t="s">
-        <v>554</v>
-      </c>
       <c r="K287" t="s">
-        <v>554</v>
+        <v>51</v>
       </c>
       <c r="L287" t="s">
         <v>34</v>
@@ -18040,7 +18040,7 @@
         <v>140</v>
       </c>
       <c r="P287" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="Q287" t="s">
         <v>45</v>
@@ -18122,7 +18122,7 @@
         <v>656</v>
       </c>
       <c r="F289" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G289" t="s">
         <v>41</v>
@@ -18137,7 +18137,7 @@
         <v>237</v>
       </c>
       <c r="K289" t="s">
-        <v>51</v>
+        <v>554</v>
       </c>
       <c r="L289" t="s">
         <v>659</v>
@@ -18178,7 +18178,7 @@
         <v>660</v>
       </c>
       <c r="F290" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G290" t="s">
         <v>41</v>
@@ -18193,7 +18193,7 @@
         <v>237</v>
       </c>
       <c r="K290" t="s">
-        <v>554</v>
+        <v>51</v>
       </c>
       <c r="L290" t="s">
         <v>663</v>
@@ -18302,7 +18302,7 @@
         <v>669</v>
       </c>
       <c r="J292" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="K292" t="s">
         <v>44</v>
@@ -18511,7 +18511,7 @@
         <v>33</v>
       </c>
       <c r="E296" t="s">
-        <v>685</v>
+        <v>506</v>
       </c>
       <c r="F296" t="s">
         <v>162</v>
@@ -18520,19 +18520,19 @@
         <v>41</v>
       </c>
       <c r="H296" t="s">
+        <v>685</v>
+      </c>
+      <c r="I296" t="s">
         <v>686</v>
       </c>
-      <c r="I296" t="s">
+      <c r="J296" t="s">
+        <v>257</v>
+      </c>
+      <c r="K296" t="s">
+        <v>44</v>
+      </c>
+      <c r="L296" t="s">
         <v>687</v>
-      </c>
-      <c r="J296" t="s">
-        <v>57</v>
-      </c>
-      <c r="K296" t="s">
-        <v>153</v>
-      </c>
-      <c r="L296" t="s">
-        <v>688</v>
       </c>
       <c r="M296" t="s">
         <v>684</v>
@@ -18544,7 +18544,7 @@
         <v>140</v>
       </c>
       <c r="P296" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="Q296" t="s">
         <v>45</v>
@@ -18567,7 +18567,7 @@
         <v>34</v>
       </c>
       <c r="E297" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F297" t="s">
         <v>162</v>
@@ -18576,16 +18576,16 @@
         <v>41</v>
       </c>
       <c r="H297" t="s">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="I297" t="s">
         <v>690</v>
       </c>
       <c r="J297" t="s">
-        <v>644</v>
+        <v>57</v>
       </c>
       <c r="K297" t="s">
-        <v>44</v>
+        <v>148</v>
       </c>
       <c r="L297" t="s">
         <v>691</v>
@@ -18638,7 +18638,7 @@
         <v>693</v>
       </c>
       <c r="J298" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="K298" t="s">
         <v>44</v>
@@ -18694,13 +18694,13 @@
         <v>696</v>
       </c>
       <c r="J299" t="s">
-        <v>697</v>
+        <v>652</v>
       </c>
       <c r="K299" t="s">
         <v>44</v>
       </c>
       <c r="L299" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="M299" t="s">
         <v>684</v>
@@ -18735,7 +18735,7 @@
         <v>34</v>
       </c>
       <c r="E300" t="s">
-        <v>506</v>
+        <v>698</v>
       </c>
       <c r="F300" t="s">
         <v>162</v>
@@ -18744,13 +18744,13 @@
         <v>41</v>
       </c>
       <c r="H300" t="s">
+        <v>679</v>
+      </c>
+      <c r="I300" t="s">
         <v>699</v>
       </c>
-      <c r="I300" t="s">
+      <c r="J300" t="s">
         <v>700</v>
-      </c>
-      <c r="J300" t="s">
-        <v>257</v>
       </c>
       <c r="K300" t="s">
         <v>44</v>
@@ -18768,7 +18768,7 @@
         <v>140</v>
       </c>
       <c r="P300" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="Q300" t="s">
         <v>45</v>
@@ -18791,7 +18791,7 @@
         <v>34</v>
       </c>
       <c r="E301" t="s">
-        <v>702</v>
+        <v>506</v>
       </c>
       <c r="F301" t="s">
         <v>162</v>
@@ -18800,16 +18800,16 @@
         <v>41</v>
       </c>
       <c r="H301" t="s">
-        <v>703</v>
+        <v>679</v>
       </c>
       <c r="I301" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="J301" t="s">
-        <v>705</v>
+        <v>257</v>
       </c>
       <c r="K301" t="s">
-        <v>44</v>
+        <v>645</v>
       </c>
       <c r="L301" t="s">
         <v>703</v>
@@ -18824,7 +18824,7 @@
         <v>140</v>
       </c>
       <c r="P301" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="Q301" t="s">
         <v>45</v>
@@ -18847,7 +18847,7 @@
         <v>34</v>
       </c>
       <c r="E302" t="s">
-        <v>506</v>
+        <v>704</v>
       </c>
       <c r="F302" t="s">
         <v>162</v>
@@ -18856,19 +18856,19 @@
         <v>41</v>
       </c>
       <c r="H302" t="s">
-        <v>679</v>
+        <v>705</v>
       </c>
       <c r="I302" t="s">
         <v>706</v>
       </c>
       <c r="J302" t="s">
-        <v>257</v>
+        <v>707</v>
       </c>
       <c r="K302" t="s">
-        <v>642</v>
+        <v>44</v>
       </c>
       <c r="L302" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="M302" t="s">
         <v>684</v>
@@ -18974,7 +18974,7 @@
         <v>712</v>
       </c>
       <c r="J304" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="K304" t="s">
         <v>44</v>
@@ -19074,7 +19074,7 @@
         <v>718</v>
       </c>
       <c r="F306" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G306" t="s">
         <v>41</v>
@@ -19142,7 +19142,7 @@
         <v>725</v>
       </c>
       <c r="J307" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="K307" t="s">
         <v>44</v>
@@ -19186,7 +19186,7 @@
         <v>729</v>
       </c>
       <c r="F308" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G308" t="s">
         <v>41</v>
@@ -19354,7 +19354,7 @@
         <v>742</v>
       </c>
       <c r="F311" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G311" t="s">
         <v>41</v>
@@ -19422,7 +19422,7 @@
         <v>748</v>
       </c>
       <c r="J312" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="K312" t="s">
         <v>44</v>
@@ -19478,7 +19478,7 @@
         <v>751</v>
       </c>
       <c r="J313" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="K313" t="s">
         <v>91</v>
@@ -19519,7 +19519,7 @@
         <v>33</v>
       </c>
       <c r="E314" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F314" t="s">
         <v>162</v>
@@ -19534,7 +19534,7 @@
         <v>756</v>
       </c>
       <c r="J314" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="K314" t="s">
         <v>44</v>
@@ -19746,7 +19746,7 @@
         <v>763</v>
       </c>
       <c r="F318" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G318" t="s">
         <v>41</v>

--- a/xlsx/dre/DRE_06_2026.xlsx
+++ b/xlsx/dre/DRE_06_2026.xlsx
@@ -447,6 +447,21 @@
     <t>R$  178,31</t>
   </si>
   <si>
+    <t>1/5</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>R$  441,79</t>
+  </si>
+  <si>
+    <t>27/02/26</t>
+  </si>
+  <si>
+    <t>Digisac MP 2026</t>
+  </si>
+  <si>
     <t>685/1</t>
   </si>
   <si>
@@ -460,21 +475,6 @@
   </si>
   <si>
     <t>22/06/26</t>
-  </si>
-  <si>
-    <t>1/5</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>R$  441,79</t>
-  </si>
-  <si>
-    <t>27/02/26</t>
-  </si>
-  <si>
-    <t>Digisac MP 2026</t>
   </si>
   <si>
     <t>4 CUSTOS E DESPESAS</t>
@@ -697,6 +697,15 @@
     <t>R$ 1.915,14</t>
   </si>
   <si>
+    <t>64301/1</t>
+  </si>
+  <si>
+    <t>PFR</t>
+  </si>
+  <si>
+    <t>R$  1.622,10</t>
+  </si>
+  <si>
     <t>76601/1</t>
   </si>
   <si>
@@ -707,69 +716,55 @@
 Título gerado pela diferença de valor da revisão.</t>
   </si>
   <si>
-    <t>64301/1</t>
-  </si>
-  <si>
-    <t>PFR</t>
-  </si>
-  <si>
-    <t>R$  1.622,10</t>
-  </si>
-  <si>
     <t>4.02.01.01.04 Compra de outras mercadorias</t>
   </si>
   <si>
     <t>R$ 2.711,52</t>
   </si>
   <si>
-    <t>698/1</t>
-  </si>
-  <si>
-    <t>R$  113,98</t>
+    <t>695/1</t>
+  </si>
+  <si>
+    <t>FERRAGENS FLORESTA EIRELI EPP</t>
+  </si>
+  <si>
+    <t>R$  232,50</t>
+  </si>
+  <si>
+    <t>03/07/26</t>
+  </si>
+  <si>
+    <t>9/6</t>
+  </si>
+  <si>
+    <t>Mercado livre</t>
+  </si>
+  <si>
+    <t>R$  91,87</t>
+  </si>
+  <si>
+    <t>09/01/26</t>
+  </si>
+  <si>
+    <t>Grapa</t>
+  </si>
+  <si>
+    <t>691/1</t>
+  </si>
+  <si>
+    <t>R$  174,73</t>
+  </si>
+  <si>
+    <t>17/06/26</t>
+  </si>
+  <si>
+    <t>703/1</t>
+  </si>
+  <si>
+    <t>R$  1.522,18</t>
   </si>
   <si>
     <t>06/07/26</t>
-  </si>
-  <si>
-    <t>D4 sign/1</t>
-  </si>
-  <si>
-    <t>R$  49,50</t>
-  </si>
-  <si>
-    <t>D4</t>
-  </si>
-  <si>
-    <t>701/1</t>
-  </si>
-  <si>
-    <t>Mercado livre</t>
-  </si>
-  <si>
-    <t>R$  76,23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22,46	Mercado Livre	Envelope + cartão
-53,77	Mercado Livre	Papel interfolhado
-</t>
-  </si>
-  <si>
-    <t>695/1</t>
-  </si>
-  <si>
-    <t>FERRAGENS FLORESTA EIRELI EPP</t>
-  </si>
-  <si>
-    <t>R$  232,50</t>
-  </si>
-  <si>
-    <t>03/07/26</t>
-  </si>
-  <si>
-    <t>703/1</t>
-  </si>
-  <si>
-    <t>R$  1.522,18</t>
   </si>
   <si>
     <t xml:space="preserve">Valor	Fornecedor	Descrição
@@ -781,25 +776,28 @@
 </t>
   </si>
   <si>
-    <t>691/1</t>
-  </si>
-  <si>
-    <t>R$  174,73</t>
-  </si>
-  <si>
-    <t>17/06/26</t>
-  </si>
-  <si>
-    <t>9/6</t>
-  </si>
-  <si>
-    <t>R$  91,87</t>
-  </si>
-  <si>
-    <t>09/01/26</t>
-  </si>
-  <si>
-    <t>Grapa</t>
+    <t>698/1</t>
+  </si>
+  <si>
+    <t>R$  113,98</t>
+  </si>
+  <si>
+    <t>687/1</t>
+  </si>
+  <si>
+    <t>R$  89,80</t>
+  </si>
+  <si>
+    <t>705/1</t>
+  </si>
+  <si>
+    <t>R$  150,41</t>
+  </si>
+  <si>
+    <t>20/07/26</t>
+  </si>
+  <si>
+    <t>Estoque</t>
   </si>
   <si>
     <t>667/1</t>
@@ -818,22 +816,24 @@
 </t>
   </si>
   <si>
-    <t>687/1</t>
-  </si>
-  <si>
-    <t>R$  89,80</t>
-  </si>
-  <si>
-    <t>705/1</t>
-  </si>
-  <si>
-    <t>R$  150,41</t>
-  </si>
-  <si>
-    <t>20/07/26</t>
-  </si>
-  <si>
-    <t>Estoque</t>
+    <t>D4 sign/1</t>
+  </si>
+  <si>
+    <t>R$  49,50</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>701/1</t>
+  </si>
+  <si>
+    <t>R$  76,23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,46	Mercado Livre	Envelope + cartão
+53,77	Mercado Livre	Papel interfolhado
+</t>
   </si>
   <si>
     <t>4.02.02 CUSTO DE TRANSPORTE</t>
@@ -878,6 +878,15 @@
     <t>R$  8.627,93</t>
   </si>
   <si>
+    <t>85601/0</t>
+  </si>
+  <si>
+    <t>R$  95,00</t>
+  </si>
+  <si>
+    <t>85601KrisdanyVSMC</t>
+  </si>
+  <si>
     <t>83001/2</t>
   </si>
   <si>
@@ -932,6 +941,9 @@
     <t>R$  1.577,95</t>
   </si>
   <si>
+    <t>R$  30,00</t>
+  </si>
+  <si>
     <t>85701/3</t>
   </si>
   <si>
@@ -968,6 +980,12 @@
     <t>85701HelgaBA</t>
   </si>
   <si>
+    <t>81801/2</t>
+  </si>
+  <si>
+    <t>Chapa de MDF cliente Andre Soy Parc 2/3</t>
+  </si>
+  <si>
     <t>84102/3</t>
   </si>
   <si>
@@ -980,24 +998,6 @@
     <t>R$  1.779,72</t>
   </si>
   <si>
-    <t>85601/0</t>
-  </si>
-  <si>
-    <t>R$  95,00</t>
-  </si>
-  <si>
-    <t>85601KrisdanyVSMC</t>
-  </si>
-  <si>
-    <t>R$  30,00</t>
-  </si>
-  <si>
-    <t>81801/2</t>
-  </si>
-  <si>
-    <t>Chapa de MDF cliente Andre Soy Parc 2/3</t>
-  </si>
-  <si>
     <t>R$  75,63</t>
   </si>
   <si>
@@ -1028,36 +1028,36 @@
     <t>FELIPE DOMINGOS BARBOSA</t>
   </si>
   <si>
+    <t>R$  228,19</t>
+  </si>
+  <si>
+    <t>R$  2.451,16</t>
+  </si>
+  <si>
+    <t>R$  164,57</t>
+  </si>
+  <si>
+    <t>R$  1.229,76</t>
+  </si>
+  <si>
+    <t>R$  993,95</t>
+  </si>
+  <si>
+    <t>R$  4.535,13</t>
+  </si>
+  <si>
+    <t>R$  223,80</t>
+  </si>
+  <si>
+    <t>R$  288,02</t>
+  </si>
+  <si>
+    <t>R$  1.149,42</t>
+  </si>
+  <si>
     <t>R$  1.614,60</t>
   </si>
   <si>
-    <t>R$  228,19</t>
-  </si>
-  <si>
-    <t>R$  2.451,16</t>
-  </si>
-  <si>
-    <t>R$  164,57</t>
-  </si>
-  <si>
-    <t>R$  1.229,76</t>
-  </si>
-  <si>
-    <t>R$  993,95</t>
-  </si>
-  <si>
-    <t>R$  4.535,13</t>
-  </si>
-  <si>
-    <t>R$  223,80</t>
-  </si>
-  <si>
-    <t>R$  288,02</t>
-  </si>
-  <si>
-    <t>R$  1.149,42</t>
-  </si>
-  <si>
     <t>4.03.01.02.02 Comissões vendas</t>
   </si>
   <si>
@@ -1223,45 +1223,45 @@
     <t>R$  1.149,31</t>
   </si>
   <si>
+    <t>RAYSSA BARBOSA LEMOS</t>
+  </si>
+  <si>
+    <t>82201/1</t>
+  </si>
+  <si>
+    <t>R$  12,29</t>
+  </si>
+  <si>
+    <t>82201RuanCGS</t>
+  </si>
+  <si>
+    <t>79202/2</t>
+  </si>
+  <si>
+    <t>PPC</t>
+  </si>
+  <si>
+    <t>84601/2</t>
+  </si>
+  <si>
+    <t>R$  2,40</t>
+  </si>
+  <si>
+    <t>Jose Carlos de Carvalho</t>
+  </si>
+  <si>
+    <t>R$  1.229,74</t>
+  </si>
+  <si>
     <t>82201/2</t>
   </si>
   <si>
-    <t>PPC</t>
-  </si>
-  <si>
-    <t>R$  12,29</t>
-  </si>
-  <si>
     <t>03/06/26</t>
   </si>
   <si>
-    <t>Jose Carlos de Carvalho</t>
-  </si>
-  <si>
     <t>R$  4.535,18</t>
   </si>
   <si>
-    <t>82201/1</t>
-  </si>
-  <si>
-    <t>82201RuanCGS</t>
-  </si>
-  <si>
-    <t>79202/2</t>
-  </si>
-  <si>
-    <t>84601/2</t>
-  </si>
-  <si>
-    <t>R$  2,40</t>
-  </si>
-  <si>
-    <t>R$  1.229,74</t>
-  </si>
-  <si>
-    <t>RAYSSA BARBOSA LEMOS</t>
-  </si>
-  <si>
     <t>85601/2</t>
   </si>
   <si>
@@ -1343,12 +1343,12 @@
     <t>DSR jun26/1</t>
   </si>
   <si>
+    <t>R$  2.151,72</t>
+  </si>
+  <si>
     <t>R$  1.207,83</t>
   </si>
   <si>
-    <t>R$  2.151,72</t>
-  </si>
-  <si>
     <t>4.03.02 COMISSÕES E BÔNUS DE TERCEIROS</t>
   </si>
   <si>
@@ -1547,6 +1547,18 @@
     <t>12/6</t>
   </si>
   <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
     <t>Google</t>
   </si>
   <si>
@@ -1568,18 +1580,6 @@
     <t>Webgiga 2026</t>
   </si>
   <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
-  </si>
-  <si>
     <t>1/4</t>
   </si>
   <si>
@@ -1634,6 +1634,57 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>Fixo jun26/1</t>
+  </si>
+  <si>
+    <t>EFRAIM RIBEIRO</t>
+  </si>
+  <si>
+    <t>R$  1.060,00</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>R$  2.365,00</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  4.687,39</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  7.800,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
     <t>fixo jun26/0</t>
   </si>
   <si>
@@ -1643,13 +1694,40 @@
     <t>R$  1.268,00</t>
   </si>
   <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  7.800,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
+    <t>R$  1.679,77</t>
+  </si>
+  <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>R$  1.419,85</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
+  </si>
+  <si>
+    <t>R$  1.024,58</t>
+  </si>
+  <si>
+    <t>Rubens - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>R$  2.536,00</t>
+  </si>
+  <si>
+    <t>19/02/26</t>
+  </si>
+  <si>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
+    <t>02/06/26</t>
   </si>
   <si>
     <t>Denny Lucas do Carmo Pereira</t>
@@ -1661,84 +1739,6 @@
     <t>Denny Lucas - Pagamento 2026</t>
   </si>
   <si>
-    <t>R$  1.419,85</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
-    <t>R$  1.024,58</t>
-  </si>
-  <si>
-    <t>Rubens - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Fixo jun26/1</t>
-  </si>
-  <si>
-    <t>R$  2.536,00</t>
-  </si>
-  <si>
-    <t>02/06/26</t>
-  </si>
-  <si>
-    <t>R$  1.679,77</t>
-  </si>
-  <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>R$  2.365,00</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>EFRAIM RIBEIRO</t>
-  </si>
-  <si>
-    <t>R$  1.060,00</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  4.687,39</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>19/02/26</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
   </si>
   <si>
@@ -1943,48 +1943,48 @@
     <t>4.04.02.05.02 Serviços de limpeza</t>
   </si>
   <si>
+    <t>664/1</t>
+  </si>
+  <si>
+    <t>Claudineuza Santos Machado</t>
+  </si>
+  <si>
+    <t>R$  230,00</t>
+  </si>
+  <si>
+    <t>08/06/26</t>
+  </si>
+  <si>
+    <t>673/1</t>
+  </si>
+  <si>
+    <t>11/06/26</t>
+  </si>
+  <si>
+    <t>Thais Pereira Pires</t>
+  </si>
+  <si>
+    <t>R$  1.600,00</t>
+  </si>
+  <si>
+    <t>Thais Limpeza - 2026</t>
+  </si>
+  <si>
+    <t>683/1</t>
+  </si>
+  <si>
+    <t>Sabrina Barbosa de Medeiros</t>
+  </si>
+  <si>
     <t>675/1</t>
   </si>
   <si>
-    <t>Claudineuza Santos Machado</t>
-  </si>
-  <si>
-    <t>R$  230,00</t>
-  </si>
-  <si>
-    <t>683/1</t>
-  </si>
-  <si>
-    <t>Sabrina Barbosa de Medeiros</t>
-  </si>
-  <si>
-    <t>664/1</t>
-  </si>
-  <si>
-    <t>08/06/26</t>
-  </si>
-  <si>
-    <t>Thais Pereira Pires</t>
-  </si>
-  <si>
-    <t>R$  1.600,00</t>
-  </si>
-  <si>
-    <t>Thais Limpeza - 2026</t>
-  </si>
-  <si>
     <t>663/1</t>
   </si>
   <si>
     <t>R$  220,00</t>
   </si>
   <si>
-    <t>673/1</t>
-  </si>
-  <si>
-    <t>11/06/26</t>
-  </si>
-  <si>
     <t>4.04.02.06 Material de escritório</t>
   </si>
   <si>
@@ -1992,18 +1992,6 @@
   </si>
   <si>
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
-  </si>
-  <si>
-    <t>699/1</t>
-  </si>
-  <si>
-    <t>Pão de Açúcar</t>
-  </si>
-  <si>
-    <t>R$  95,17</t>
-  </si>
-  <si>
-    <t>material limpeza</t>
   </si>
   <si>
     <t>700/1</t>
@@ -2022,6 +2010,18 @@
 </t>
   </si>
   <si>
+    <t>699/1</t>
+  </si>
+  <si>
+    <t>Pão de Açúcar</t>
+  </si>
+  <si>
+    <t>R$  95,17</t>
+  </si>
+  <si>
+    <t>material limpeza</t>
+  </si>
+  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2085,6 +2085,48 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>64/1</t>
+  </si>
+  <si>
+    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  146,67</t>
+  </si>
+  <si>
+    <t>ISO Implantação -Saude ocupacional</t>
+  </si>
+  <si>
+    <t>63/1</t>
+  </si>
+  <si>
+    <t>R$  376,38</t>
+  </si>
+  <si>
+    <t>Promob 2026/4</t>
+  </si>
+  <si>
+    <t>62/1</t>
+  </si>
+  <si>
+    <t>R$  293,11</t>
+  </si>
+  <si>
+    <t>Promob 2026/3</t>
+  </si>
+  <si>
+    <t>3/5</t>
+  </si>
+  <si>
+    <t>R$  1.248,76</t>
+  </si>
+  <si>
+    <t>13/02/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/2</t>
+  </si>
+  <si>
     <t>D4 sign</t>
   </si>
   <si>
@@ -2094,64 +2136,22 @@
     <t>D4 sign 2026</t>
   </si>
   <si>
-    <t>64/1</t>
-  </si>
-  <si>
-    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  146,67</t>
-  </si>
-  <si>
-    <t>ISO Implantação -Saude ocupacional</t>
-  </si>
-  <si>
-    <t>63/1</t>
-  </si>
-  <si>
-    <t>R$  376,38</t>
-  </si>
-  <si>
-    <t>Promob 2026/4</t>
-  </si>
-  <si>
-    <t>62/1</t>
-  </si>
-  <si>
-    <t>R$  293,11</t>
-  </si>
-  <si>
-    <t>Promob 2026/3</t>
-  </si>
-  <si>
-    <t>3/5</t>
-  </si>
-  <si>
-    <t>R$  1.248,76</t>
-  </si>
-  <si>
-    <t>13/02/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/2</t>
+    <t>61/2</t>
+  </si>
+  <si>
+    <t>Pipefy</t>
+  </si>
+  <si>
+    <t>R$  95,96</t>
+  </si>
+  <si>
+    <t>21/05/26</t>
   </si>
   <si>
     <t>R$  599,00</t>
   </si>
   <si>
     <t>Promob 2026</t>
-  </si>
-  <si>
-    <t>61/2</t>
-  </si>
-  <si>
-    <t>Pipefy</t>
-  </si>
-  <si>
-    <t>R$  95,96</t>
-  </si>
-  <si>
-    <t>21/05/26</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -4514,25 +4514,25 @@
         <v>144</v>
       </c>
       <c r="F46" t="s">
+        <v>48</v>
+      </c>
+      <c r="G46" t="s">
+        <v>41</v>
+      </c>
+      <c r="H46" t="s">
         <v>145</v>
       </c>
-      <c r="G46" t="s">
-        <v>41</v>
-      </c>
-      <c r="H46" t="s">
+      <c r="I46" t="s">
         <v>146</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>147</v>
       </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
+        <v>91</v>
+      </c>
+      <c r="L46" t="s">
         <v>148</v>
-      </c>
-      <c r="K46" t="s">
-        <v>57</v>
-      </c>
-      <c r="L46" t="s">
-        <v>34</v>
       </c>
       <c r="M46" t="s">
         <v>133</v>
@@ -4544,7 +4544,7 @@
         <v>140</v>
       </c>
       <c r="P46" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q46" t="s">
         <v>45</v>
@@ -4570,25 +4570,25 @@
         <v>149</v>
       </c>
       <c r="F47" t="s">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="G47" t="s">
         <v>41</v>
       </c>
       <c r="H47" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J47" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K47" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="L47" t="s">
-        <v>153</v>
+        <v>34</v>
       </c>
       <c r="M47" t="s">
         <v>133</v>
@@ -4600,7 +4600,7 @@
         <v>140</v>
       </c>
       <c r="P47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q47" t="s">
         <v>45</v>
@@ -4847,7 +4847,7 @@
         <v>33</v>
       </c>
       <c r="E52" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F52" t="s">
         <v>162</v>
@@ -5186,7 +5186,7 @@
         <v>190</v>
       </c>
       <c r="F58" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G58" t="s">
         <v>41</v>
@@ -5522,13 +5522,13 @@
         <v>205</v>
       </c>
       <c r="F64" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G64" t="s">
         <v>41</v>
       </c>
       <c r="H64" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I64" t="s">
         <v>206</v>
@@ -5578,7 +5578,7 @@
         <v>62</v>
       </c>
       <c r="F65" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G65" t="s">
         <v>41</v>
@@ -5634,13 +5634,13 @@
         <v>210</v>
       </c>
       <c r="F66" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G66" t="s">
         <v>41</v>
       </c>
       <c r="H66" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I66" t="s">
         <v>206</v>
@@ -6026,25 +6026,25 @@
         <v>227</v>
       </c>
       <c r="F73" t="s">
-        <v>48</v>
+        <v>228</v>
       </c>
       <c r="G73" t="s">
         <v>41</v>
       </c>
       <c r="H73" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="I73" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J73" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="K73" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="L73" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="M73" t="s">
         <v>225</v>
@@ -6082,25 +6082,25 @@
         <v>230</v>
       </c>
       <c r="F74" t="s">
+        <v>48</v>
+      </c>
+      <c r="G74" t="s">
+        <v>41</v>
+      </c>
+      <c r="H74" t="s">
+        <v>203</v>
+      </c>
+      <c r="I74" t="s">
         <v>231</v>
       </c>
-      <c r="G74" t="s">
-        <v>41</v>
-      </c>
-      <c r="H74" t="s">
-        <v>188</v>
-      </c>
-      <c r="I74" t="s">
+      <c r="J74" t="s">
+        <v>138</v>
+      </c>
+      <c r="K74" t="s">
+        <v>138</v>
+      </c>
+      <c r="L74" t="s">
         <v>232</v>
-      </c>
-      <c r="J74" t="s">
-        <v>87</v>
-      </c>
-      <c r="K74" t="s">
-        <v>87</v>
-      </c>
-      <c r="L74" t="s">
-        <v>215</v>
       </c>
       <c r="M74" t="s">
         <v>225</v>
@@ -6138,22 +6138,22 @@
         <v>235</v>
       </c>
       <c r="F75" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G75" t="s">
         <v>41</v>
       </c>
       <c r="H75" t="s">
-        <v>146</v>
+        <v>236</v>
       </c>
       <c r="I75" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J75" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K75" t="s">
-        <v>51</v>
+        <v>177</v>
       </c>
       <c r="L75" t="s">
         <v>34</v>
@@ -6168,7 +6168,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q75" t="s">
         <v>45</v>
@@ -6191,28 +6191,28 @@
         <v>34</v>
       </c>
       <c r="E76" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F76" t="s">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="G76" t="s">
         <v>41</v>
       </c>
       <c r="H76" t="s">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="I76" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J76" t="s">
-        <v>177</v>
+        <v>242</v>
       </c>
       <c r="K76" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
       <c r="L76" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="M76" t="s">
         <v>233</v>
@@ -6224,7 +6224,7 @@
         <v>140</v>
       </c>
       <c r="P76" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q76" t="s">
         <v>45</v>
@@ -6247,28 +6247,28 @@
         <v>34</v>
       </c>
       <c r="E77" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F77" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G77" t="s">
         <v>41</v>
       </c>
       <c r="H77" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="I77" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J77" t="s">
-        <v>237</v>
+        <v>129</v>
       </c>
       <c r="K77" t="s">
-        <v>177</v>
+        <v>246</v>
       </c>
       <c r="L77" t="s">
-        <v>244</v>
+        <v>34</v>
       </c>
       <c r="M77" t="s">
         <v>233</v>
@@ -6280,7 +6280,7 @@
         <v>140</v>
       </c>
       <c r="P77" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q77" t="s">
         <v>45</v>
@@ -6303,28 +6303,28 @@
         <v>34</v>
       </c>
       <c r="E78" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F78" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G78" t="s">
         <v>41</v>
       </c>
       <c r="H78" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="I78" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J78" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K78" t="s">
-        <v>177</v>
+        <v>51</v>
       </c>
       <c r="L78" t="s">
-        <v>34</v>
+        <v>250</v>
       </c>
       <c r="M78" t="s">
         <v>233</v>
@@ -6336,7 +6336,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q78" t="s">
         <v>45</v>
@@ -6359,28 +6359,28 @@
         <v>34</v>
       </c>
       <c r="E79" t="s">
+        <v>251</v>
+      </c>
+      <c r="F79" t="s">
+        <v>150</v>
+      </c>
+      <c r="G79" t="s">
+        <v>41</v>
+      </c>
+      <c r="H79" t="s">
+        <v>151</v>
+      </c>
+      <c r="I79" t="s">
+        <v>252</v>
+      </c>
+      <c r="J79" t="s">
         <v>249</v>
-      </c>
-      <c r="F79" t="s">
-        <v>145</v>
-      </c>
-      <c r="G79" t="s">
-        <v>41</v>
-      </c>
-      <c r="H79" t="s">
-        <v>242</v>
-      </c>
-      <c r="I79" t="s">
-        <v>250</v>
-      </c>
-      <c r="J79" t="s">
-        <v>237</v>
       </c>
       <c r="K79" t="s">
         <v>51</v>
       </c>
       <c r="L79" t="s">
-        <v>251</v>
+        <v>34</v>
       </c>
       <c r="M79" t="s">
         <v>233</v>
@@ -6392,7 +6392,7 @@
         <v>140</v>
       </c>
       <c r="P79" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q79" t="s">
         <v>45</v>
@@ -6415,25 +6415,25 @@
         <v>34</v>
       </c>
       <c r="E80" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F80" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G80" t="s">
         <v>41</v>
       </c>
       <c r="H80" t="s">
-        <v>246</v>
+        <v>151</v>
       </c>
       <c r="I80" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J80" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="K80" t="s">
-        <v>254</v>
+        <v>138</v>
       </c>
       <c r="L80" t="s">
         <v>34</v>
@@ -6448,7 +6448,7 @@
         <v>140</v>
       </c>
       <c r="P80" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q80" t="s">
         <v>45</v>
@@ -6474,13 +6474,13 @@
         <v>255</v>
       </c>
       <c r="F81" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G81" t="s">
         <v>41</v>
       </c>
       <c r="H81" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="I81" t="s">
         <v>256</v>
@@ -6489,7 +6489,7 @@
         <v>257</v>
       </c>
       <c r="K81" t="s">
-        <v>44</v>
+        <v>246</v>
       </c>
       <c r="L81" t="s">
         <v>258</v>
@@ -6530,7 +6530,7 @@
         <v>259</v>
       </c>
       <c r="F82" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G82" t="s">
         <v>41</v>
@@ -6586,25 +6586,25 @@
         <v>264</v>
       </c>
       <c r="F83" t="s">
+        <v>48</v>
+      </c>
+      <c r="G83" t="s">
+        <v>41</v>
+      </c>
+      <c r="H83" t="s">
         <v>145</v>
-      </c>
-      <c r="G83" t="s">
-        <v>41</v>
-      </c>
-      <c r="H83" t="s">
-        <v>146</v>
       </c>
       <c r="I83" t="s">
         <v>265</v>
       </c>
       <c r="J83" t="s">
-        <v>117</v>
+        <v>177</v>
       </c>
       <c r="K83" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="L83" t="s">
-        <v>34</v>
+        <v>266</v>
       </c>
       <c r="M83" t="s">
         <v>233</v>
@@ -6639,25 +6639,25 @@
         <v>34</v>
       </c>
       <c r="E84" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F84" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G84" t="s">
         <v>41</v>
       </c>
       <c r="H84" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="I84" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J84" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="K84" t="s">
-        <v>254</v>
+        <v>177</v>
       </c>
       <c r="L84" t="s">
         <v>269</v>
@@ -6672,7 +6672,7 @@
         <v>140</v>
       </c>
       <c r="P84" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q84" t="s">
         <v>45</v>
@@ -7034,7 +7034,7 @@
         <v>284</v>
       </c>
       <c r="F91" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="G91" t="s">
         <v>41</v>
@@ -7046,13 +7046,13 @@
         <v>285</v>
       </c>
       <c r="J91" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="K91" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="L91" t="s">
-        <v>276</v>
+        <v>34</v>
       </c>
       <c r="M91" t="s">
         <v>273</v>
@@ -7061,7 +7061,7 @@
         <v>45</v>
       </c>
       <c r="O91" t="s">
-        <v>66</v>
+        <v>286</v>
       </c>
       <c r="P91" t="s">
         <v>285</v>
@@ -7087,7 +7087,7 @@
         <v>34</v>
       </c>
       <c r="E92" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F92" t="s">
         <v>187</v>
@@ -7096,16 +7096,16 @@
         <v>41</v>
       </c>
       <c r="H92" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="I92" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J92" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="K92" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="L92" t="s">
         <v>276</v>
@@ -7117,10 +7117,10 @@
         <v>45</v>
       </c>
       <c r="O92" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="P92" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q92" t="s">
         <v>45</v>
@@ -7143,7 +7143,7 @@
         <v>34</v>
       </c>
       <c r="E93" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F93" t="s">
         <v>187</v>
@@ -7152,10 +7152,10 @@
         <v>41</v>
       </c>
       <c r="H93" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="I93" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J93" t="s">
         <v>44</v>
@@ -7176,7 +7176,7 @@
         <v>46</v>
       </c>
       <c r="P93" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q93" t="s">
         <v>45</v>
@@ -7199,7 +7199,7 @@
         <v>34</v>
       </c>
       <c r="E94" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F94" t="s">
         <v>187</v>
@@ -7211,13 +7211,13 @@
         <v>274</v>
       </c>
       <c r="I94" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J94" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="K94" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L94" t="s">
         <v>276</v>
@@ -7229,10 +7229,10 @@
         <v>45</v>
       </c>
       <c r="O94" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="P94" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q94" t="s">
         <v>45</v>
@@ -7255,7 +7255,7 @@
         <v>34</v>
       </c>
       <c r="E95" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F95" t="s">
         <v>187</v>
@@ -7264,10 +7264,10 @@
         <v>41</v>
       </c>
       <c r="H95" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="I95" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J95" t="s">
         <v>52</v>
@@ -7288,7 +7288,7 @@
         <v>61</v>
       </c>
       <c r="P95" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q95" t="s">
         <v>45</v>
@@ -7311,7 +7311,7 @@
         <v>34</v>
       </c>
       <c r="E96" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F96" t="s">
         <v>187</v>
@@ -7323,13 +7323,13 @@
         <v>278</v>
       </c>
       <c r="I96" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J96" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="K96" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="L96" t="s">
         <v>276</v>
@@ -7341,10 +7341,10 @@
         <v>45</v>
       </c>
       <c r="O96" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="P96" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q96" t="s">
         <v>45</v>
@@ -7367,7 +7367,7 @@
         <v>34</v>
       </c>
       <c r="E97" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F97" t="s">
         <v>187</v>
@@ -7379,13 +7379,13 @@
         <v>278</v>
       </c>
       <c r="I97" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J97" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="K97" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="L97" t="s">
         <v>276</v>
@@ -7397,10 +7397,10 @@
         <v>45</v>
       </c>
       <c r="O97" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="P97" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q97" t="s">
         <v>45</v>
@@ -7423,7 +7423,7 @@
         <v>34</v>
       </c>
       <c r="E98" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F98" t="s">
         <v>187</v>
@@ -7432,10 +7432,10 @@
         <v>41</v>
       </c>
       <c r="H98" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="I98" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J98" t="s">
         <v>98</v>
@@ -7456,7 +7456,7 @@
         <v>99</v>
       </c>
       <c r="P98" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q98" t="s">
         <v>45</v>
@@ -7479,7 +7479,7 @@
         <v>34</v>
       </c>
       <c r="E99" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F99" t="s">
         <v>187</v>
@@ -7488,16 +7488,16 @@
         <v>41</v>
       </c>
       <c r="H99" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="I99" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J99" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="K99" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="L99" t="s">
         <v>276</v>
@@ -7509,10 +7509,10 @@
         <v>45</v>
       </c>
       <c r="O99" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="P99" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q99" t="s">
         <v>45</v>
@@ -7535,7 +7535,7 @@
         <v>34</v>
       </c>
       <c r="E100" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F100" t="s">
         <v>187</v>
@@ -7547,13 +7547,13 @@
         <v>278</v>
       </c>
       <c r="I100" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J100" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K100" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L100" t="s">
         <v>276</v>
@@ -7565,10 +7565,10 @@
         <v>45</v>
       </c>
       <c r="O100" t="s">
+        <v>81</v>
+      </c>
+      <c r="P100" t="s">
         <v>304</v>
-      </c>
-      <c r="P100" t="s">
-        <v>303</v>
       </c>
       <c r="Q100" t="s">
         <v>45</v>
@@ -7591,28 +7591,28 @@
         <v>34</v>
       </c>
       <c r="E101" t="s">
+        <v>39</v>
+      </c>
+      <c r="F101" t="s">
+        <v>150</v>
+      </c>
+      <c r="G101" t="s">
+        <v>41</v>
+      </c>
+      <c r="H101" t="s">
+        <v>274</v>
+      </c>
+      <c r="I101" t="s">
         <v>305</v>
       </c>
-      <c r="F101" t="s">
-        <v>187</v>
-      </c>
-      <c r="G101" t="s">
-        <v>41</v>
-      </c>
-      <c r="H101" t="s">
-        <v>278</v>
-      </c>
-      <c r="I101" t="s">
-        <v>306</v>
-      </c>
       <c r="J101" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="K101" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="L101" t="s">
-        <v>276</v>
+        <v>34</v>
       </c>
       <c r="M101" t="s">
         <v>273</v>
@@ -7621,10 +7621,10 @@
         <v>45</v>
       </c>
       <c r="O101" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="P101" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q101" t="s">
         <v>45</v>
@@ -7647,7 +7647,7 @@
         <v>34</v>
       </c>
       <c r="E102" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F102" t="s">
         <v>187</v>
@@ -7656,16 +7656,16 @@
         <v>41</v>
       </c>
       <c r="H102" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="I102" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J102" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="K102" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="L102" t="s">
         <v>276</v>
@@ -7677,10 +7677,10 @@
         <v>45</v>
       </c>
       <c r="O102" t="s">
-        <v>81</v>
+        <v>308</v>
       </c>
       <c r="P102" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q102" t="s">
         <v>45</v>
@@ -7712,7 +7712,7 @@
         <v>41</v>
       </c>
       <c r="H103" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="I103" t="s">
         <v>310</v>
@@ -7774,10 +7774,10 @@
         <v>312</v>
       </c>
       <c r="J104" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K104" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L104" t="s">
         <v>276</v>
@@ -7789,7 +7789,7 @@
         <v>45</v>
       </c>
       <c r="O104" t="s">
-        <v>313</v>
+        <v>81</v>
       </c>
       <c r="P104" t="s">
         <v>312</v>
@@ -7815,7 +7815,7 @@
         <v>34</v>
       </c>
       <c r="E105" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F105" t="s">
         <v>187</v>
@@ -7824,16 +7824,16 @@
         <v>41</v>
       </c>
       <c r="H105" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="I105" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J105" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="K105" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="L105" t="s">
         <v>276</v>
@@ -7845,10 +7845,10 @@
         <v>45</v>
       </c>
       <c r="O105" t="s">
-        <v>58</v>
+        <v>121</v>
       </c>
       <c r="P105" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q105" t="s">
         <v>45</v>
@@ -7871,7 +7871,7 @@
         <v>34</v>
       </c>
       <c r="E106" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F106" t="s">
         <v>187</v>
@@ -7883,13 +7883,13 @@
         <v>274</v>
       </c>
       <c r="I106" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J106" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="K106" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="L106" t="s">
         <v>276</v>
@@ -7901,10 +7901,10 @@
         <v>45</v>
       </c>
       <c r="O106" t="s">
-        <v>58</v>
+        <v>317</v>
       </c>
       <c r="P106" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q106" t="s">
         <v>45</v>
@@ -7930,25 +7930,25 @@
         <v>318</v>
       </c>
       <c r="F107" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G107" t="s">
         <v>41</v>
       </c>
       <c r="H107" t="s">
-        <v>274</v>
+        <v>151</v>
       </c>
       <c r="I107" t="s">
+        <v>206</v>
+      </c>
+      <c r="J107" t="s">
+        <v>44</v>
+      </c>
+      <c r="K107" t="s">
+        <v>44</v>
+      </c>
+      <c r="L107" t="s">
         <v>319</v>
-      </c>
-      <c r="J107" t="s">
-        <v>57</v>
-      </c>
-      <c r="K107" t="s">
-        <v>57</v>
-      </c>
-      <c r="L107" t="s">
-        <v>34</v>
       </c>
       <c r="M107" t="s">
         <v>273</v>
@@ -7957,10 +7957,10 @@
         <v>45</v>
       </c>
       <c r="O107" t="s">
-        <v>320</v>
+        <v>207</v>
       </c>
       <c r="P107" t="s">
-        <v>319</v>
+        <v>206</v>
       </c>
       <c r="Q107" t="s">
         <v>45</v>
@@ -7983,28 +7983,28 @@
         <v>34</v>
       </c>
       <c r="E108" t="s">
-        <v>39</v>
+        <v>320</v>
       </c>
       <c r="F108" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="G108" t="s">
         <v>41</v>
       </c>
       <c r="H108" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="I108" t="s">
         <v>321</v>
       </c>
       <c r="J108" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="K108" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="L108" t="s">
-        <v>34</v>
+        <v>276</v>
       </c>
       <c r="M108" t="s">
         <v>273</v>
@@ -8013,7 +8013,7 @@
         <v>45</v>
       </c>
       <c r="O108" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="P108" t="s">
         <v>321</v>
@@ -8042,25 +8042,25 @@
         <v>322</v>
       </c>
       <c r="F109" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="G109" t="s">
         <v>41</v>
       </c>
       <c r="H109" t="s">
-        <v>146</v>
+        <v>274</v>
       </c>
       <c r="I109" t="s">
-        <v>206</v>
+        <v>323</v>
       </c>
       <c r="J109" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="K109" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="L109" t="s">
-        <v>323</v>
+        <v>276</v>
       </c>
       <c r="M109" t="s">
         <v>273</v>
@@ -8069,10 +8069,10 @@
         <v>45</v>
       </c>
       <c r="O109" t="s">
-        <v>207</v>
+        <v>58</v>
       </c>
       <c r="P109" t="s">
-        <v>206</v>
+        <v>323</v>
       </c>
       <c r="Q109" t="s">
         <v>45</v>
@@ -8098,7 +8098,7 @@
         <v>95</v>
       </c>
       <c r="F110" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G110" t="s">
         <v>41</v>
@@ -8154,7 +8154,7 @@
         <v>62</v>
       </c>
       <c r="F111" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G111" t="s">
         <v>41</v>
@@ -8163,7 +8163,7 @@
         <v>274</v>
       </c>
       <c r="I111" t="s">
-        <v>319</v>
+        <v>285</v>
       </c>
       <c r="J111" t="s">
         <v>65</v>
@@ -8184,7 +8184,7 @@
         <v>66</v>
       </c>
       <c r="P111" t="s">
-        <v>319</v>
+        <v>285</v>
       </c>
       <c r="Q111" t="s">
         <v>45</v>
@@ -8431,7 +8431,7 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="F116" t="s">
         <v>187</v>
@@ -8449,7 +8449,7 @@
         <v>103</v>
       </c>
       <c r="K116" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="L116" t="s">
         <v>34</v>
@@ -8461,7 +8461,7 @@
         <v>45</v>
       </c>
       <c r="O116" t="s">
-        <v>92</v>
+        <v>308</v>
       </c>
       <c r="P116" t="s">
         <v>334</v>
@@ -8487,7 +8487,7 @@
         <v>34</v>
       </c>
       <c r="E117" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F117" t="s">
         <v>187</v>
@@ -8517,7 +8517,7 @@
         <v>45</v>
       </c>
       <c r="O117" t="s">
-        <v>304</v>
+        <v>99</v>
       </c>
       <c r="P117" t="s">
         <v>335</v>
@@ -8543,7 +8543,7 @@
         <v>34</v>
       </c>
       <c r="E118" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F118" t="s">
         <v>187</v>
@@ -8573,7 +8573,7 @@
         <v>45</v>
       </c>
       <c r="O118" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="P118" t="s">
         <v>336</v>
@@ -8599,7 +8599,7 @@
         <v>34</v>
       </c>
       <c r="E119" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="F119" t="s">
         <v>187</v>
@@ -8617,7 +8617,7 @@
         <v>103</v>
       </c>
       <c r="K119" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="L119" t="s">
         <v>34</v>
@@ -8629,7 +8629,7 @@
         <v>45</v>
       </c>
       <c r="O119" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="P119" t="s">
         <v>337</v>
@@ -8655,7 +8655,7 @@
         <v>34</v>
       </c>
       <c r="E120" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="F120" t="s">
         <v>187</v>
@@ -8673,7 +8673,7 @@
         <v>103</v>
       </c>
       <c r="K120" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="L120" t="s">
         <v>34</v>
@@ -8685,7 +8685,7 @@
         <v>45</v>
       </c>
       <c r="O120" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="P120" t="s">
         <v>338</v>
@@ -8711,7 +8711,7 @@
         <v>34</v>
       </c>
       <c r="E121" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="F121" t="s">
         <v>187</v>
@@ -8729,7 +8729,7 @@
         <v>103</v>
       </c>
       <c r="K121" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="L121" t="s">
         <v>34</v>
@@ -8741,7 +8741,7 @@
         <v>45</v>
       </c>
       <c r="O121" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="P121" t="s">
         <v>339</v>
@@ -8767,7 +8767,7 @@
         <v>34</v>
       </c>
       <c r="E122" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F122" t="s">
         <v>187</v>
@@ -8785,7 +8785,7 @@
         <v>103</v>
       </c>
       <c r="K122" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="L122" t="s">
         <v>34</v>
@@ -8797,7 +8797,7 @@
         <v>45</v>
       </c>
       <c r="O122" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="P122" t="s">
         <v>340</v>
@@ -8823,7 +8823,7 @@
         <v>34</v>
       </c>
       <c r="E123" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F123" t="s">
         <v>187</v>
@@ -8841,7 +8841,7 @@
         <v>103</v>
       </c>
       <c r="K123" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="L123" t="s">
         <v>34</v>
@@ -8853,7 +8853,7 @@
         <v>45</v>
       </c>
       <c r="O123" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="P123" t="s">
         <v>341</v>
@@ -8879,7 +8879,7 @@
         <v>34</v>
       </c>
       <c r="E124" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F124" t="s">
         <v>187</v>
@@ -8897,7 +8897,7 @@
         <v>103</v>
       </c>
       <c r="K124" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L124" t="s">
         <v>34</v>
@@ -8909,7 +8909,7 @@
         <v>45</v>
       </c>
       <c r="O124" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="P124" t="s">
         <v>342</v>
@@ -8935,7 +8935,7 @@
         <v>34</v>
       </c>
       <c r="E125" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F125" t="s">
         <v>187</v>
@@ -8953,7 +8953,7 @@
         <v>103</v>
       </c>
       <c r="K125" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="L125" t="s">
         <v>34</v>
@@ -8965,7 +8965,7 @@
         <v>45</v>
       </c>
       <c r="O125" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="P125" t="s">
         <v>343</v>
@@ -9077,7 +9077,7 @@
         <v>45</v>
       </c>
       <c r="O127" t="s">
-        <v>320</v>
+        <v>286</v>
       </c>
       <c r="P127" t="s">
         <v>349</v>
@@ -10253,7 +10253,7 @@
         <v>45</v>
       </c>
       <c r="O148" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="P148" t="s">
         <v>375</v>
@@ -10365,7 +10365,7 @@
         <v>45</v>
       </c>
       <c r="O150" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="P150" t="s">
         <v>377</v>
@@ -10403,7 +10403,7 @@
         <v>378</v>
       </c>
       <c r="I151" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="J151" t="s">
         <v>103</v>
@@ -10424,7 +10424,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="Q151" t="s">
         <v>45</v>
@@ -10515,7 +10515,7 @@
         <v>378</v>
       </c>
       <c r="I153" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J153" t="s">
         <v>103</v>
@@ -10536,7 +10536,7 @@
         <v>61</v>
       </c>
       <c r="P153" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q153" t="s">
         <v>45</v>
@@ -10571,7 +10571,7 @@
         <v>378</v>
       </c>
       <c r="I154" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J154" t="s">
         <v>103</v>
@@ -10592,7 +10592,7 @@
         <v>46</v>
       </c>
       <c r="P154" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q154" t="s">
         <v>45</v>
@@ -10627,7 +10627,7 @@
         <v>378</v>
       </c>
       <c r="I155" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J155" t="s">
         <v>103</v>
@@ -10648,7 +10648,7 @@
         <v>66</v>
       </c>
       <c r="P155" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q155" t="s">
         <v>45</v>
@@ -10683,7 +10683,7 @@
         <v>378</v>
       </c>
       <c r="I156" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J156" t="s">
         <v>103</v>
@@ -10704,7 +10704,7 @@
         <v>118</v>
       </c>
       <c r="P156" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q156" t="s">
         <v>45</v>
@@ -10739,7 +10739,7 @@
         <v>378</v>
       </c>
       <c r="I157" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J157" t="s">
         <v>103</v>
@@ -10760,7 +10760,7 @@
         <v>58</v>
       </c>
       <c r="P157" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q157" t="s">
         <v>45</v>
@@ -10795,7 +10795,7 @@
         <v>378</v>
       </c>
       <c r="I158" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J158" t="s">
         <v>103</v>
@@ -10816,7 +10816,7 @@
         <v>81</v>
       </c>
       <c r="P158" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q158" t="s">
         <v>45</v>
@@ -10851,7 +10851,7 @@
         <v>378</v>
       </c>
       <c r="I159" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J159" t="s">
         <v>103</v>
@@ -10872,7 +10872,7 @@
         <v>99</v>
       </c>
       <c r="P159" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q159" t="s">
         <v>45</v>
@@ -10925,7 +10925,7 @@
         <v>45</v>
       </c>
       <c r="O160" t="s">
-        <v>320</v>
+        <v>286</v>
       </c>
       <c r="P160" t="s">
         <v>380</v>
@@ -10963,7 +10963,7 @@
         <v>378</v>
       </c>
       <c r="I161" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J161" t="s">
         <v>103</v>
@@ -10981,10 +10981,10 @@
         <v>45</v>
       </c>
       <c r="O161" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="P161" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q161" t="s">
         <v>45</v>
@@ -11075,7 +11075,7 @@
         <v>378</v>
       </c>
       <c r="I163" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J163" t="s">
         <v>103</v>
@@ -11096,7 +11096,7 @@
         <v>121</v>
       </c>
       <c r="P163" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q163" t="s">
         <v>45</v>
@@ -11205,7 +11205,7 @@
         <v>45</v>
       </c>
       <c r="O165" t="s">
-        <v>320</v>
+        <v>286</v>
       </c>
       <c r="P165" t="s">
         <v>384</v>
@@ -11511,7 +11511,7 @@
         <v>33</v>
       </c>
       <c r="E171" t="s">
-        <v>347</v>
+        <v>195</v>
       </c>
       <c r="F171" t="s">
         <v>187</v>
@@ -11523,13 +11523,13 @@
         <v>391</v>
       </c>
       <c r="I171" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="J171" t="s">
         <v>103</v>
       </c>
       <c r="K171" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L171" t="s">
         <v>34</v>
@@ -11541,10 +11541,10 @@
         <v>45</v>
       </c>
       <c r="O171" t="s">
-        <v>320</v>
+        <v>61</v>
       </c>
       <c r="P171" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="Q171" t="s">
         <v>45</v>
@@ -11567,25 +11567,25 @@
         <v>34</v>
       </c>
       <c r="E172" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="F172" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="G172" t="s">
         <v>41</v>
       </c>
       <c r="H172" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="I172" t="s">
-        <v>398</v>
+        <v>334</v>
       </c>
       <c r="J172" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="K172" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L172" t="s">
         <v>34</v>
@@ -11597,10 +11597,10 @@
         <v>45</v>
       </c>
       <c r="O172" t="s">
-        <v>61</v>
+        <v>308</v>
       </c>
       <c r="P172" t="s">
-        <v>398</v>
+        <v>334</v>
       </c>
       <c r="Q172" t="s">
         <v>45</v>
@@ -11635,7 +11635,7 @@
         <v>388</v>
       </c>
       <c r="I173" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J173" t="s">
         <v>390</v>
@@ -11656,7 +11656,7 @@
         <v>66</v>
       </c>
       <c r="P173" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q173" t="s">
         <v>45</v>
@@ -11679,7 +11679,7 @@
         <v>34</v>
       </c>
       <c r="E174" t="s">
-        <v>107</v>
+        <v>400</v>
       </c>
       <c r="F174" t="s">
         <v>187</v>
@@ -11688,16 +11688,16 @@
         <v>41</v>
       </c>
       <c r="H174" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="I174" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="J174" t="s">
         <v>103</v>
       </c>
       <c r="K174" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="L174" t="s">
         <v>34</v>
@@ -11709,10 +11709,10 @@
         <v>45</v>
       </c>
       <c r="O174" t="s">
-        <v>111</v>
+        <v>402</v>
       </c>
       <c r="P174" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="Q174" t="s">
         <v>45</v>
@@ -11735,10 +11735,10 @@
         <v>34</v>
       </c>
       <c r="E175" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="F175" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G175" t="s">
         <v>41</v>
@@ -11747,13 +11747,13 @@
         <v>203</v>
       </c>
       <c r="I175" t="s">
-        <v>401</v>
+        <v>379</v>
       </c>
       <c r="J175" t="s">
-        <v>402</v>
+        <v>104</v>
       </c>
       <c r="K175" t="s">
-        <v>402</v>
+        <v>104</v>
       </c>
       <c r="L175" t="s">
         <v>34</v>
@@ -11791,25 +11791,25 @@
         <v>34</v>
       </c>
       <c r="E176" t="s">
-        <v>280</v>
+        <v>107</v>
       </c>
       <c r="F176" t="s">
-        <v>400</v>
+        <v>187</v>
       </c>
       <c r="G176" t="s">
         <v>41</v>
       </c>
       <c r="H176" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="I176" t="s">
-        <v>404</v>
+        <v>381</v>
       </c>
       <c r="J176" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="K176" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="L176" t="s">
         <v>34</v>
@@ -11821,13 +11821,13 @@
         <v>45</v>
       </c>
       <c r="O176" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="P176" t="s">
-        <v>34</v>
+        <v>381</v>
       </c>
       <c r="Q176" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R176" t="s">
         <v>34</v>
@@ -11850,22 +11850,22 @@
         <v>405</v>
       </c>
       <c r="F177" t="s">
-        <v>187</v>
+        <v>404</v>
       </c>
       <c r="G177" t="s">
         <v>41</v>
       </c>
       <c r="H177" t="s">
-        <v>391</v>
+        <v>203</v>
       </c>
       <c r="I177" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="J177" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="K177" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="L177" t="s">
         <v>34</v>
@@ -11877,13 +11877,13 @@
         <v>45</v>
       </c>
       <c r="O177" t="s">
-        <v>406</v>
+        <v>34</v>
       </c>
       <c r="P177" t="s">
-        <v>401</v>
+        <v>34</v>
       </c>
       <c r="Q177" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R177" t="s">
         <v>34</v>
@@ -11903,25 +11903,25 @@
         <v>34</v>
       </c>
       <c r="E178" t="s">
+        <v>186</v>
+      </c>
+      <c r="F178" t="s">
+        <v>187</v>
+      </c>
+      <c r="G178" t="s">
+        <v>41</v>
+      </c>
+      <c r="H178" t="s">
         <v>407</v>
       </c>
-      <c r="F178" t="s">
-        <v>400</v>
-      </c>
-      <c r="G178" t="s">
-        <v>41</v>
-      </c>
-      <c r="H178" t="s">
-        <v>203</v>
-      </c>
       <c r="I178" t="s">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="J178" t="s">
-        <v>104</v>
+        <v>390</v>
       </c>
       <c r="K178" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="L178" t="s">
         <v>34</v>
@@ -11933,13 +11933,13 @@
         <v>45</v>
       </c>
       <c r="O178" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="P178" t="s">
-        <v>34</v>
+        <v>408</v>
       </c>
       <c r="Q178" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R178" t="s">
         <v>34</v>
@@ -11959,10 +11959,10 @@
         <v>34</v>
       </c>
       <c r="E179" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F179" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G179" t="s">
         <v>41</v>
@@ -11971,13 +11971,13 @@
         <v>203</v>
       </c>
       <c r="I179" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="J179" t="s">
-        <v>75</v>
+        <v>410</v>
       </c>
       <c r="K179" t="s">
-        <v>75</v>
+        <v>410</v>
       </c>
       <c r="L179" t="s">
         <v>34</v>
@@ -12015,25 +12015,25 @@
         <v>34</v>
       </c>
       <c r="E180" t="s">
-        <v>186</v>
+        <v>280</v>
       </c>
       <c r="F180" t="s">
-        <v>187</v>
+        <v>404</v>
       </c>
       <c r="G180" t="s">
         <v>41</v>
       </c>
       <c r="H180" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="I180" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J180" t="s">
-        <v>390</v>
+        <v>117</v>
       </c>
       <c r="K180" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="L180" t="s">
         <v>34</v>
@@ -12045,13 +12045,13 @@
         <v>45</v>
       </c>
       <c r="O180" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="P180" t="s">
-        <v>410</v>
+        <v>34</v>
       </c>
       <c r="Q180" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R180" t="s">
         <v>34</v>
@@ -12071,25 +12071,25 @@
         <v>34</v>
       </c>
       <c r="E181" t="s">
-        <v>218</v>
+        <v>412</v>
       </c>
       <c r="F181" t="s">
-        <v>145</v>
+        <v>404</v>
       </c>
       <c r="G181" t="s">
         <v>41</v>
       </c>
       <c r="H181" t="s">
-        <v>411</v>
+        <v>203</v>
       </c>
       <c r="I181" t="s">
-        <v>335</v>
+        <v>380</v>
       </c>
       <c r="J181" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="K181" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="L181" t="s">
         <v>34</v>
@@ -12101,13 +12101,13 @@
         <v>45</v>
       </c>
       <c r="O181" t="s">
-        <v>304</v>
+        <v>34</v>
       </c>
       <c r="P181" t="s">
-        <v>335</v>
+        <v>34</v>
       </c>
       <c r="Q181" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R181" t="s">
         <v>34</v>
@@ -12127,25 +12127,25 @@
         <v>34</v>
       </c>
       <c r="E182" t="s">
-        <v>412</v>
+        <v>347</v>
       </c>
       <c r="F182" t="s">
-        <v>400</v>
+        <v>187</v>
       </c>
       <c r="G182" t="s">
         <v>41</v>
       </c>
       <c r="H182" t="s">
-        <v>203</v>
+        <v>391</v>
       </c>
       <c r="I182" t="s">
         <v>380</v>
       </c>
       <c r="J182" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="K182" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="L182" t="s">
         <v>34</v>
@@ -12157,13 +12157,13 @@
         <v>45</v>
       </c>
       <c r="O182" t="s">
-        <v>34</v>
+        <v>286</v>
       </c>
       <c r="P182" t="s">
-        <v>34</v>
+        <v>380</v>
       </c>
       <c r="Q182" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R182" t="s">
         <v>34</v>
@@ -12183,10 +12183,10 @@
         <v>33</v>
       </c>
       <c r="E183" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="F183" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G183" t="s">
         <v>41</v>
@@ -12198,10 +12198,10 @@
         <v>415</v>
       </c>
       <c r="J183" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="K183" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="L183" t="s">
         <v>34</v>
@@ -12242,7 +12242,7 @@
         <v>199</v>
       </c>
       <c r="F184" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G184" t="s">
         <v>41</v>
@@ -12298,7 +12298,7 @@
         <v>417</v>
       </c>
       <c r="F185" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G185" t="s">
         <v>41</v>
@@ -12354,7 +12354,7 @@
         <v>186</v>
       </c>
       <c r="F186" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G186" t="s">
         <v>41</v>
@@ -12410,7 +12410,7 @@
         <v>347</v>
       </c>
       <c r="F187" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G187" t="s">
         <v>41</v>
@@ -12466,7 +12466,7 @@
         <v>190</v>
       </c>
       <c r="F188" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G188" t="s">
         <v>41</v>
@@ -12522,7 +12522,7 @@
         <v>360</v>
       </c>
       <c r="F189" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G189" t="s">
         <v>41</v>
@@ -12578,7 +12578,7 @@
         <v>54</v>
       </c>
       <c r="F190" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G190" t="s">
         <v>41</v>
@@ -12634,7 +12634,7 @@
         <v>107</v>
       </c>
       <c r="F191" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G191" t="s">
         <v>41</v>
@@ -12690,7 +12690,7 @@
         <v>119</v>
       </c>
       <c r="F192" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G192" t="s">
         <v>41</v>
@@ -12746,7 +12746,7 @@
         <v>95</v>
       </c>
       <c r="F193" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G193" t="s">
         <v>41</v>
@@ -12802,7 +12802,7 @@
         <v>430</v>
       </c>
       <c r="F194" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G194" t="s">
         <v>41</v>
@@ -12829,7 +12829,7 @@
         <v>45</v>
       </c>
       <c r="O194" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="P194" t="s">
         <v>432</v>
@@ -12858,7 +12858,7 @@
         <v>59</v>
       </c>
       <c r="F195" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G195" t="s">
         <v>41</v>
@@ -12870,7 +12870,7 @@
         <v>433</v>
       </c>
       <c r="J195" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="K195" t="s">
         <v>52</v>
@@ -12914,7 +12914,7 @@
         <v>62</v>
       </c>
       <c r="F196" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G196" t="s">
         <v>41</v>
@@ -12970,7 +12970,7 @@
         <v>88</v>
       </c>
       <c r="F197" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G197" t="s">
         <v>41</v>
@@ -13026,13 +13026,13 @@
         <v>438</v>
       </c>
       <c r="F198" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G198" t="s">
         <v>41</v>
       </c>
       <c r="H198" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="I198" t="s">
         <v>439</v>
@@ -13082,13 +13082,13 @@
         <v>438</v>
       </c>
       <c r="F199" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G199" t="s">
         <v>41</v>
       </c>
       <c r="H199" t="s">
-        <v>371</v>
+        <v>333</v>
       </c>
       <c r="I199" t="s">
         <v>440</v>
@@ -13250,7 +13250,7 @@
         <v>186</v>
       </c>
       <c r="F202" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G202" t="s">
         <v>41</v>
@@ -13418,7 +13418,7 @@
         <v>95</v>
       </c>
       <c r="F205" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G205" t="s">
         <v>41</v>
@@ -13474,7 +13474,7 @@
         <v>454</v>
       </c>
       <c r="F206" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G206" t="s">
         <v>41</v>
@@ -13530,7 +13530,7 @@
         <v>457</v>
       </c>
       <c r="F207" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G207" t="s">
         <v>41</v>
@@ -13586,7 +13586,7 @@
         <v>59</v>
       </c>
       <c r="F208" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G208" t="s">
         <v>41</v>
@@ -13642,7 +13642,7 @@
         <v>54</v>
       </c>
       <c r="F209" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G209" t="s">
         <v>41</v>
@@ -13698,7 +13698,7 @@
         <v>462</v>
       </c>
       <c r="F210" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G210" t="s">
         <v>41</v>
@@ -13754,7 +13754,7 @@
         <v>466</v>
       </c>
       <c r="F211" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G211" t="s">
         <v>41</v>
@@ -13810,7 +13810,7 @@
         <v>347</v>
       </c>
       <c r="F212" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G212" t="s">
         <v>41</v>
@@ -13837,7 +13837,7 @@
         <v>45</v>
       </c>
       <c r="O212" t="s">
-        <v>320</v>
+        <v>286</v>
       </c>
       <c r="P212" t="s">
         <v>470</v>
@@ -13866,7 +13866,7 @@
         <v>471</v>
       </c>
       <c r="F213" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G213" t="s">
         <v>41</v>
@@ -13922,7 +13922,7 @@
         <v>474</v>
       </c>
       <c r="F214" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G214" t="s">
         <v>41</v>
@@ -13978,7 +13978,7 @@
         <v>476</v>
       </c>
       <c r="F215" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G215" t="s">
         <v>41</v>
@@ -14034,7 +14034,7 @@
         <v>479</v>
       </c>
       <c r="F216" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G216" t="s">
         <v>41</v>
@@ -14090,7 +14090,7 @@
         <v>482</v>
       </c>
       <c r="F217" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G217" t="s">
         <v>41</v>
@@ -14146,7 +14146,7 @@
         <v>485</v>
       </c>
       <c r="F218" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G218" t="s">
         <v>41</v>
@@ -14202,7 +14202,7 @@
         <v>487</v>
       </c>
       <c r="F219" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G219" t="s">
         <v>41</v>
@@ -14258,7 +14258,7 @@
         <v>490</v>
       </c>
       <c r="F220" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G220" t="s">
         <v>41</v>
@@ -14314,7 +14314,7 @@
         <v>493</v>
       </c>
       <c r="F221" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G221" t="s">
         <v>41</v>
@@ -14479,7 +14479,7 @@
         <v>33</v>
       </c>
       <c r="E224" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="F224" t="s">
         <v>162</v>
@@ -14494,10 +14494,10 @@
         <v>501</v>
       </c>
       <c r="J224" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="K224" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="L224" t="s">
         <v>34</v>
@@ -14509,7 +14509,7 @@
         <v>45</v>
       </c>
       <c r="O224" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P224" t="s">
         <v>501</v>
@@ -14535,7 +14535,7 @@
         <v>34</v>
       </c>
       <c r="E225" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="F225" t="s">
         <v>162</v>
@@ -14550,10 +14550,10 @@
         <v>501</v>
       </c>
       <c r="J225" t="s">
-        <v>148</v>
+        <v>72</v>
       </c>
       <c r="K225" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="L225" t="s">
         <v>34</v>
@@ -14565,7 +14565,7 @@
         <v>45</v>
       </c>
       <c r="O225" t="s">
-        <v>81</v>
+        <v>308</v>
       </c>
       <c r="P225" t="s">
         <v>501</v>
@@ -14591,7 +14591,7 @@
         <v>34</v>
       </c>
       <c r="E226" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="F226" t="s">
         <v>162</v>
@@ -14606,10 +14606,10 @@
         <v>501</v>
       </c>
       <c r="J226" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K226" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="L226" t="s">
         <v>34</v>
@@ -14621,7 +14621,7 @@
         <v>45</v>
       </c>
       <c r="O226" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="P226" t="s">
         <v>501</v>
@@ -14647,7 +14647,7 @@
         <v>34</v>
       </c>
       <c r="E227" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="F227" t="s">
         <v>162</v>
@@ -14662,10 +14662,10 @@
         <v>501</v>
       </c>
       <c r="J227" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="K227" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="L227" t="s">
         <v>34</v>
@@ -14677,7 +14677,7 @@
         <v>45</v>
       </c>
       <c r="O227" t="s">
-        <v>304</v>
+        <v>92</v>
       </c>
       <c r="P227" t="s">
         <v>501</v>
@@ -14703,7 +14703,7 @@
         <v>34</v>
       </c>
       <c r="E228" t="s">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="F228" t="s">
         <v>162</v>
@@ -14718,10 +14718,10 @@
         <v>501</v>
       </c>
       <c r="J228" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="K228" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="L228" t="s">
         <v>34</v>
@@ -14733,7 +14733,7 @@
         <v>45</v>
       </c>
       <c r="O228" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="P228" t="s">
         <v>501</v>
@@ -14759,7 +14759,7 @@
         <v>34</v>
       </c>
       <c r="E229" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F229" t="s">
         <v>162</v>
@@ -14774,10 +14774,10 @@
         <v>501</v>
       </c>
       <c r="J229" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="K229" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="L229" t="s">
         <v>34</v>
@@ -14789,7 +14789,7 @@
         <v>45</v>
       </c>
       <c r="O229" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="P229" t="s">
         <v>501</v>
@@ -14815,7 +14815,7 @@
         <v>34</v>
       </c>
       <c r="E230" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="F230" t="s">
         <v>162</v>
@@ -14830,10 +14830,10 @@
         <v>501</v>
       </c>
       <c r="J230" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="K230" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="L230" t="s">
         <v>34</v>
@@ -14845,7 +14845,7 @@
         <v>45</v>
       </c>
       <c r="O230" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="P230" t="s">
         <v>501</v>
@@ -15110,13 +15110,13 @@
         <v>508</v>
       </c>
       <c r="J235" t="s">
-        <v>257</v>
+        <v>509</v>
       </c>
       <c r="K235" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="L235" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M235" t="s">
         <v>505</v>
@@ -15151,7 +15151,7 @@
         <v>34</v>
       </c>
       <c r="E236" t="s">
-        <v>149</v>
+        <v>506</v>
       </c>
       <c r="F236" t="s">
         <v>162</v>
@@ -15160,16 +15160,16 @@
         <v>41</v>
       </c>
       <c r="H236" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I236" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J236" t="s">
-        <v>512</v>
+        <v>242</v>
       </c>
       <c r="K236" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="L236" t="s">
         <v>513</v>
@@ -15184,7 +15184,7 @@
         <v>140</v>
       </c>
       <c r="P236" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Q236" t="s">
         <v>45</v>
@@ -15207,7 +15207,7 @@
         <v>34</v>
       </c>
       <c r="E237" t="s">
-        <v>506</v>
+        <v>144</v>
       </c>
       <c r="F237" t="s">
         <v>162</v>
@@ -15225,7 +15225,7 @@
         <v>516</v>
       </c>
       <c r="K237" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="L237" t="s">
         <v>517</v>
@@ -15502,7 +15502,7 @@
         <v>529</v>
       </c>
       <c r="J242" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="K242" t="s">
         <v>44</v>
@@ -15658,7 +15658,7 @@
         <v>536</v>
       </c>
       <c r="F245" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G245" t="s">
         <v>41</v>
@@ -15726,7 +15726,7 @@
         <v>540</v>
       </c>
       <c r="J246" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="K246" t="s">
         <v>44</v>
@@ -15782,7 +15782,7 @@
         <v>543</v>
       </c>
       <c r="J247" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="K247" t="s">
         <v>44</v>
@@ -15823,7 +15823,7 @@
         <v>34</v>
       </c>
       <c r="E248" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="F248" t="s">
         <v>162</v>
@@ -15832,19 +15832,19 @@
         <v>41</v>
       </c>
       <c r="H248" t="s">
-        <v>333</v>
+        <v>545</v>
       </c>
       <c r="I248" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="J248" t="s">
-        <v>546</v>
+        <v>509</v>
       </c>
       <c r="K248" t="s">
         <v>44</v>
       </c>
       <c r="L248" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="M248" t="s">
         <v>535</v>
@@ -15856,7 +15856,7 @@
         <v>140</v>
       </c>
       <c r="P248" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="Q248" t="s">
         <v>45</v>
@@ -15888,13 +15888,13 @@
         <v>41</v>
       </c>
       <c r="H249" t="s">
+        <v>547</v>
+      </c>
+      <c r="I249" t="s">
         <v>548</v>
       </c>
-      <c r="I249" t="s">
-        <v>529</v>
-      </c>
       <c r="J249" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="K249" t="s">
         <v>44</v>
@@ -15912,7 +15912,7 @@
         <v>140</v>
       </c>
       <c r="P249" t="s">
-        <v>529</v>
+        <v>548</v>
       </c>
       <c r="Q249" t="s">
         <v>45</v>
@@ -15944,19 +15944,19 @@
         <v>41</v>
       </c>
       <c r="H250" t="s">
-        <v>391</v>
+        <v>550</v>
       </c>
       <c r="I250" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J250" t="s">
-        <v>257</v>
+        <v>509</v>
       </c>
       <c r="K250" t="s">
         <v>44</v>
       </c>
       <c r="L250" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M250" t="s">
         <v>535</v>
@@ -15968,7 +15968,7 @@
         <v>140</v>
       </c>
       <c r="P250" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="Q250" t="s">
         <v>45</v>
@@ -15991,25 +15991,25 @@
         <v>34</v>
       </c>
       <c r="E251" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F251" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G251" t="s">
         <v>41</v>
       </c>
       <c r="H251" t="s">
-        <v>356</v>
+        <v>554</v>
       </c>
       <c r="I251" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="J251" t="s">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="K251" t="s">
-        <v>554</v>
+        <v>138</v>
       </c>
       <c r="L251" t="s">
         <v>34</v>
@@ -16024,7 +16024,7 @@
         <v>140</v>
       </c>
       <c r="P251" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="Q251" t="s">
         <v>45</v>
@@ -16047,7 +16047,7 @@
         <v>34</v>
       </c>
       <c r="E252" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F252" t="s">
         <v>162</v>
@@ -16059,16 +16059,16 @@
         <v>388</v>
       </c>
       <c r="I252" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J252" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="K252" t="s">
         <v>44</v>
       </c>
       <c r="L252" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M252" t="s">
         <v>535</v>
@@ -16080,7 +16080,7 @@
         <v>140</v>
       </c>
       <c r="P252" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="Q252" t="s">
         <v>45</v>
@@ -16103,7 +16103,7 @@
         <v>34</v>
       </c>
       <c r="E253" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="F253" t="s">
         <v>162</v>
@@ -16112,19 +16112,19 @@
         <v>41</v>
       </c>
       <c r="H253" t="s">
-        <v>558</v>
+        <v>333</v>
       </c>
       <c r="I253" t="s">
         <v>559</v>
       </c>
       <c r="J253" t="s">
-        <v>516</v>
+        <v>560</v>
       </c>
       <c r="K253" t="s">
         <v>44</v>
       </c>
       <c r="L253" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M253" t="s">
         <v>535</v>
@@ -16159,28 +16159,28 @@
         <v>34</v>
       </c>
       <c r="E254" t="s">
-        <v>552</v>
+        <v>506</v>
       </c>
       <c r="F254" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="G254" t="s">
         <v>41</v>
       </c>
       <c r="H254" t="s">
-        <v>561</v>
+        <v>391</v>
       </c>
       <c r="I254" t="s">
         <v>562</v>
       </c>
       <c r="J254" t="s">
-        <v>138</v>
+        <v>242</v>
       </c>
       <c r="K254" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="L254" t="s">
-        <v>34</v>
+        <v>563</v>
       </c>
       <c r="M254" t="s">
         <v>535</v>
@@ -16215,7 +16215,7 @@
         <v>34</v>
       </c>
       <c r="E255" t="s">
-        <v>506</v>
+        <v>144</v>
       </c>
       <c r="F255" t="s">
         <v>162</v>
@@ -16224,19 +16224,19 @@
         <v>41</v>
       </c>
       <c r="H255" t="s">
-        <v>563</v>
+        <v>350</v>
       </c>
       <c r="I255" t="s">
         <v>564</v>
       </c>
       <c r="J255" t="s">
-        <v>516</v>
+        <v>565</v>
       </c>
       <c r="K255" t="s">
         <v>44</v>
       </c>
       <c r="L255" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M255" t="s">
         <v>535</v>
@@ -16271,28 +16271,28 @@
         <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>149</v>
+        <v>536</v>
       </c>
       <c r="F256" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G256" t="s">
         <v>41</v>
       </c>
       <c r="H256" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="I256" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="J256" t="s">
-        <v>566</v>
+        <v>177</v>
       </c>
       <c r="K256" t="s">
-        <v>44</v>
+        <v>567</v>
       </c>
       <c r="L256" t="s">
-        <v>567</v>
+        <v>34</v>
       </c>
       <c r="M256" t="s">
         <v>535</v>
@@ -16304,7 +16304,7 @@
         <v>140</v>
       </c>
       <c r="P256" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="Q256" t="s">
         <v>45</v>
@@ -16342,7 +16342,7 @@
         <v>569</v>
       </c>
       <c r="J257" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="K257" t="s">
         <v>44</v>
@@ -16946,7 +16946,7 @@
         <v>593</v>
       </c>
       <c r="F268" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G268" t="s">
         <v>41</v>
@@ -17002,7 +17002,7 @@
         <v>593</v>
       </c>
       <c r="F269" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G269" t="s">
         <v>41</v>
@@ -17182,7 +17182,7 @@
         <v>604</v>
       </c>
       <c r="J272" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="K272" t="s">
         <v>138</v>
@@ -17226,7 +17226,7 @@
         <v>608</v>
       </c>
       <c r="F273" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G273" t="s">
         <v>41</v>
@@ -17462,7 +17462,7 @@
         <v>622</v>
       </c>
       <c r="J277" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="K277" t="s">
         <v>44</v>
@@ -17630,10 +17630,10 @@
         <v>634</v>
       </c>
       <c r="J280" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="K280" t="s">
-        <v>554</v>
+        <v>567</v>
       </c>
       <c r="L280" t="s">
         <v>635</v>
@@ -17730,7 +17730,7 @@
         <v>639</v>
       </c>
       <c r="F282" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G282" t="s">
         <v>41</v>
@@ -17742,10 +17742,10 @@
         <v>641</v>
       </c>
       <c r="J282" t="s">
-        <v>51</v>
+        <v>642</v>
       </c>
       <c r="K282" t="s">
-        <v>51</v>
+        <v>262</v>
       </c>
       <c r="L282" t="s">
         <v>34</v>
@@ -17783,25 +17783,25 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F283" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G283" t="s">
         <v>41</v>
       </c>
       <c r="H283" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="I283" t="s">
         <v>641</v>
       </c>
       <c r="J283" t="s">
-        <v>91</v>
+        <v>644</v>
       </c>
       <c r="K283" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="L283" t="s">
         <v>34</v>
@@ -17839,28 +17839,28 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>644</v>
+        <v>602</v>
       </c>
       <c r="F284" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="G284" t="s">
         <v>41</v>
       </c>
       <c r="H284" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="I284" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="J284" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="K284" t="s">
-        <v>262</v>
+        <v>138</v>
       </c>
       <c r="L284" t="s">
-        <v>34</v>
+        <v>647</v>
       </c>
       <c r="M284" t="s">
         <v>638</v>
@@ -17872,7 +17872,7 @@
         <v>140</v>
       </c>
       <c r="P284" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="Q284" t="s">
         <v>45</v>
@@ -17895,28 +17895,28 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>602</v>
+        <v>648</v>
       </c>
       <c r="F285" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G285" t="s">
         <v>41</v>
       </c>
       <c r="H285" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="I285" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="J285" t="s">
-        <v>516</v>
+        <v>91</v>
       </c>
       <c r="K285" t="s">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="L285" t="s">
-        <v>648</v>
+        <v>34</v>
       </c>
       <c r="M285" t="s">
         <v>638</v>
@@ -17928,7 +17928,7 @@
         <v>140</v>
       </c>
       <c r="P285" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="Q285" t="s">
         <v>45</v>
@@ -17951,10 +17951,10 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F286" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G286" t="s">
         <v>41</v>
@@ -17963,13 +17963,13 @@
         <v>640</v>
       </c>
       <c r="I286" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="J286" t="s">
-        <v>554</v>
+        <v>51</v>
       </c>
       <c r="K286" t="s">
-        <v>554</v>
+        <v>51</v>
       </c>
       <c r="L286" t="s">
         <v>34</v>
@@ -17984,7 +17984,7 @@
         <v>140</v>
       </c>
       <c r="P286" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="Q286" t="s">
         <v>45</v>
@@ -18010,7 +18010,7 @@
         <v>651</v>
       </c>
       <c r="F287" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G287" t="s">
         <v>41</v>
@@ -18019,13 +18019,13 @@
         <v>640</v>
       </c>
       <c r="I287" t="s">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="J287" t="s">
-        <v>652</v>
+        <v>567</v>
       </c>
       <c r="K287" t="s">
-        <v>51</v>
+        <v>567</v>
       </c>
       <c r="L287" t="s">
         <v>34</v>
@@ -18040,7 +18040,7 @@
         <v>140</v>
       </c>
       <c r="P287" t="s">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="Q287" t="s">
         <v>45</v>
@@ -18122,7 +18122,7 @@
         <v>656</v>
       </c>
       <c r="F289" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G289" t="s">
         <v>41</v>
@@ -18134,10 +18134,10 @@
         <v>658</v>
       </c>
       <c r="J289" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="K289" t="s">
-        <v>554</v>
+        <v>51</v>
       </c>
       <c r="L289" t="s">
         <v>659</v>
@@ -18178,7 +18178,7 @@
         <v>660</v>
       </c>
       <c r="F290" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G290" t="s">
         <v>41</v>
@@ -18190,10 +18190,10 @@
         <v>662</v>
       </c>
       <c r="J290" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="K290" t="s">
-        <v>51</v>
+        <v>567</v>
       </c>
       <c r="L290" t="s">
         <v>663</v>
@@ -18302,7 +18302,7 @@
         <v>669</v>
       </c>
       <c r="J292" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="K292" t="s">
         <v>44</v>
@@ -18511,7 +18511,7 @@
         <v>33</v>
       </c>
       <c r="E296" t="s">
-        <v>506</v>
+        <v>685</v>
       </c>
       <c r="F296" t="s">
         <v>162</v>
@@ -18520,19 +18520,19 @@
         <v>41</v>
       </c>
       <c r="H296" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="I296" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="J296" t="s">
-        <v>257</v>
+        <v>57</v>
       </c>
       <c r="K296" t="s">
-        <v>44</v>
+        <v>153</v>
       </c>
       <c r="L296" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M296" t="s">
         <v>684</v>
@@ -18544,7 +18544,7 @@
         <v>140</v>
       </c>
       <c r="P296" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="Q296" t="s">
         <v>45</v>
@@ -18567,7 +18567,7 @@
         <v>34</v>
       </c>
       <c r="E297" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F297" t="s">
         <v>162</v>
@@ -18576,16 +18576,16 @@
         <v>41</v>
       </c>
       <c r="H297" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="I297" t="s">
         <v>690</v>
       </c>
       <c r="J297" t="s">
-        <v>57</v>
+        <v>644</v>
       </c>
       <c r="K297" t="s">
-        <v>148</v>
+        <v>44</v>
       </c>
       <c r="L297" t="s">
         <v>691</v>
@@ -18638,7 +18638,7 @@
         <v>693</v>
       </c>
       <c r="J298" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="K298" t="s">
         <v>44</v>
@@ -18694,13 +18694,13 @@
         <v>696</v>
       </c>
       <c r="J299" t="s">
-        <v>652</v>
+        <v>697</v>
       </c>
       <c r="K299" t="s">
         <v>44</v>
       </c>
       <c r="L299" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M299" t="s">
         <v>684</v>
@@ -18735,7 +18735,7 @@
         <v>34</v>
       </c>
       <c r="E300" t="s">
-        <v>698</v>
+        <v>506</v>
       </c>
       <c r="F300" t="s">
         <v>162</v>
@@ -18744,13 +18744,13 @@
         <v>41</v>
       </c>
       <c r="H300" t="s">
-        <v>679</v>
+        <v>699</v>
       </c>
       <c r="I300" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="J300" t="s">
-        <v>700</v>
+        <v>242</v>
       </c>
       <c r="K300" t="s">
         <v>44</v>
@@ -18768,7 +18768,7 @@
         <v>140</v>
       </c>
       <c r="P300" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="Q300" t="s">
         <v>45</v>
@@ -18791,7 +18791,7 @@
         <v>34</v>
       </c>
       <c r="E301" t="s">
-        <v>506</v>
+        <v>702</v>
       </c>
       <c r="F301" t="s">
         <v>162</v>
@@ -18800,16 +18800,16 @@
         <v>41</v>
       </c>
       <c r="H301" t="s">
-        <v>679</v>
+        <v>703</v>
       </c>
       <c r="I301" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="J301" t="s">
-        <v>257</v>
+        <v>705</v>
       </c>
       <c r="K301" t="s">
-        <v>645</v>
+        <v>44</v>
       </c>
       <c r="L301" t="s">
         <v>703</v>
@@ -18824,7 +18824,7 @@
         <v>140</v>
       </c>
       <c r="P301" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="Q301" t="s">
         <v>45</v>
@@ -18847,7 +18847,7 @@
         <v>34</v>
       </c>
       <c r="E302" t="s">
-        <v>704</v>
+        <v>506</v>
       </c>
       <c r="F302" t="s">
         <v>162</v>
@@ -18856,19 +18856,19 @@
         <v>41</v>
       </c>
       <c r="H302" t="s">
-        <v>705</v>
+        <v>679</v>
       </c>
       <c r="I302" t="s">
         <v>706</v>
       </c>
       <c r="J302" t="s">
+        <v>242</v>
+      </c>
+      <c r="K302" t="s">
+        <v>642</v>
+      </c>
+      <c r="L302" t="s">
         <v>707</v>
-      </c>
-      <c r="K302" t="s">
-        <v>44</v>
-      </c>
-      <c r="L302" t="s">
-        <v>705</v>
       </c>
       <c r="M302" t="s">
         <v>684</v>
@@ -18974,7 +18974,7 @@
         <v>712</v>
       </c>
       <c r="J304" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="K304" t="s">
         <v>44</v>
@@ -19074,7 +19074,7 @@
         <v>718</v>
       </c>
       <c r="F306" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G306" t="s">
         <v>41</v>
@@ -19142,7 +19142,7 @@
         <v>725</v>
       </c>
       <c r="J307" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="K307" t="s">
         <v>44</v>
@@ -19186,7 +19186,7 @@
         <v>729</v>
       </c>
       <c r="F308" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G308" t="s">
         <v>41</v>
@@ -19354,7 +19354,7 @@
         <v>742</v>
       </c>
       <c r="F311" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G311" t="s">
         <v>41</v>
@@ -19422,7 +19422,7 @@
         <v>748</v>
       </c>
       <c r="J312" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="K312" t="s">
         <v>44</v>
@@ -19478,7 +19478,7 @@
         <v>751</v>
       </c>
       <c r="J313" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="K313" t="s">
         <v>91</v>
@@ -19519,7 +19519,7 @@
         <v>33</v>
       </c>
       <c r="E314" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F314" t="s">
         <v>162</v>
@@ -19534,7 +19534,7 @@
         <v>756</v>
       </c>
       <c r="J314" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="K314" t="s">
         <v>44</v>
@@ -19746,7 +19746,7 @@
         <v>763</v>
       </c>
       <c r="F318" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G318" t="s">
         <v>41</v>
@@ -19758,7 +19758,7 @@
         <v>765</v>
       </c>
       <c r="J318" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="K318" t="s">
         <v>51</v>
@@ -20639,7 +20639,7 @@
         <v>34</v>
       </c>
       <c r="E334" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="F334" t="s">
         <v>202</v>
@@ -20654,10 +20654,10 @@
         <v>786</v>
       </c>
       <c r="J334" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="K334" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="L334" t="s">
         <v>773</v>

--- a/xlsx/dre/DRE_06_2026.xlsx
+++ b/xlsx/dre/DRE_06_2026.xlsx
@@ -447,6 +447,21 @@
     <t>R$  178,31</t>
   </si>
   <si>
+    <t>1/5</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>R$  441,79</t>
+  </si>
+  <si>
+    <t>27/02/26</t>
+  </si>
+  <si>
+    <t>Digisac MP 2026</t>
+  </si>
+  <si>
     <t>685/1</t>
   </si>
   <si>
@@ -460,21 +475,6 @@
   </si>
   <si>
     <t>22/06/26</t>
-  </si>
-  <si>
-    <t>1/5</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>R$  441,79</t>
-  </si>
-  <si>
-    <t>27/02/26</t>
-  </si>
-  <si>
-    <t>Digisac MP 2026</t>
   </si>
   <si>
     <t>4 CUSTOS E DESPESAS</t>
@@ -1349,12 +1349,12 @@
     <t>DSR jun26/1</t>
   </si>
   <si>
+    <t>R$  2.151,72</t>
+  </si>
+  <si>
     <t>R$  1.207,83</t>
   </si>
   <si>
-    <t>R$  2.151,72</t>
-  </si>
-  <si>
     <t>4.03.02 COMISSÕES E BÔNUS DE TERCEIROS</t>
   </si>
   <si>
@@ -1553,6 +1553,18 @@
     <t>12/6</t>
   </si>
   <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
     <t>Google</t>
   </si>
   <si>
@@ -1574,18 +1586,6 @@
     <t>Webgiga 2026</t>
   </si>
   <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
-  </si>
-  <si>
     <t>1/4</t>
   </si>
   <si>
@@ -1961,48 +1961,48 @@
     <t>4.04.02.05.02 Serviços de limpeza</t>
   </si>
   <si>
+    <t>664/1</t>
+  </si>
+  <si>
+    <t>Claudineuza Santos Machado</t>
+  </si>
+  <si>
+    <t>R$  230,00</t>
+  </si>
+  <si>
+    <t>08/06/26</t>
+  </si>
+  <si>
+    <t>673/1</t>
+  </si>
+  <si>
+    <t>11/06/26</t>
+  </si>
+  <si>
+    <t>Thais Pereira Pires</t>
+  </si>
+  <si>
+    <t>R$  1.600,00</t>
+  </si>
+  <si>
+    <t>Thais Limpeza - 2026</t>
+  </si>
+  <si>
+    <t>683/1</t>
+  </si>
+  <si>
+    <t>Sabrina Barbosa de Medeiros</t>
+  </si>
+  <si>
     <t>675/1</t>
   </si>
   <si>
-    <t>Claudineuza Santos Machado</t>
-  </si>
-  <si>
-    <t>R$  230,00</t>
-  </si>
-  <si>
-    <t>683/1</t>
-  </si>
-  <si>
-    <t>Sabrina Barbosa de Medeiros</t>
-  </si>
-  <si>
-    <t>664/1</t>
-  </si>
-  <si>
-    <t>08/06/26</t>
-  </si>
-  <si>
-    <t>Thais Pereira Pires</t>
-  </si>
-  <si>
-    <t>R$  1.600,00</t>
-  </si>
-  <si>
-    <t>Thais Limpeza - 2026</t>
-  </si>
-  <si>
     <t>663/1</t>
   </si>
   <si>
     <t>R$  220,00</t>
   </si>
   <si>
-    <t>673/1</t>
-  </si>
-  <si>
-    <t>11/06/26</t>
-  </si>
-  <si>
     <t>4.04.02.06 Material de escritório</t>
   </si>
   <si>
@@ -2010,18 +2010,6 @@
   </si>
   <si>
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
-  </si>
-  <si>
-    <t>699/1</t>
-  </si>
-  <si>
-    <t>Pão de Açúcar</t>
-  </si>
-  <si>
-    <t>R$  95,17</t>
-  </si>
-  <si>
-    <t>material limpeza</t>
   </si>
   <si>
     <t>700/1</t>
@@ -2040,6 +2028,18 @@
 </t>
   </si>
   <si>
+    <t>699/1</t>
+  </si>
+  <si>
+    <t>Pão de Açúcar</t>
+  </si>
+  <si>
+    <t>R$  95,17</t>
+  </si>
+  <si>
+    <t>material limpeza</t>
+  </si>
+  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2103,6 +2103,48 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>64/1</t>
+  </si>
+  <si>
+    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  146,67</t>
+  </si>
+  <si>
+    <t>ISO Implantação -Saude ocupacional</t>
+  </si>
+  <si>
+    <t>63/1</t>
+  </si>
+  <si>
+    <t>R$  376,38</t>
+  </si>
+  <si>
+    <t>Promob 2026/4</t>
+  </si>
+  <si>
+    <t>62/1</t>
+  </si>
+  <si>
+    <t>R$  293,11</t>
+  </si>
+  <si>
+    <t>Promob 2026/3</t>
+  </si>
+  <si>
+    <t>3/5</t>
+  </si>
+  <si>
+    <t>R$  1.248,76</t>
+  </si>
+  <si>
+    <t>13/02/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/2</t>
+  </si>
+  <si>
     <t>D4 sign</t>
   </si>
   <si>
@@ -2112,64 +2154,22 @@
     <t>D4 sign 2026</t>
   </si>
   <si>
-    <t>64/1</t>
-  </si>
-  <si>
-    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  146,67</t>
-  </si>
-  <si>
-    <t>ISO Implantação -Saude ocupacional</t>
-  </si>
-  <si>
-    <t>63/1</t>
-  </si>
-  <si>
-    <t>R$  376,38</t>
-  </si>
-  <si>
-    <t>Promob 2026/4</t>
-  </si>
-  <si>
-    <t>62/1</t>
-  </si>
-  <si>
-    <t>R$  293,11</t>
-  </si>
-  <si>
-    <t>Promob 2026/3</t>
-  </si>
-  <si>
-    <t>3/5</t>
-  </si>
-  <si>
-    <t>R$  1.248,76</t>
-  </si>
-  <si>
-    <t>13/02/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/2</t>
+    <t>61/2</t>
+  </si>
+  <si>
+    <t>Pipefy</t>
+  </si>
+  <si>
+    <t>R$  95,96</t>
+  </si>
+  <si>
+    <t>21/05/26</t>
   </si>
   <si>
     <t>R$  599,00</t>
   </si>
   <si>
     <t>Promob 2026</t>
-  </si>
-  <si>
-    <t>61/2</t>
-  </si>
-  <si>
-    <t>Pipefy</t>
-  </si>
-  <si>
-    <t>R$  95,96</t>
-  </si>
-  <si>
-    <t>21/05/26</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -4532,25 +4532,25 @@
         <v>144</v>
       </c>
       <c r="F46" t="s">
+        <v>48</v>
+      </c>
+      <c r="G46" t="s">
+        <v>41</v>
+      </c>
+      <c r="H46" t="s">
         <v>145</v>
       </c>
-      <c r="G46" t="s">
-        <v>41</v>
-      </c>
-      <c r="H46" t="s">
+      <c r="I46" t="s">
         <v>146</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>147</v>
       </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
+        <v>91</v>
+      </c>
+      <c r="L46" t="s">
         <v>148</v>
-      </c>
-      <c r="K46" t="s">
-        <v>57</v>
-      </c>
-      <c r="L46" t="s">
-        <v>34</v>
       </c>
       <c r="M46" t="s">
         <v>133</v>
@@ -4562,7 +4562,7 @@
         <v>140</v>
       </c>
       <c r="P46" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q46" t="s">
         <v>45</v>
@@ -4588,25 +4588,25 @@
         <v>149</v>
       </c>
       <c r="F47" t="s">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="G47" t="s">
         <v>41</v>
       </c>
       <c r="H47" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J47" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K47" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="L47" t="s">
-        <v>153</v>
+        <v>34</v>
       </c>
       <c r="M47" t="s">
         <v>133</v>
@@ -4618,7 +4618,7 @@
         <v>140</v>
       </c>
       <c r="P47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q47" t="s">
         <v>45</v>
@@ -4865,7 +4865,7 @@
         <v>33</v>
       </c>
       <c r="E52" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F52" t="s">
         <v>162</v>
@@ -5148,7 +5148,7 @@
         <v>186</v>
       </c>
       <c r="F57" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G57" t="s">
         <v>41</v>
@@ -5820,13 +5820,13 @@
         <v>213</v>
       </c>
       <c r="F69" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G69" t="s">
         <v>41</v>
       </c>
       <c r="H69" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I69" t="s">
         <v>214</v>
@@ -5876,7 +5876,7 @@
         <v>62</v>
       </c>
       <c r="F70" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G70" t="s">
         <v>41</v>
@@ -5932,13 +5932,13 @@
         <v>219</v>
       </c>
       <c r="F71" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G71" t="s">
         <v>41</v>
       </c>
       <c r="H71" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I71" t="s">
         <v>214</v>
@@ -5988,7 +5988,7 @@
         <v>198</v>
       </c>
       <c r="F72" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G72" t="s">
         <v>41</v>
@@ -6212,7 +6212,7 @@
         <v>236</v>
       </c>
       <c r="F76" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G76" t="s">
         <v>41</v>
@@ -6324,7 +6324,7 @@
         <v>245</v>
       </c>
       <c r="F78" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G78" t="s">
         <v>41</v>
@@ -6380,7 +6380,7 @@
         <v>248</v>
       </c>
       <c r="F79" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G79" t="s">
         <v>41</v>
@@ -6436,13 +6436,13 @@
         <v>252</v>
       </c>
       <c r="F80" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G80" t="s">
         <v>41</v>
       </c>
       <c r="H80" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I80" t="s">
         <v>253</v>
@@ -6492,13 +6492,13 @@
         <v>254</v>
       </c>
       <c r="F81" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G81" t="s">
         <v>41</v>
       </c>
       <c r="H81" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I81" t="s">
         <v>255</v>
@@ -6548,7 +6548,7 @@
         <v>256</v>
       </c>
       <c r="F82" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G82" t="s">
         <v>41</v>
@@ -6604,7 +6604,7 @@
         <v>260</v>
       </c>
       <c r="F83" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G83" t="s">
         <v>41</v>
@@ -6666,7 +6666,7 @@
         <v>41</v>
       </c>
       <c r="H84" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I84" t="s">
         <v>266</v>
@@ -6716,7 +6716,7 @@
         <v>268</v>
       </c>
       <c r="F85" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G85" t="s">
         <v>41</v>
@@ -7108,7 +7108,7 @@
         <v>285</v>
       </c>
       <c r="F92" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G92" t="s">
         <v>41</v>
@@ -7668,7 +7668,7 @@
         <v>39</v>
       </c>
       <c r="F102" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G102" t="s">
         <v>41</v>
@@ -8004,13 +8004,13 @@
         <v>319</v>
       </c>
       <c r="F108" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G108" t="s">
         <v>41</v>
       </c>
       <c r="H108" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I108" t="s">
         <v>214</v>
@@ -8172,7 +8172,7 @@
         <v>95</v>
       </c>
       <c r="F111" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G111" t="s">
         <v>41</v>
@@ -8228,7 +8228,7 @@
         <v>62</v>
       </c>
       <c r="F112" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G112" t="s">
         <v>41</v>
@@ -11644,7 +11644,7 @@
         <v>205</v>
       </c>
       <c r="F173" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G173" t="s">
         <v>41</v>
@@ -12652,7 +12652,7 @@
         <v>54</v>
       </c>
       <c r="F191" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G191" t="s">
         <v>41</v>
@@ -12764,7 +12764,7 @@
         <v>119</v>
       </c>
       <c r="F193" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G193" t="s">
         <v>41</v>
@@ -12820,7 +12820,7 @@
         <v>95</v>
       </c>
       <c r="F194" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G194" t="s">
         <v>41</v>
@@ -12876,7 +12876,7 @@
         <v>432</v>
       </c>
       <c r="F195" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G195" t="s">
         <v>41</v>
@@ -12932,7 +12932,7 @@
         <v>59</v>
       </c>
       <c r="F196" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G196" t="s">
         <v>41</v>
@@ -12988,7 +12988,7 @@
         <v>62</v>
       </c>
       <c r="F197" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G197" t="s">
         <v>41</v>
@@ -13044,7 +13044,7 @@
         <v>88</v>
       </c>
       <c r="F198" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G198" t="s">
         <v>41</v>
@@ -13100,13 +13100,13 @@
         <v>440</v>
       </c>
       <c r="F199" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G199" t="s">
         <v>41</v>
       </c>
       <c r="H199" t="s">
-        <v>334</v>
+        <v>372</v>
       </c>
       <c r="I199" t="s">
         <v>441</v>
@@ -13156,13 +13156,13 @@
         <v>440</v>
       </c>
       <c r="F200" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G200" t="s">
         <v>41</v>
       </c>
       <c r="H200" t="s">
-        <v>372</v>
+        <v>334</v>
       </c>
       <c r="I200" t="s">
         <v>442</v>
@@ -13324,7 +13324,7 @@
         <v>200</v>
       </c>
       <c r="F203" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G203" t="s">
         <v>41</v>
@@ -13492,7 +13492,7 @@
         <v>95</v>
       </c>
       <c r="F206" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G206" t="s">
         <v>41</v>
@@ -13548,7 +13548,7 @@
         <v>456</v>
       </c>
       <c r="F207" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G207" t="s">
         <v>41</v>
@@ -13604,7 +13604,7 @@
         <v>459</v>
       </c>
       <c r="F208" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G208" t="s">
         <v>41</v>
@@ -13660,7 +13660,7 @@
         <v>59</v>
       </c>
       <c r="F209" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G209" t="s">
         <v>41</v>
@@ -13716,7 +13716,7 @@
         <v>54</v>
       </c>
       <c r="F210" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G210" t="s">
         <v>41</v>
@@ -13772,7 +13772,7 @@
         <v>464</v>
       </c>
       <c r="F211" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G211" t="s">
         <v>41</v>
@@ -13828,7 +13828,7 @@
         <v>468</v>
       </c>
       <c r="F212" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G212" t="s">
         <v>41</v>
@@ -13884,7 +13884,7 @@
         <v>348</v>
       </c>
       <c r="F213" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G213" t="s">
         <v>41</v>
@@ -13940,7 +13940,7 @@
         <v>473</v>
       </c>
       <c r="F214" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G214" t="s">
         <v>41</v>
@@ -13996,7 +13996,7 @@
         <v>476</v>
       </c>
       <c r="F215" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G215" t="s">
         <v>41</v>
@@ -14052,7 +14052,7 @@
         <v>478</v>
       </c>
       <c r="F216" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G216" t="s">
         <v>41</v>
@@ -14108,7 +14108,7 @@
         <v>481</v>
       </c>
       <c r="F217" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G217" t="s">
         <v>41</v>
@@ -14164,7 +14164,7 @@
         <v>484</v>
       </c>
       <c r="F218" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G218" t="s">
         <v>41</v>
@@ -14220,7 +14220,7 @@
         <v>487</v>
       </c>
       <c r="F219" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G219" t="s">
         <v>41</v>
@@ -14276,7 +14276,7 @@
         <v>489</v>
       </c>
       <c r="F220" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G220" t="s">
         <v>41</v>
@@ -14332,7 +14332,7 @@
         <v>492</v>
       </c>
       <c r="F221" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G221" t="s">
         <v>41</v>
@@ -14388,7 +14388,7 @@
         <v>495</v>
       </c>
       <c r="F222" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G222" t="s">
         <v>41</v>
@@ -14553,7 +14553,7 @@
         <v>33</v>
       </c>
       <c r="E225" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="F225" t="s">
         <v>162</v>
@@ -14568,10 +14568,10 @@
         <v>503</v>
       </c>
       <c r="J225" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="K225" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="L225" t="s">
         <v>34</v>
@@ -14583,7 +14583,7 @@
         <v>45</v>
       </c>
       <c r="O225" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P225" t="s">
         <v>503</v>
@@ -14609,7 +14609,7 @@
         <v>34</v>
       </c>
       <c r="E226" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F226" t="s">
         <v>162</v>
@@ -14624,10 +14624,10 @@
         <v>503</v>
       </c>
       <c r="J226" t="s">
-        <v>148</v>
+        <v>72</v>
       </c>
       <c r="K226" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="L226" t="s">
         <v>34</v>
@@ -14639,7 +14639,7 @@
         <v>45</v>
       </c>
       <c r="O226" t="s">
-        <v>81</v>
+        <v>309</v>
       </c>
       <c r="P226" t="s">
         <v>503</v>
@@ -14665,7 +14665,7 @@
         <v>34</v>
       </c>
       <c r="E227" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F227" t="s">
         <v>162</v>
@@ -14680,10 +14680,10 @@
         <v>503</v>
       </c>
       <c r="J227" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K227" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="L227" t="s">
         <v>34</v>
@@ -14695,7 +14695,7 @@
         <v>45</v>
       </c>
       <c r="O227" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="P227" t="s">
         <v>503</v>
@@ -14721,7 +14721,7 @@
         <v>34</v>
       </c>
       <c r="E228" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F228" t="s">
         <v>162</v>
@@ -14736,10 +14736,10 @@
         <v>503</v>
       </c>
       <c r="J228" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="K228" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="L228" t="s">
         <v>34</v>
@@ -14751,7 +14751,7 @@
         <v>45</v>
       </c>
       <c r="O228" t="s">
-        <v>309</v>
+        <v>92</v>
       </c>
       <c r="P228" t="s">
         <v>503</v>
@@ -14777,7 +14777,7 @@
         <v>34</v>
       </c>
       <c r="E229" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="F229" t="s">
         <v>162</v>
@@ -14792,10 +14792,10 @@
         <v>503</v>
       </c>
       <c r="J229" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="K229" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="L229" t="s">
         <v>34</v>
@@ -14807,7 +14807,7 @@
         <v>45</v>
       </c>
       <c r="O229" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="P229" t="s">
         <v>503</v>
@@ -14833,7 +14833,7 @@
         <v>34</v>
       </c>
       <c r="E230" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F230" t="s">
         <v>162</v>
@@ -14848,10 +14848,10 @@
         <v>503</v>
       </c>
       <c r="J230" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="K230" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="L230" t="s">
         <v>34</v>
@@ -14863,7 +14863,7 @@
         <v>45</v>
       </c>
       <c r="O230" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="P230" t="s">
         <v>503</v>
@@ -14889,7 +14889,7 @@
         <v>34</v>
       </c>
       <c r="E231" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F231" t="s">
         <v>162</v>
@@ -14904,10 +14904,10 @@
         <v>503</v>
       </c>
       <c r="J231" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="K231" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="L231" t="s">
         <v>34</v>
@@ -14919,7 +14919,7 @@
         <v>45</v>
       </c>
       <c r="O231" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="P231" t="s">
         <v>503</v>
@@ -15184,13 +15184,13 @@
         <v>510</v>
       </c>
       <c r="J236" t="s">
-        <v>243</v>
+        <v>511</v>
       </c>
       <c r="K236" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="L236" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M236" t="s">
         <v>507</v>
@@ -15225,7 +15225,7 @@
         <v>34</v>
       </c>
       <c r="E237" t="s">
-        <v>149</v>
+        <v>508</v>
       </c>
       <c r="F237" t="s">
         <v>162</v>
@@ -15234,16 +15234,16 @@
         <v>41</v>
       </c>
       <c r="H237" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="I237" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J237" t="s">
-        <v>514</v>
+        <v>243</v>
       </c>
       <c r="K237" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="L237" t="s">
         <v>515</v>
@@ -15258,7 +15258,7 @@
         <v>140</v>
       </c>
       <c r="P237" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="Q237" t="s">
         <v>45</v>
@@ -15281,7 +15281,7 @@
         <v>34</v>
       </c>
       <c r="E238" t="s">
-        <v>508</v>
+        <v>144</v>
       </c>
       <c r="F238" t="s">
         <v>162</v>
@@ -15299,7 +15299,7 @@
         <v>518</v>
       </c>
       <c r="K238" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="L238" t="s">
         <v>519</v>
@@ -15576,7 +15576,7 @@
         <v>531</v>
       </c>
       <c r="J243" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K243" t="s">
         <v>44</v>
@@ -15744,7 +15744,7 @@
         <v>539</v>
       </c>
       <c r="J246" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K246" t="s">
         <v>44</v>
@@ -15788,7 +15788,7 @@
         <v>541</v>
       </c>
       <c r="F247" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G247" t="s">
         <v>41</v>
@@ -15856,7 +15856,7 @@
         <v>531</v>
       </c>
       <c r="J248" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K248" t="s">
         <v>44</v>
@@ -15953,7 +15953,7 @@
         <v>34</v>
       </c>
       <c r="E250" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F250" t="s">
         <v>162</v>
@@ -16080,7 +16080,7 @@
         <v>557</v>
       </c>
       <c r="J252" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K252" t="s">
         <v>44</v>
@@ -16124,7 +16124,7 @@
         <v>559</v>
       </c>
       <c r="F253" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G253" t="s">
         <v>41</v>
@@ -16192,7 +16192,7 @@
         <v>563</v>
       </c>
       <c r="J254" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K254" t="s">
         <v>44</v>
@@ -16248,7 +16248,7 @@
         <v>566</v>
       </c>
       <c r="J255" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K255" t="s">
         <v>44</v>
@@ -16304,7 +16304,7 @@
         <v>569</v>
       </c>
       <c r="J256" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K256" t="s">
         <v>44</v>
@@ -16401,7 +16401,7 @@
         <v>34</v>
       </c>
       <c r="E258" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F258" t="s">
         <v>162</v>
@@ -16460,7 +16460,7 @@
         <v>559</v>
       </c>
       <c r="F259" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G259" t="s">
         <v>41</v>
@@ -17076,7 +17076,7 @@
         <v>599</v>
       </c>
       <c r="F270" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G270" t="s">
         <v>41</v>
@@ -17132,7 +17132,7 @@
         <v>599</v>
       </c>
       <c r="F271" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G271" t="s">
         <v>41</v>
@@ -17312,7 +17312,7 @@
         <v>610</v>
       </c>
       <c r="J274" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K274" t="s">
         <v>138</v>
@@ -17356,7 +17356,7 @@
         <v>614</v>
       </c>
       <c r="F275" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G275" t="s">
         <v>41</v>
@@ -17592,7 +17592,7 @@
         <v>628</v>
       </c>
       <c r="J279" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K279" t="s">
         <v>44</v>
@@ -17760,7 +17760,7 @@
         <v>640</v>
       </c>
       <c r="J282" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K282" t="s">
         <v>576</v>
@@ -17860,7 +17860,7 @@
         <v>645</v>
       </c>
       <c r="F284" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G284" t="s">
         <v>41</v>
@@ -17872,10 +17872,10 @@
         <v>647</v>
       </c>
       <c r="J284" t="s">
-        <v>51</v>
+        <v>648</v>
       </c>
       <c r="K284" t="s">
-        <v>51</v>
+        <v>263</v>
       </c>
       <c r="L284" t="s">
         <v>34</v>
@@ -17913,25 +17913,25 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F285" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G285" t="s">
         <v>41</v>
       </c>
       <c r="H285" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I285" t="s">
         <v>647</v>
       </c>
       <c r="J285" t="s">
-        <v>91</v>
+        <v>650</v>
       </c>
       <c r="K285" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="L285" t="s">
         <v>34</v>
@@ -17969,28 +17969,28 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
-        <v>650</v>
+        <v>608</v>
       </c>
       <c r="F286" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="G286" t="s">
         <v>41</v>
       </c>
       <c r="H286" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="I286" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="J286" t="s">
-        <v>651</v>
+        <v>511</v>
       </c>
       <c r="K286" t="s">
-        <v>263</v>
+        <v>138</v>
       </c>
       <c r="L286" t="s">
-        <v>34</v>
+        <v>653</v>
       </c>
       <c r="M286" t="s">
         <v>644</v>
@@ -18002,7 +18002,7 @@
         <v>140</v>
       </c>
       <c r="P286" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="Q286" t="s">
         <v>45</v>
@@ -18025,28 +18025,28 @@
         <v>34</v>
       </c>
       <c r="E287" t="s">
-        <v>608</v>
+        <v>654</v>
       </c>
       <c r="F287" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G287" t="s">
         <v>41</v>
       </c>
       <c r="H287" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="I287" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="J287" t="s">
-        <v>518</v>
+        <v>91</v>
       </c>
       <c r="K287" t="s">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="L287" t="s">
-        <v>654</v>
+        <v>34</v>
       </c>
       <c r="M287" t="s">
         <v>644</v>
@@ -18058,7 +18058,7 @@
         <v>140</v>
       </c>
       <c r="P287" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="Q287" t="s">
         <v>45</v>
@@ -18081,10 +18081,10 @@
         <v>34</v>
       </c>
       <c r="E288" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F288" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G288" t="s">
         <v>41</v>
@@ -18093,13 +18093,13 @@
         <v>646</v>
       </c>
       <c r="I288" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="J288" t="s">
-        <v>576</v>
+        <v>51</v>
       </c>
       <c r="K288" t="s">
-        <v>576</v>
+        <v>51</v>
       </c>
       <c r="L288" t="s">
         <v>34</v>
@@ -18114,7 +18114,7 @@
         <v>140</v>
       </c>
       <c r="P288" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="Q288" t="s">
         <v>45</v>
@@ -18140,7 +18140,7 @@
         <v>657</v>
       </c>
       <c r="F289" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G289" t="s">
         <v>41</v>
@@ -18149,13 +18149,13 @@
         <v>646</v>
       </c>
       <c r="I289" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="J289" t="s">
-        <v>658</v>
+        <v>576</v>
       </c>
       <c r="K289" t="s">
-        <v>51</v>
+        <v>576</v>
       </c>
       <c r="L289" t="s">
         <v>34</v>
@@ -18170,7 +18170,7 @@
         <v>140</v>
       </c>
       <c r="P289" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="Q289" t="s">
         <v>45</v>
@@ -18252,7 +18252,7 @@
         <v>662</v>
       </c>
       <c r="F291" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G291" t="s">
         <v>41</v>
@@ -18267,7 +18267,7 @@
         <v>250</v>
       </c>
       <c r="K291" t="s">
-        <v>576</v>
+        <v>51</v>
       </c>
       <c r="L291" t="s">
         <v>665</v>
@@ -18308,7 +18308,7 @@
         <v>666</v>
       </c>
       <c r="F292" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G292" t="s">
         <v>41</v>
@@ -18323,7 +18323,7 @@
         <v>250</v>
       </c>
       <c r="K292" t="s">
-        <v>51</v>
+        <v>576</v>
       </c>
       <c r="L292" t="s">
         <v>669</v>
@@ -18432,7 +18432,7 @@
         <v>675</v>
       </c>
       <c r="J294" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K294" t="s">
         <v>44</v>
@@ -18641,7 +18641,7 @@
         <v>33</v>
       </c>
       <c r="E298" t="s">
-        <v>508</v>
+        <v>691</v>
       </c>
       <c r="F298" t="s">
         <v>162</v>
@@ -18650,19 +18650,19 @@
         <v>41</v>
       </c>
       <c r="H298" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="I298" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="J298" t="s">
-        <v>243</v>
+        <v>57</v>
       </c>
       <c r="K298" t="s">
-        <v>44</v>
+        <v>153</v>
       </c>
       <c r="L298" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M298" t="s">
         <v>690</v>
@@ -18674,7 +18674,7 @@
         <v>140</v>
       </c>
       <c r="P298" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="Q298" t="s">
         <v>45</v>
@@ -18697,7 +18697,7 @@
         <v>34</v>
       </c>
       <c r="E299" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F299" t="s">
         <v>162</v>
@@ -18706,16 +18706,16 @@
         <v>41</v>
       </c>
       <c r="H299" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="I299" t="s">
         <v>696</v>
       </c>
       <c r="J299" t="s">
-        <v>57</v>
+        <v>650</v>
       </c>
       <c r="K299" t="s">
-        <v>148</v>
+        <v>44</v>
       </c>
       <c r="L299" t="s">
         <v>697</v>
@@ -18768,7 +18768,7 @@
         <v>699</v>
       </c>
       <c r="J300" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="K300" t="s">
         <v>44</v>
@@ -18824,13 +18824,13 @@
         <v>702</v>
       </c>
       <c r="J301" t="s">
-        <v>658</v>
+        <v>703</v>
       </c>
       <c r="K301" t="s">
         <v>44</v>
       </c>
       <c r="L301" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M301" t="s">
         <v>690</v>
@@ -18865,7 +18865,7 @@
         <v>34</v>
       </c>
       <c r="E302" t="s">
-        <v>704</v>
+        <v>508</v>
       </c>
       <c r="F302" t="s">
         <v>162</v>
@@ -18874,13 +18874,13 @@
         <v>41</v>
       </c>
       <c r="H302" t="s">
-        <v>685</v>
+        <v>705</v>
       </c>
       <c r="I302" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="J302" t="s">
-        <v>706</v>
+        <v>243</v>
       </c>
       <c r="K302" t="s">
         <v>44</v>
@@ -18898,7 +18898,7 @@
         <v>140</v>
       </c>
       <c r="P302" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="Q302" t="s">
         <v>45</v>
@@ -18921,7 +18921,7 @@
         <v>34</v>
       </c>
       <c r="E303" t="s">
-        <v>508</v>
+        <v>708</v>
       </c>
       <c r="F303" t="s">
         <v>162</v>
@@ -18930,16 +18930,16 @@
         <v>41</v>
       </c>
       <c r="H303" t="s">
-        <v>685</v>
+        <v>709</v>
       </c>
       <c r="I303" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="J303" t="s">
-        <v>243</v>
+        <v>711</v>
       </c>
       <c r="K303" t="s">
-        <v>651</v>
+        <v>44</v>
       </c>
       <c r="L303" t="s">
         <v>709</v>
@@ -18954,7 +18954,7 @@
         <v>140</v>
       </c>
       <c r="P303" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="Q303" t="s">
         <v>45</v>
@@ -18977,7 +18977,7 @@
         <v>34</v>
       </c>
       <c r="E304" t="s">
-        <v>710</v>
+        <v>508</v>
       </c>
       <c r="F304" t="s">
         <v>162</v>
@@ -18986,19 +18986,19 @@
         <v>41</v>
       </c>
       <c r="H304" t="s">
-        <v>711</v>
+        <v>685</v>
       </c>
       <c r="I304" t="s">
         <v>712</v>
       </c>
       <c r="J304" t="s">
+        <v>243</v>
+      </c>
+      <c r="K304" t="s">
+        <v>648</v>
+      </c>
+      <c r="L304" t="s">
         <v>713</v>
-      </c>
-      <c r="K304" t="s">
-        <v>44</v>
-      </c>
-      <c r="L304" t="s">
-        <v>711</v>
       </c>
       <c r="M304" t="s">
         <v>690</v>
@@ -19104,7 +19104,7 @@
         <v>718</v>
       </c>
       <c r="J306" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="K306" t="s">
         <v>44</v>
@@ -19204,7 +19204,7 @@
         <v>724</v>
       </c>
       <c r="F308" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G308" t="s">
         <v>41</v>
@@ -19272,7 +19272,7 @@
         <v>731</v>
       </c>
       <c r="J309" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K309" t="s">
         <v>44</v>
@@ -19316,7 +19316,7 @@
         <v>735</v>
       </c>
       <c r="F310" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G310" t="s">
         <v>41</v>
@@ -19484,7 +19484,7 @@
         <v>748</v>
       </c>
       <c r="F313" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G313" t="s">
         <v>41</v>
@@ -19552,7 +19552,7 @@
         <v>754</v>
       </c>
       <c r="J314" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K314" t="s">
         <v>44</v>
@@ -19608,7 +19608,7 @@
         <v>757</v>
       </c>
       <c r="J315" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="K315" t="s">
         <v>91</v>
@@ -19649,7 +19649,7 @@
         <v>33</v>
       </c>
       <c r="E316" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F316" t="s">
         <v>162</v>
@@ -19664,7 +19664,7 @@
         <v>762</v>
       </c>
       <c r="J316" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="K316" t="s">
         <v>44</v>
@@ -19876,7 +19876,7 @@
         <v>769</v>
       </c>
       <c r="F320" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G320" t="s">
         <v>41</v>

--- a/xlsx/dre/DRE_06_2026.xlsx
+++ b/xlsx/dre/DRE_06_2026.xlsx
@@ -700,15 +700,6 @@
     <t>R$ 1.915,14</t>
   </si>
   <si>
-    <t>64301/1</t>
-  </si>
-  <si>
-    <t>PFR</t>
-  </si>
-  <si>
-    <t>R$  1.622,10</t>
-  </si>
-  <si>
     <t>76601/1</t>
   </si>
   <si>
@@ -717,6 +708,15 @@
   <si>
     <t>Título referente a Frete. 
 Título gerado pela diferença de valor da revisão.</t>
+  </si>
+  <si>
+    <t>64301/1</t>
+  </si>
+  <si>
+    <t>PFR</t>
+  </si>
+  <si>
+    <t>R$  1.622,10</t>
   </si>
   <si>
     <t>4.02.01.01.04 Compra de outras mercadorias</t>
@@ -881,6 +881,108 @@
     <t>R$  8.627,93</t>
   </si>
   <si>
+    <t>83001/2</t>
+  </si>
+  <si>
+    <t>R$  317,58</t>
+  </si>
+  <si>
+    <t>82901/3</t>
+  </si>
+  <si>
+    <t>R$  403,84</t>
+  </si>
+  <si>
+    <t>82901/2</t>
+  </si>
+  <si>
+    <t>R$  376,99</t>
+  </si>
+  <si>
+    <t>81902/2</t>
+  </si>
+  <si>
+    <t>R$  1.907,88</t>
+  </si>
+  <si>
+    <t>81902/3</t>
+  </si>
+  <si>
+    <t>R$  2.043,81</t>
+  </si>
+  <si>
+    <t>83001/3</t>
+  </si>
+  <si>
+    <t>R$  340,21</t>
+  </si>
+  <si>
+    <t>85201/3</t>
+  </si>
+  <si>
+    <t>R$  5.004,04</t>
+  </si>
+  <si>
+    <t>85201/2</t>
+  </si>
+  <si>
+    <t>R$  4.671,21</t>
+  </si>
+  <si>
+    <t>84201/3</t>
+  </si>
+  <si>
+    <t>R$  1.577,95</t>
+  </si>
+  <si>
+    <t>85701/3</t>
+  </si>
+  <si>
+    <t>R$  397,24</t>
+  </si>
+  <si>
+    <t>85701THIAGOSS</t>
+  </si>
+  <si>
+    <t>84401/3</t>
+  </si>
+  <si>
+    <t>R$  298,62</t>
+  </si>
+  <si>
+    <t>84201/2</t>
+  </si>
+  <si>
+    <t>R$  1.473,00</t>
+  </si>
+  <si>
+    <t>84401/2</t>
+  </si>
+  <si>
+    <t>R$  278,76</t>
+  </si>
+  <si>
+    <t>85701/2</t>
+  </si>
+  <si>
+    <t>R$  370,82</t>
+  </si>
+  <si>
+    <t>85701HelgaBA</t>
+  </si>
+  <si>
+    <t>84102/3</t>
+  </si>
+  <si>
+    <t>R$  1.906,52</t>
+  </si>
+  <si>
+    <t>84102/2</t>
+  </si>
+  <si>
+    <t>R$  1.779,72</t>
+  </si>
+  <si>
     <t>85601/0</t>
   </si>
   <si>
@@ -890,115 +992,13 @@
     <t>85601KrisdanyVSMC</t>
   </si>
   <si>
-    <t>83001/2</t>
-  </si>
-  <si>
-    <t>R$  317,58</t>
-  </si>
-  <si>
-    <t>82901/3</t>
-  </si>
-  <si>
-    <t>R$  403,84</t>
-  </si>
-  <si>
-    <t>82901/2</t>
-  </si>
-  <si>
-    <t>R$  376,99</t>
-  </si>
-  <si>
-    <t>81902/2</t>
-  </si>
-  <si>
-    <t>R$  1.907,88</t>
-  </si>
-  <si>
-    <t>81902/3</t>
-  </si>
-  <si>
-    <t>R$  2.043,81</t>
-  </si>
-  <si>
-    <t>83001/3</t>
-  </si>
-  <si>
-    <t>R$  340,21</t>
-  </si>
-  <si>
-    <t>85201/3</t>
-  </si>
-  <si>
-    <t>R$  5.004,04</t>
-  </si>
-  <si>
-    <t>85201/2</t>
-  </si>
-  <si>
-    <t>R$  4.671,21</t>
-  </si>
-  <si>
-    <t>84201/3</t>
-  </si>
-  <si>
-    <t>R$  1.577,95</t>
-  </si>
-  <si>
     <t>R$  30,00</t>
   </si>
   <si>
-    <t>85701/3</t>
-  </si>
-  <si>
-    <t>R$  397,24</t>
-  </si>
-  <si>
-    <t>85701THIAGOSS</t>
-  </si>
-  <si>
-    <t>84401/3</t>
-  </si>
-  <si>
-    <t>R$  298,62</t>
-  </si>
-  <si>
-    <t>84201/2</t>
-  </si>
-  <si>
-    <t>R$  1.473,00</t>
-  </si>
-  <si>
-    <t>84401/2</t>
-  </si>
-  <si>
-    <t>R$  278,76</t>
-  </si>
-  <si>
-    <t>85701/2</t>
-  </si>
-  <si>
-    <t>R$  370,82</t>
-  </si>
-  <si>
-    <t>85701HelgaBA</t>
-  </si>
-  <si>
     <t>81801/2</t>
   </si>
   <si>
     <t>Chapa de MDF cliente Andre Soy Parc 2/3</t>
-  </si>
-  <si>
-    <t>84102/3</t>
-  </si>
-  <si>
-    <t>R$  1.906,52</t>
-  </si>
-  <si>
-    <t>84102/2</t>
-  </si>
-  <si>
-    <t>R$  1.779,72</t>
   </si>
   <si>
     <t>R$  75,63</t>
@@ -6100,25 +6100,25 @@
         <v>228</v>
       </c>
       <c r="F74" t="s">
+        <v>48</v>
+      </c>
+      <c r="G74" t="s">
+        <v>41</v>
+      </c>
+      <c r="H74" t="s">
+        <v>224</v>
+      </c>
+      <c r="I74" t="s">
         <v>229</v>
       </c>
-      <c r="G74" t="s">
-        <v>41</v>
-      </c>
-      <c r="H74" t="s">
-        <v>187</v>
-      </c>
-      <c r="I74" t="s">
+      <c r="J74" t="s">
+        <v>138</v>
+      </c>
+      <c r="K74" t="s">
+        <v>138</v>
+      </c>
+      <c r="L74" t="s">
         <v>230</v>
-      </c>
-      <c r="J74" t="s">
-        <v>87</v>
-      </c>
-      <c r="K74" t="s">
-        <v>87</v>
-      </c>
-      <c r="L74" t="s">
-        <v>212</v>
       </c>
       <c r="M74" t="s">
         <v>226</v>
@@ -6156,25 +6156,25 @@
         <v>231</v>
       </c>
       <c r="F75" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="G75" t="s">
         <v>41</v>
       </c>
       <c r="H75" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="I75" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J75" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="K75" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="L75" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="M75" t="s">
         <v>226</v>
@@ -7108,7 +7108,7 @@
         <v>285</v>
       </c>
       <c r="F92" t="s">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="G92" t="s">
         <v>41</v>
@@ -7120,13 +7120,13 @@
         <v>286</v>
       </c>
       <c r="J92" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="K92" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="L92" t="s">
-        <v>34</v>
+        <v>277</v>
       </c>
       <c r="M92" t="s">
         <v>274</v>
@@ -7135,7 +7135,7 @@
         <v>45</v>
       </c>
       <c r="O92" t="s">
-        <v>287</v>
+        <v>66</v>
       </c>
       <c r="P92" t="s">
         <v>286</v>
@@ -7161,7 +7161,7 @@
         <v>34</v>
       </c>
       <c r="E93" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F93" t="s">
         <v>190</v>
@@ -7170,16 +7170,16 @@
         <v>41</v>
       </c>
       <c r="H93" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I93" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J93" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="K93" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="L93" t="s">
         <v>277</v>
@@ -7191,10 +7191,10 @@
         <v>45</v>
       </c>
       <c r="O93" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="P93" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q93" t="s">
         <v>45</v>
@@ -7217,7 +7217,7 @@
         <v>34</v>
       </c>
       <c r="E94" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F94" t="s">
         <v>190</v>
@@ -7226,10 +7226,10 @@
         <v>41</v>
       </c>
       <c r="H94" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="I94" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J94" t="s">
         <v>44</v>
@@ -7250,7 +7250,7 @@
         <v>46</v>
       </c>
       <c r="P94" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q94" t="s">
         <v>45</v>
@@ -7273,7 +7273,7 @@
         <v>34</v>
       </c>
       <c r="E95" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F95" t="s">
         <v>190</v>
@@ -7285,13 +7285,13 @@
         <v>275</v>
       </c>
       <c r="I95" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J95" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="K95" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L95" t="s">
         <v>277</v>
@@ -7303,10 +7303,10 @@
         <v>45</v>
       </c>
       <c r="O95" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="P95" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q95" t="s">
         <v>45</v>
@@ -7329,7 +7329,7 @@
         <v>34</v>
       </c>
       <c r="E96" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F96" t="s">
         <v>190</v>
@@ -7338,10 +7338,10 @@
         <v>41</v>
       </c>
       <c r="H96" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I96" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J96" t="s">
         <v>52</v>
@@ -7362,7 +7362,7 @@
         <v>61</v>
       </c>
       <c r="P96" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q96" t="s">
         <v>45</v>
@@ -7385,7 +7385,7 @@
         <v>34</v>
       </c>
       <c r="E97" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F97" t="s">
         <v>190</v>
@@ -7397,13 +7397,13 @@
         <v>279</v>
       </c>
       <c r="I97" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J97" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="K97" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="L97" t="s">
         <v>277</v>
@@ -7415,10 +7415,10 @@
         <v>45</v>
       </c>
       <c r="O97" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="P97" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q97" t="s">
         <v>45</v>
@@ -7441,7 +7441,7 @@
         <v>34</v>
       </c>
       <c r="E98" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F98" t="s">
         <v>190</v>
@@ -7453,13 +7453,13 @@
         <v>279</v>
       </c>
       <c r="I98" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J98" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="K98" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="L98" t="s">
         <v>277</v>
@@ -7471,10 +7471,10 @@
         <v>45</v>
       </c>
       <c r="O98" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="P98" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q98" t="s">
         <v>45</v>
@@ -7497,7 +7497,7 @@
         <v>34</v>
       </c>
       <c r="E99" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F99" t="s">
         <v>190</v>
@@ -7506,10 +7506,10 @@
         <v>41</v>
       </c>
       <c r="H99" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="I99" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J99" t="s">
         <v>98</v>
@@ -7530,7 +7530,7 @@
         <v>99</v>
       </c>
       <c r="P99" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q99" t="s">
         <v>45</v>
@@ -7553,7 +7553,7 @@
         <v>34</v>
       </c>
       <c r="E100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F100" t="s">
         <v>190</v>
@@ -7562,16 +7562,16 @@
         <v>41</v>
       </c>
       <c r="H100" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J100" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="K100" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="L100" t="s">
         <v>277</v>
@@ -7583,10 +7583,10 @@
         <v>45</v>
       </c>
       <c r="O100" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="P100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q100" t="s">
         <v>45</v>
@@ -7609,7 +7609,7 @@
         <v>34</v>
       </c>
       <c r="E101" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F101" t="s">
         <v>190</v>
@@ -7621,13 +7621,13 @@
         <v>279</v>
       </c>
       <c r="I101" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J101" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="K101" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="L101" t="s">
         <v>277</v>
@@ -7639,10 +7639,10 @@
         <v>45</v>
       </c>
       <c r="O101" t="s">
-        <v>81</v>
+        <v>305</v>
       </c>
       <c r="P101" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q101" t="s">
         <v>45</v>
@@ -7665,28 +7665,28 @@
         <v>34</v>
       </c>
       <c r="E102" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
       <c r="F102" t="s">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="G102" t="s">
         <v>41</v>
       </c>
       <c r="H102" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I102" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J102" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="K102" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="L102" t="s">
-        <v>34</v>
+        <v>277</v>
       </c>
       <c r="M102" t="s">
         <v>274</v>
@@ -7695,10 +7695,10 @@
         <v>45</v>
       </c>
       <c r="O102" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="P102" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q102" t="s">
         <v>45</v>
@@ -7721,7 +7721,7 @@
         <v>34</v>
       </c>
       <c r="E103" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F103" t="s">
         <v>190</v>
@@ -7730,16 +7730,16 @@
         <v>41</v>
       </c>
       <c r="H103" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="I103" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J103" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K103" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L103" t="s">
         <v>277</v>
@@ -7751,10 +7751,10 @@
         <v>45</v>
       </c>
       <c r="O103" t="s">
+        <v>81</v>
+      </c>
+      <c r="P103" t="s">
         <v>309</v>
-      </c>
-      <c r="P103" t="s">
-        <v>308</v>
       </c>
       <c r="Q103" t="s">
         <v>45</v>
@@ -7786,7 +7786,7 @@
         <v>41</v>
       </c>
       <c r="H104" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="I104" t="s">
         <v>311</v>
@@ -7848,10 +7848,10 @@
         <v>313</v>
       </c>
       <c r="J105" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="K105" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="L105" t="s">
         <v>277</v>
@@ -7863,7 +7863,7 @@
         <v>45</v>
       </c>
       <c r="O105" t="s">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="P105" t="s">
         <v>313</v>
@@ -7889,7 +7889,7 @@
         <v>34</v>
       </c>
       <c r="E106" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F106" t="s">
         <v>190</v>
@@ -7898,16 +7898,16 @@
         <v>41</v>
       </c>
       <c r="H106" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I106" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J106" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="K106" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="L106" t="s">
         <v>277</v>
@@ -7919,10 +7919,10 @@
         <v>45</v>
       </c>
       <c r="O106" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="P106" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q106" t="s">
         <v>45</v>
@@ -7945,7 +7945,7 @@
         <v>34</v>
       </c>
       <c r="E107" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F107" t="s">
         <v>190</v>
@@ -7957,13 +7957,13 @@
         <v>275</v>
       </c>
       <c r="I107" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J107" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="K107" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="L107" t="s">
         <v>277</v>
@@ -7975,10 +7975,10 @@
         <v>45</v>
       </c>
       <c r="O107" t="s">
+        <v>58</v>
+      </c>
+      <c r="P107" t="s">
         <v>318</v>
-      </c>
-      <c r="P107" t="s">
-        <v>317</v>
       </c>
       <c r="Q107" t="s">
         <v>45</v>
@@ -8010,19 +8010,19 @@
         <v>41</v>
       </c>
       <c r="H108" t="s">
-        <v>151</v>
+        <v>275</v>
       </c>
       <c r="I108" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
       <c r="J108" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="K108" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="L108" t="s">
-        <v>320</v>
+        <v>34</v>
       </c>
       <c r="M108" t="s">
         <v>274</v>
@@ -8031,10 +8031,10 @@
         <v>45</v>
       </c>
       <c r="O108" t="s">
-        <v>216</v>
+        <v>321</v>
       </c>
       <c r="P108" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
       <c r="Q108" t="s">
         <v>45</v>
@@ -8057,28 +8057,28 @@
         <v>34</v>
       </c>
       <c r="E109" t="s">
-        <v>321</v>
+        <v>39</v>
       </c>
       <c r="F109" t="s">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="G109" t="s">
         <v>41</v>
       </c>
       <c r="H109" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="I109" t="s">
         <v>322</v>
       </c>
       <c r="J109" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="K109" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="L109" t="s">
-        <v>277</v>
+        <v>34</v>
       </c>
       <c r="M109" t="s">
         <v>274</v>
@@ -8087,7 +8087,7 @@
         <v>45</v>
       </c>
       <c r="O109" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="P109" t="s">
         <v>322</v>
@@ -8116,25 +8116,25 @@
         <v>323</v>
       </c>
       <c r="F110" t="s">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="G110" t="s">
         <v>41</v>
       </c>
       <c r="H110" t="s">
-        <v>275</v>
+        <v>151</v>
       </c>
       <c r="I110" t="s">
+        <v>214</v>
+      </c>
+      <c r="J110" t="s">
+        <v>44</v>
+      </c>
+      <c r="K110" t="s">
+        <v>44</v>
+      </c>
+      <c r="L110" t="s">
         <v>324</v>
-      </c>
-      <c r="J110" t="s">
-        <v>57</v>
-      </c>
-      <c r="K110" t="s">
-        <v>57</v>
-      </c>
-      <c r="L110" t="s">
-        <v>277</v>
       </c>
       <c r="M110" t="s">
         <v>274</v>
@@ -8143,10 +8143,10 @@
         <v>45</v>
       </c>
       <c r="O110" t="s">
-        <v>58</v>
+        <v>216</v>
       </c>
       <c r="P110" t="s">
-        <v>324</v>
+        <v>214</v>
       </c>
       <c r="Q110" t="s">
         <v>45</v>
@@ -8237,7 +8237,7 @@
         <v>275</v>
       </c>
       <c r="I112" t="s">
-        <v>286</v>
+        <v>320</v>
       </c>
       <c r="J112" t="s">
         <v>65</v>
@@ -8258,7 +8258,7 @@
         <v>66</v>
       </c>
       <c r="P112" t="s">
-        <v>286</v>
+        <v>320</v>
       </c>
       <c r="Q112" t="s">
         <v>45</v>
@@ -8535,7 +8535,7 @@
         <v>45</v>
       </c>
       <c r="O117" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P117" t="s">
         <v>335</v>
@@ -9151,7 +9151,7 @@
         <v>45</v>
       </c>
       <c r="O128" t="s">
-        <v>287</v>
+        <v>321</v>
       </c>
       <c r="P128" t="s">
         <v>350</v>
@@ -10327,7 +10327,7 @@
         <v>45</v>
       </c>
       <c r="O149" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P149" t="s">
         <v>376</v>
@@ -10439,7 +10439,7 @@
         <v>45</v>
       </c>
       <c r="O151" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P151" t="s">
         <v>378</v>
@@ -10999,7 +10999,7 @@
         <v>45</v>
       </c>
       <c r="O161" t="s">
-        <v>287</v>
+        <v>321</v>
       </c>
       <c r="P161" t="s">
         <v>381</v>
@@ -11055,7 +11055,7 @@
         <v>45</v>
       </c>
       <c r="O162" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P162" t="s">
         <v>335</v>
@@ -11279,7 +11279,7 @@
         <v>45</v>
       </c>
       <c r="O166" t="s">
-        <v>287</v>
+        <v>321</v>
       </c>
       <c r="P166" t="s">
         <v>385</v>
@@ -11671,7 +11671,7 @@
         <v>45</v>
       </c>
       <c r="O173" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P173" t="s">
         <v>335</v>
@@ -11727,7 +11727,7 @@
         <v>45</v>
       </c>
       <c r="O174" t="s">
-        <v>287</v>
+        <v>321</v>
       </c>
       <c r="P174" t="s">
         <v>381</v>
@@ -12903,7 +12903,7 @@
         <v>45</v>
       </c>
       <c r="O195" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="P195" t="s">
         <v>434</v>
@@ -13911,7 +13911,7 @@
         <v>45</v>
       </c>
       <c r="O213" t="s">
-        <v>287</v>
+        <v>321</v>
       </c>
       <c r="P213" t="s">
         <v>472</v>
@@ -14639,7 +14639,7 @@
         <v>45</v>
       </c>
       <c r="O226" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P226" t="s">
         <v>503</v>

--- a/xlsx/dre/DRE_06_2026.xlsx
+++ b/xlsx/dre/DRE_06_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7114" uniqueCount="881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7114" uniqueCount="882">
   <si>
     <t>Movimentações Financeiras</t>
   </si>
@@ -480,7 +480,7 @@
     <t>4 CUSTOS E DESPESAS</t>
   </si>
   <si>
-    <t>R$ 653.716,10</t>
+    <t>R$ 652.525,31</t>
   </si>
   <si>
     <t>4.01 DEDUÇÕES DE RECEITA</t>
@@ -1223,54 +1223,54 @@
     <t>R$ 7.548,44</t>
   </si>
   <si>
+    <t>Jose Carlos de Carvalho</t>
+  </si>
+  <si>
+    <t>R$  4.535,18</t>
+  </si>
+  <si>
+    <t>05/10/26</t>
+  </si>
+  <si>
     <t>Ray</t>
   </si>
   <si>
     <t>R$  1.149,31</t>
   </si>
   <si>
+    <t>82201/1</t>
+  </si>
+  <si>
+    <t>R$  12,29</t>
+  </si>
+  <si>
+    <t>82201RuanCGS</t>
+  </si>
+  <si>
     <t>79202/2</t>
   </si>
   <si>
     <t>PPC</t>
   </si>
   <si>
+    <t>85601/2</t>
+  </si>
+  <si>
     <t>84601/2</t>
   </si>
   <si>
     <t>R$  2,40</t>
   </si>
   <si>
-    <t>Jose Carlos de Carvalho</t>
-  </si>
-  <si>
     <t>R$  1.229,74</t>
   </si>
   <si>
     <t>82201/2</t>
   </si>
   <si>
-    <t>R$  12,29</t>
-  </si>
-  <si>
     <t>03/06/26</t>
   </si>
   <si>
-    <t>85601/2</t>
-  </si>
-  <si>
-    <t>R$  4.535,18</t>
-  </si>
-  <si>
-    <t>05/10/26</t>
-  </si>
-  <si>
-    <t>82201/1</t>
-  </si>
-  <si>
-    <t>82201RuanCGS</t>
-  </si>
-  <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
   </si>
   <si>
@@ -1391,9 +1391,36 @@
     <t>Uber</t>
   </si>
   <si>
+    <t>R$  11,21</t>
+  </si>
+  <si>
+    <t>Lalamove</t>
+  </si>
+  <si>
+    <t>R$  100,00</t>
+  </si>
+  <si>
+    <t>42001/0</t>
+  </si>
+  <si>
+    <t>R$  35,08</t>
+  </si>
+  <si>
+    <t>42001LaysSB</t>
+  </si>
+  <si>
     <t>R$  79,10</t>
   </si>
   <si>
+    <t>51301UBER/0</t>
+  </si>
+  <si>
+    <t>R$  30,35</t>
+  </si>
+  <si>
+    <t>51301ElisangelaTSO</t>
+  </si>
+  <si>
     <t>46201UBER/0</t>
   </si>
   <si>
@@ -1403,6 +1430,9 @@
     <t>46201ANGELASC</t>
   </si>
   <si>
+    <t>R$  33,27</t>
+  </si>
+  <si>
     <t>37801/0</t>
   </si>
   <si>
@@ -1412,10 +1442,64 @@
     <t>37801fabiotp</t>
   </si>
   <si>
-    <t>R$  33,27</t>
-  </si>
-  <si>
-    <t>R$  11,21</t>
+    <t>30901/0</t>
+  </si>
+  <si>
+    <t>R$  25,15</t>
+  </si>
+  <si>
+    <t>30901RobertoP</t>
+  </si>
+  <si>
+    <t>47101UBER/0</t>
+  </si>
+  <si>
+    <t>R$  12,69</t>
+  </si>
+  <si>
+    <t>47101MarciaOA</t>
+  </si>
+  <si>
+    <t>52001/0</t>
+  </si>
+  <si>
+    <t>R$  43,42</t>
+  </si>
+  <si>
+    <t>52001LucianaXM</t>
+  </si>
+  <si>
+    <t>23801/0</t>
+  </si>
+  <si>
+    <t>R$  1,74</t>
+  </si>
+  <si>
+    <t>DiegoSB0023801</t>
+  </si>
+  <si>
+    <t>29901UBER/0</t>
+  </si>
+  <si>
+    <t>R$  14,48</t>
+  </si>
+  <si>
+    <t>29901FL8</t>
+  </si>
+  <si>
+    <t>40901/0</t>
+  </si>
+  <si>
+    <t>R$  11,73</t>
+  </si>
+  <si>
+    <t>40901DOUGLASJOS</t>
+  </si>
+  <si>
+    <t>ADM-UBER/0</t>
+  </si>
+  <si>
+    <t>R$  269,33</t>
   </si>
   <si>
     <t>13301U/0</t>
@@ -1430,96 +1514,12 @@
     <t>FlaviaCM0013301</t>
   </si>
   <si>
-    <t>51301UBER/0</t>
-  </si>
-  <si>
-    <t>R$  30,35</t>
-  </si>
-  <si>
-    <t>51301ElisangelaTSO</t>
-  </si>
-  <si>
-    <t>Lalamove</t>
-  </si>
-  <si>
-    <t>R$  100,00</t>
-  </si>
-  <si>
-    <t>52001/0</t>
-  </si>
-  <si>
-    <t>R$  43,42</t>
-  </si>
-  <si>
-    <t>52001LucianaXM</t>
-  </si>
-  <si>
     <t>81902UB/0</t>
   </si>
   <si>
     <t>R$  13,37</t>
   </si>
   <si>
-    <t>29901UBER/0</t>
-  </si>
-  <si>
-    <t>R$  14,48</t>
-  </si>
-  <si>
-    <t>29901FL8</t>
-  </si>
-  <si>
-    <t>30901/0</t>
-  </si>
-  <si>
-    <t>R$  25,15</t>
-  </si>
-  <si>
-    <t>30901RobertoP</t>
-  </si>
-  <si>
-    <t>40901/0</t>
-  </si>
-  <si>
-    <t>R$  11,73</t>
-  </si>
-  <si>
-    <t>40901DOUGLASJOS</t>
-  </si>
-  <si>
-    <t>ADM-UBER/0</t>
-  </si>
-  <si>
-    <t>R$  269,33</t>
-  </si>
-  <si>
-    <t>47101UBER/0</t>
-  </si>
-  <si>
-    <t>R$  12,69</t>
-  </si>
-  <si>
-    <t>47101MarciaOA</t>
-  </si>
-  <si>
-    <t>23801/0</t>
-  </si>
-  <si>
-    <t>R$  1,74</t>
-  </si>
-  <si>
-    <t>DiegoSB0023801</t>
-  </si>
-  <si>
-    <t>42001/0</t>
-  </si>
-  <si>
-    <t>R$  35,08</t>
-  </si>
-  <si>
-    <t>42001LaysSB</t>
-  </si>
-  <si>
     <t>4.03.03.02 Agregados e outros gastos de montagens</t>
   </si>
   <si>
@@ -1649,6 +1649,12 @@
     <t>Gutemberg Dias - Pagamento</t>
   </si>
   <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
     <t>fixo jun26/0</t>
   </si>
   <si>
@@ -1658,12 +1664,6 @@
     <t>R$  1.268,00</t>
   </si>
   <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
     <t>80/6</t>
   </si>
   <si>
@@ -1676,6 +1676,15 @@
     <t>Fixo Mayara</t>
   </si>
   <si>
+    <t>R$  1.419,85</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
+  </si>
+  <si>
     <t>R$  1.679,77</t>
   </si>
   <si>
@@ -1685,15 +1694,6 @@
     <t>Fernanda Dochvat - Fixo 2026</t>
   </si>
   <si>
-    <t>R$  1.419,85</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
     <t>CARINA PEREIRA</t>
   </si>
   <si>
@@ -1703,58 +1703,58 @@
     <t>Carina - Pagamento 2026</t>
   </si>
   <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  4.687,39</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>R$  2.145,57</t>
+  </si>
+  <si>
+    <t>Denny Lucas - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
     <t>Fixo jun26/1</t>
   </si>
   <si>
+    <t>R$  2.536,00</t>
+  </si>
+  <si>
+    <t>02/06/26</t>
+  </si>
+  <si>
+    <t>R$  1.024,58</t>
+  </si>
+  <si>
+    <t>Rubens - Pagamento 2026</t>
+  </si>
+  <si>
     <t>EFRAIM RIBEIRO</t>
   </si>
   <si>
     <t>R$  1.060,00</t>
   </si>
   <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  4.687,39</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>R$  2.145,57</t>
-  </si>
-  <si>
-    <t>Denny Lucas - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>R$  1.024,58</t>
-  </si>
-  <si>
-    <t>Rubens - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>R$  2.536,00</t>
-  </si>
-  <si>
     <t>19/02/26</t>
   </si>
   <si>
     <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
-    <t>02/06/26</t>
   </si>
   <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
@@ -2349,7 +2349,7 @@
     <t>4.07 DESPESAS FINANCEIRAS VARIÁVEIS</t>
   </si>
   <si>
-    <t>R$ 44.467,95</t>
+    <t>R$ 43.277,16</t>
   </si>
   <si>
     <t>4.07.01 DESPESAS FINANCEIRAS VARIÁVEIS</t>
@@ -2364,51 +2364,54 @@
     <t>Italíneacredi</t>
   </si>
   <si>
-    <t>R$  7.334,01</t>
+    <t>R$  2.068,67</t>
   </si>
   <si>
     <t>Título referente a Valor da Taxa Financeira</t>
   </si>
   <si>
+    <t>R$  7.195,10</t>
+  </si>
+  <si>
+    <t>R$  8.826,30</t>
+  </si>
+  <si>
+    <t>R$  610,79</t>
+  </si>
+  <si>
+    <t>R$  306,73</t>
+  </si>
+  <si>
+    <t>R$  12.457,40</t>
+  </si>
+  <si>
+    <t>R$  5.736,32</t>
+  </si>
+  <si>
+    <t>R$  2.399,95</t>
+  </si>
+  <si>
+    <t>R$  29,43</t>
+  </si>
+  <si>
+    <t>82201AnaBFF</t>
+  </si>
+  <si>
+    <t>R$  37,53</t>
+  </si>
+  <si>
     <t>PAGSEGURO</t>
   </si>
   <si>
-    <t>R$  79,90</t>
-  </si>
-  <si>
-    <t>R$  2.568,49</t>
-  </si>
-  <si>
-    <t>R$  454,41</t>
-  </si>
-  <si>
-    <t>R$  425,82</t>
-  </si>
-  <si>
-    <t>R$  9.022,94</t>
+    <t>R$  85,30</t>
+  </si>
+  <si>
+    <t>R$  402,24</t>
   </si>
   <si>
     <t>R$  3.121,40</t>
   </si>
   <si>
-    <t>R$  44,03</t>
-  </si>
-  <si>
-    <t>R$  6.135,60</t>
-  </si>
-  <si>
-    <t>R$  12.517,46</t>
-  </si>
-  <si>
-    <t>R$  679,88</t>
-  </si>
-  <si>
-    <t>R$  2.068,47</t>
-  </si>
-  <si>
-    <t>R$  15,54</t>
-  </si>
-  <si>
     <t>7.01 RECEITAS</t>
   </si>
   <si>
@@ -2550,7 +2553,7 @@
     <t>7.08 (-) DESPESAS E RECEITAS FINANCEIRAS</t>
   </si>
   <si>
-    <t>R$ 44.474,67</t>
+    <t>R$ 43.283,88</t>
   </si>
   <si>
     <t>7.08.01 Despesas e receitas financeiras fixas</t>
@@ -2568,7 +2571,7 @@
     <t>7.09 = RESULTADO OPERACIONAL</t>
   </si>
   <si>
-    <t>R$ 86.603,44</t>
+    <t>R$ 87.794,23</t>
   </si>
   <si>
     <t>7.11 = RESULTADO LÍQUIDO DO EXERCÍCIO</t>
@@ -2583,7 +2586,7 @@
     <t>7.50.02 TOTAL DOS CUSTOS VARIÁVEIS</t>
   </si>
   <si>
-    <t>R$ 569.397,45</t>
+    <t>R$ 568.206,66</t>
   </si>
   <si>
     <t>7.50.02.01 Deduções de receita</t>
@@ -2616,13 +2619,13 @@
     <t>7.60.02 TOTAL DE VENDAS - VALOR À VISTA</t>
   </si>
   <si>
-    <t>R$ 695.851,59</t>
+    <t>R$ 697.042,38</t>
   </si>
   <si>
     <t>7.60.03 TOTAL DE VENDAS - VALOR LÍQUIDO</t>
   </si>
   <si>
-    <t>R$ 693.392,11</t>
+    <t>R$ 694.582,90</t>
   </si>
   <si>
     <t>7.60.06 CUSTO DAS VENDAS - MERCADORIA</t>
@@ -2649,7 +2652,7 @@
     <t>7.70 BREAK-EVEN POINT</t>
   </si>
   <si>
-    <t>R$ 365.211,68</t>
+    <t>R$ 362.684,91</t>
   </si>
   <si>
     <t>7.80.01 Mark Up Negociado</t>
@@ -2664,13 +2667,13 @@
     <t>7.80.02 Mark Up à Vista</t>
   </si>
   <si>
+    <t>2,48</t>
+  </si>
+  <si>
+    <t>7.80.03 Mark Up Líquido</t>
+  </si>
+  <si>
     <t>2,47</t>
-  </si>
-  <si>
-    <t>7.80.03 Mark Up Líquido</t>
-  </si>
-  <si>
-    <t>2,46</t>
   </si>
 </sst>
 </file>
@@ -11641,10 +11644,10 @@
         <v>34</v>
       </c>
       <c r="E173" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F173" t="s">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="G173" t="s">
         <v>41</v>
@@ -11653,13 +11656,13 @@
         <v>399</v>
       </c>
       <c r="I173" t="s">
-        <v>335</v>
+        <v>400</v>
       </c>
       <c r="J173" t="s">
-        <v>44</v>
+        <v>401</v>
       </c>
       <c r="K173" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="L173" t="s">
         <v>34</v>
@@ -11671,10 +11674,10 @@
         <v>45</v>
       </c>
       <c r="O173" t="s">
-        <v>305</v>
+        <v>118</v>
       </c>
       <c r="P173" t="s">
-        <v>335</v>
+        <v>400</v>
       </c>
       <c r="Q173" t="s">
         <v>45</v>
@@ -11697,22 +11700,22 @@
         <v>34</v>
       </c>
       <c r="E174" t="s">
-        <v>348</v>
+        <v>205</v>
       </c>
       <c r="F174" t="s">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="G174" t="s">
         <v>41</v>
       </c>
       <c r="H174" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="I174" t="s">
-        <v>381</v>
+        <v>335</v>
       </c>
       <c r="J174" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="K174" t="s">
         <v>44</v>
@@ -11727,10 +11730,10 @@
         <v>45</v>
       </c>
       <c r="O174" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="P174" t="s">
-        <v>381</v>
+        <v>335</v>
       </c>
       <c r="Q174" t="s">
         <v>45</v>
@@ -11753,7 +11756,7 @@
         <v>34</v>
       </c>
       <c r="E175" t="s">
-        <v>194</v>
+        <v>348</v>
       </c>
       <c r="F175" t="s">
         <v>190</v>
@@ -11765,13 +11768,13 @@
         <v>392</v>
       </c>
       <c r="I175" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="J175" t="s">
         <v>103</v>
       </c>
       <c r="K175" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L175" t="s">
         <v>34</v>
@@ -11783,10 +11786,10 @@
         <v>45</v>
       </c>
       <c r="O175" t="s">
-        <v>61</v>
+        <v>321</v>
       </c>
       <c r="P175" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="Q175" t="s">
         <v>45</v>
@@ -11809,25 +11812,25 @@
         <v>34</v>
       </c>
       <c r="E176" t="s">
-        <v>401</v>
+        <v>194</v>
       </c>
       <c r="F176" t="s">
-        <v>402</v>
+        <v>190</v>
       </c>
       <c r="G176" t="s">
         <v>41</v>
       </c>
       <c r="H176" t="s">
-        <v>224</v>
+        <v>392</v>
       </c>
       <c r="I176" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="J176" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K176" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="L176" t="s">
         <v>34</v>
@@ -11839,13 +11842,13 @@
         <v>45</v>
       </c>
       <c r="O176" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P176" t="s">
-        <v>34</v>
+        <v>403</v>
       </c>
       <c r="Q176" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R176" t="s">
         <v>34</v>
@@ -11865,7 +11868,7 @@
         <v>34</v>
       </c>
       <c r="E177" t="s">
-        <v>107</v>
+        <v>404</v>
       </c>
       <c r="F177" t="s">
         <v>190</v>
@@ -11874,16 +11877,16 @@
         <v>41</v>
       </c>
       <c r="H177" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="I177" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="J177" t="s">
         <v>103</v>
       </c>
       <c r="K177" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="L177" t="s">
         <v>34</v>
@@ -11895,10 +11898,10 @@
         <v>45</v>
       </c>
       <c r="O177" t="s">
-        <v>111</v>
+        <v>406</v>
       </c>
       <c r="P177" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="Q177" t="s">
         <v>45</v>
@@ -11921,25 +11924,25 @@
         <v>34</v>
       </c>
       <c r="E178" t="s">
-        <v>403</v>
+        <v>107</v>
       </c>
       <c r="F178" t="s">
-        <v>402</v>
+        <v>190</v>
       </c>
       <c r="G178" t="s">
         <v>41</v>
       </c>
       <c r="H178" t="s">
-        <v>224</v>
+        <v>389</v>
       </c>
       <c r="I178" t="s">
-        <v>404</v>
+        <v>382</v>
       </c>
       <c r="J178" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="K178" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="L178" t="s">
         <v>34</v>
@@ -11951,13 +11954,13 @@
         <v>45</v>
       </c>
       <c r="O178" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="P178" t="s">
-        <v>34</v>
+        <v>382</v>
       </c>
       <c r="Q178" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R178" t="s">
         <v>34</v>
@@ -11977,25 +11980,25 @@
         <v>34</v>
       </c>
       <c r="E179" t="s">
-        <v>200</v>
+        <v>407</v>
       </c>
       <c r="F179" t="s">
-        <v>190</v>
+        <v>408</v>
       </c>
       <c r="G179" t="s">
         <v>41</v>
       </c>
       <c r="H179" t="s">
-        <v>405</v>
+        <v>224</v>
       </c>
       <c r="I179" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="J179" t="s">
-        <v>391</v>
+        <v>104</v>
       </c>
       <c r="K179" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="L179" t="s">
         <v>34</v>
@@ -12007,13 +12010,13 @@
         <v>45</v>
       </c>
       <c r="O179" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="P179" t="s">
-        <v>406</v>
+        <v>34</v>
       </c>
       <c r="Q179" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R179" t="s">
         <v>34</v>
@@ -12033,10 +12036,10 @@
         <v>34</v>
       </c>
       <c r="E180" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F180" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="G180" t="s">
         <v>41</v>
@@ -12045,13 +12048,13 @@
         <v>224</v>
       </c>
       <c r="I180" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="J180" t="s">
-        <v>409</v>
+        <v>57</v>
       </c>
       <c r="K180" t="s">
-        <v>409</v>
+        <v>57</v>
       </c>
       <c r="L180" t="s">
         <v>34</v>
@@ -12092,7 +12095,7 @@
         <v>410</v>
       </c>
       <c r="F181" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="G181" t="s">
         <v>41</v>
@@ -12101,13 +12104,13 @@
         <v>224</v>
       </c>
       <c r="I181" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="J181" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="K181" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="L181" t="s">
         <v>34</v>
@@ -12145,7 +12148,7 @@
         <v>34</v>
       </c>
       <c r="E182" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F182" t="s">
         <v>190</v>
@@ -12154,16 +12157,16 @@
         <v>41</v>
       </c>
       <c r="H182" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="I182" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J182" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="K182" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="L182" t="s">
         <v>34</v>
@@ -12175,10 +12178,10 @@
         <v>45</v>
       </c>
       <c r="O182" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="P182" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q182" t="s">
         <v>45</v>
@@ -12204,22 +12207,22 @@
         <v>413</v>
       </c>
       <c r="F183" t="s">
-        <v>190</v>
+        <v>408</v>
       </c>
       <c r="G183" t="s">
         <v>41</v>
       </c>
       <c r="H183" t="s">
-        <v>392</v>
+        <v>224</v>
       </c>
       <c r="I183" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="J183" t="s">
-        <v>103</v>
+        <v>414</v>
       </c>
       <c r="K183" t="s">
-        <v>44</v>
+        <v>414</v>
       </c>
       <c r="L183" t="s">
         <v>34</v>
@@ -12231,13 +12234,13 @@
         <v>45</v>
       </c>
       <c r="O183" t="s">
-        <v>414</v>
+        <v>34</v>
       </c>
       <c r="P183" t="s">
-        <v>408</v>
+        <v>34</v>
       </c>
       <c r="Q183" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R183" t="s">
         <v>34</v>
@@ -12257,10 +12260,10 @@
         <v>33</v>
       </c>
       <c r="E184" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="F184" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="G184" t="s">
         <v>41</v>
@@ -12272,10 +12275,10 @@
         <v>417</v>
       </c>
       <c r="J184" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="K184" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="L184" t="s">
         <v>34</v>
@@ -12316,7 +12319,7 @@
         <v>189</v>
       </c>
       <c r="F185" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="G185" t="s">
         <v>41</v>
@@ -12372,7 +12375,7 @@
         <v>419</v>
       </c>
       <c r="F186" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="G186" t="s">
         <v>41</v>
@@ -12428,7 +12431,7 @@
         <v>200</v>
       </c>
       <c r="F187" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="G187" t="s">
         <v>41</v>
@@ -12484,7 +12487,7 @@
         <v>348</v>
       </c>
       <c r="F188" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="G188" t="s">
         <v>41</v>
@@ -12540,7 +12543,7 @@
         <v>198</v>
       </c>
       <c r="F189" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="G189" t="s">
         <v>41</v>
@@ -12596,7 +12599,7 @@
         <v>361</v>
       </c>
       <c r="F190" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="G190" t="s">
         <v>41</v>
@@ -12708,7 +12711,7 @@
         <v>107</v>
       </c>
       <c r="F192" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="G192" t="s">
         <v>41</v>
@@ -12944,7 +12947,7 @@
         <v>435</v>
       </c>
       <c r="J196" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="K196" t="s">
         <v>52</v>
@@ -13489,7 +13492,7 @@
         <v>33</v>
       </c>
       <c r="E206" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="F206" t="s">
         <v>150</v>
@@ -13504,10 +13507,10 @@
         <v>455</v>
       </c>
       <c r="J206" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="K206" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="L206" t="s">
         <v>34</v>
@@ -13519,7 +13522,7 @@
         <v>45</v>
       </c>
       <c r="O206" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="P206" t="s">
         <v>455</v>
@@ -13545,7 +13548,7 @@
         <v>34</v>
       </c>
       <c r="E207" t="s">
-        <v>456</v>
+        <v>348</v>
       </c>
       <c r="F207" t="s">
         <v>150</v>
@@ -13554,16 +13557,16 @@
         <v>41</v>
       </c>
       <c r="H207" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="I207" t="s">
         <v>457</v>
       </c>
       <c r="J207" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K207" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L207" t="s">
         <v>34</v>
@@ -13575,7 +13578,7 @@
         <v>45</v>
       </c>
       <c r="O207" t="s">
-        <v>458</v>
+        <v>321</v>
       </c>
       <c r="P207" t="s">
         <v>457</v>
@@ -13601,7 +13604,7 @@
         <v>34</v>
       </c>
       <c r="E208" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F208" t="s">
         <v>150</v>
@@ -13613,7 +13616,7 @@
         <v>454</v>
       </c>
       <c r="I208" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J208" t="s">
         <v>51</v>
@@ -13631,10 +13634,10 @@
         <v>45</v>
       </c>
       <c r="O208" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="P208" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Q208" t="s">
         <v>45</v>
@@ -13657,7 +13660,7 @@
         <v>34</v>
       </c>
       <c r="E209" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="F209" t="s">
         <v>150</v>
@@ -13669,13 +13672,13 @@
         <v>454</v>
       </c>
       <c r="I209" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="J209" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="K209" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="L209" t="s">
         <v>34</v>
@@ -13687,10 +13690,10 @@
         <v>45</v>
       </c>
       <c r="O209" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="P209" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q209" t="s">
         <v>45</v>
@@ -13713,7 +13716,7 @@
         <v>34</v>
       </c>
       <c r="E210" t="s">
-        <v>54</v>
+        <v>462</v>
       </c>
       <c r="F210" t="s">
         <v>150</v>
@@ -13728,10 +13731,10 @@
         <v>463</v>
       </c>
       <c r="J210" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="K210" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="L210" t="s">
         <v>34</v>
@@ -13743,7 +13746,7 @@
         <v>45</v>
       </c>
       <c r="O210" t="s">
-        <v>58</v>
+        <v>464</v>
       </c>
       <c r="P210" t="s">
         <v>463</v>
@@ -13769,7 +13772,7 @@
         <v>34</v>
       </c>
       <c r="E211" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F211" t="s">
         <v>150</v>
@@ -13781,13 +13784,13 @@
         <v>454</v>
       </c>
       <c r="I211" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J211" t="s">
-        <v>466</v>
+        <v>51</v>
       </c>
       <c r="K211" t="s">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="L211" t="s">
         <v>34</v>
@@ -13802,7 +13805,7 @@
         <v>467</v>
       </c>
       <c r="P211" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Q211" t="s">
         <v>45</v>
@@ -13825,7 +13828,7 @@
         <v>34</v>
       </c>
       <c r="E212" t="s">
-        <v>468</v>
+        <v>59</v>
       </c>
       <c r="F212" t="s">
         <v>150</v>
@@ -13837,13 +13840,13 @@
         <v>454</v>
       </c>
       <c r="I212" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J212" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K212" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L212" t="s">
         <v>34</v>
@@ -13855,10 +13858,10 @@
         <v>45</v>
       </c>
       <c r="O212" t="s">
-        <v>470</v>
+        <v>61</v>
       </c>
       <c r="P212" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="Q212" t="s">
         <v>45</v>
@@ -13881,7 +13884,7 @@
         <v>34</v>
       </c>
       <c r="E213" t="s">
-        <v>348</v>
+        <v>469</v>
       </c>
       <c r="F213" t="s">
         <v>150</v>
@@ -13890,16 +13893,16 @@
         <v>41</v>
       </c>
       <c r="H213" t="s">
-        <v>471</v>
+        <v>454</v>
       </c>
       <c r="I213" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="J213" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="K213" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="L213" t="s">
         <v>34</v>
@@ -13911,10 +13914,10 @@
         <v>45</v>
       </c>
       <c r="O213" t="s">
-        <v>321</v>
+        <v>471</v>
       </c>
       <c r="P213" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="Q213" t="s">
         <v>45</v>
@@ -13937,7 +13940,7 @@
         <v>34</v>
       </c>
       <c r="E214" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F214" t="s">
         <v>150</v>
@@ -13949,7 +13952,7 @@
         <v>454</v>
       </c>
       <c r="I214" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J214" t="s">
         <v>51</v>
@@ -13967,10 +13970,10 @@
         <v>45</v>
       </c>
       <c r="O214" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="P214" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Q214" t="s">
         <v>45</v>
@@ -13993,7 +13996,7 @@
         <v>34</v>
       </c>
       <c r="E215" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F215" t="s">
         <v>150</v>
@@ -14005,13 +14008,13 @@
         <v>454</v>
       </c>
       <c r="I215" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J215" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K215" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L215" t="s">
         <v>34</v>
@@ -14023,10 +14026,10 @@
         <v>45</v>
       </c>
       <c r="O215" t="s">
-        <v>61</v>
+        <v>477</v>
       </c>
       <c r="P215" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q215" t="s">
         <v>45</v>
@@ -14247,7 +14250,7 @@
         <v>45</v>
       </c>
       <c r="O219" t="s">
-        <v>140</v>
+        <v>489</v>
       </c>
       <c r="P219" t="s">
         <v>488</v>
@@ -14273,7 +14276,7 @@
         <v>34</v>
       </c>
       <c r="E220" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F220" t="s">
         <v>150</v>
@@ -14285,7 +14288,7 @@
         <v>454</v>
       </c>
       <c r="I220" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J220" t="s">
         <v>51</v>
@@ -14303,10 +14306,10 @@
         <v>45</v>
       </c>
       <c r="O220" t="s">
+        <v>140</v>
+      </c>
+      <c r="P220" t="s">
         <v>491</v>
-      </c>
-      <c r="P220" t="s">
-        <v>490</v>
       </c>
       <c r="Q220" t="s">
         <v>45</v>
@@ -14344,10 +14347,10 @@
         <v>493</v>
       </c>
       <c r="J221" t="s">
-        <v>51</v>
+        <v>494</v>
       </c>
       <c r="K221" t="s">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="L221" t="s">
         <v>34</v>
@@ -14359,7 +14362,7 @@
         <v>45</v>
       </c>
       <c r="O221" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P221" t="s">
         <v>493</v>
@@ -14385,7 +14388,7 @@
         <v>34</v>
       </c>
       <c r="E222" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F222" t="s">
         <v>150</v>
@@ -14397,13 +14400,13 @@
         <v>454</v>
       </c>
       <c r="I222" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J222" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K222" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L222" t="s">
         <v>34</v>
@@ -14415,10 +14418,10 @@
         <v>45</v>
       </c>
       <c r="O222" t="s">
+        <v>61</v>
+      </c>
+      <c r="P222" t="s">
         <v>497</v>
-      </c>
-      <c r="P222" t="s">
-        <v>496</v>
       </c>
       <c r="Q222" t="s">
         <v>45</v>
@@ -15785,28 +15788,28 @@
         <v>34</v>
       </c>
       <c r="E247" t="s">
+        <v>508</v>
+      </c>
+      <c r="F247" t="s">
+        <v>162</v>
+      </c>
+      <c r="G247" t="s">
+        <v>41</v>
+      </c>
+      <c r="H247" t="s">
         <v>541</v>
       </c>
-      <c r="F247" t="s">
-        <v>150</v>
-      </c>
-      <c r="G247" t="s">
-        <v>41</v>
-      </c>
-      <c r="H247" t="s">
+      <c r="I247" t="s">
+        <v>531</v>
+      </c>
+      <c r="J247" t="s">
+        <v>511</v>
+      </c>
+      <c r="K247" t="s">
+        <v>44</v>
+      </c>
+      <c r="L247" t="s">
         <v>542</v>
-      </c>
-      <c r="I247" t="s">
-        <v>543</v>
-      </c>
-      <c r="J247" t="s">
-        <v>138</v>
-      </c>
-      <c r="K247" t="s">
-        <v>138</v>
-      </c>
-      <c r="L247" t="s">
-        <v>34</v>
       </c>
       <c r="M247" t="s">
         <v>537</v>
@@ -15818,7 +15821,7 @@
         <v>140</v>
       </c>
       <c r="P247" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="Q247" t="s">
         <v>45</v>
@@ -15841,10 +15844,10 @@
         <v>34</v>
       </c>
       <c r="E248" t="s">
-        <v>508</v>
+        <v>543</v>
       </c>
       <c r="F248" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G248" t="s">
         <v>41</v>
@@ -15853,16 +15856,16 @@
         <v>544</v>
       </c>
       <c r="I248" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="J248" t="s">
-        <v>511</v>
+        <v>138</v>
       </c>
       <c r="K248" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="L248" t="s">
-        <v>545</v>
+        <v>34</v>
       </c>
       <c r="M248" t="s">
         <v>537</v>
@@ -15874,7 +15877,7 @@
         <v>140</v>
       </c>
       <c r="P248" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="Q248" t="s">
         <v>45</v>
@@ -15953,7 +15956,7 @@
         <v>34</v>
       </c>
       <c r="E250" t="s">
-        <v>144</v>
+        <v>520</v>
       </c>
       <c r="F250" t="s">
         <v>162</v>
@@ -15962,7 +15965,7 @@
         <v>41</v>
       </c>
       <c r="H250" t="s">
-        <v>389</v>
+        <v>334</v>
       </c>
       <c r="I250" t="s">
         <v>550</v>
@@ -16009,7 +16012,7 @@
         <v>34</v>
       </c>
       <c r="E251" t="s">
-        <v>520</v>
+        <v>144</v>
       </c>
       <c r="F251" t="s">
         <v>162</v>
@@ -16018,7 +16021,7 @@
         <v>41</v>
       </c>
       <c r="H251" t="s">
-        <v>334</v>
+        <v>389</v>
       </c>
       <c r="I251" t="s">
         <v>553</v>
@@ -16121,28 +16124,28 @@
         <v>34</v>
       </c>
       <c r="E253" t="s">
+        <v>508</v>
+      </c>
+      <c r="F253" t="s">
+        <v>162</v>
+      </c>
+      <c r="G253" t="s">
+        <v>41</v>
+      </c>
+      <c r="H253" t="s">
         <v>559</v>
       </c>
-      <c r="F253" t="s">
-        <v>150</v>
-      </c>
-      <c r="G253" t="s">
-        <v>41</v>
-      </c>
-      <c r="H253" t="s">
+      <c r="I253" t="s">
         <v>560</v>
       </c>
-      <c r="I253" t="s">
+      <c r="J253" t="s">
+        <v>511</v>
+      </c>
+      <c r="K253" t="s">
+        <v>44</v>
+      </c>
+      <c r="L253" t="s">
         <v>561</v>
-      </c>
-      <c r="J253" t="s">
-        <v>138</v>
-      </c>
-      <c r="K253" t="s">
-        <v>138</v>
-      </c>
-      <c r="L253" t="s">
-        <v>34</v>
       </c>
       <c r="M253" t="s">
         <v>537</v>
@@ -16154,7 +16157,7 @@
         <v>140</v>
       </c>
       <c r="P253" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="Q253" t="s">
         <v>45</v>
@@ -16289,28 +16292,28 @@
         <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>508</v>
+        <v>568</v>
       </c>
       <c r="F256" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G256" t="s">
         <v>41</v>
       </c>
       <c r="H256" t="s">
-        <v>568</v>
+        <v>357</v>
       </c>
       <c r="I256" t="s">
         <v>569</v>
       </c>
       <c r="J256" t="s">
-        <v>511</v>
+        <v>177</v>
       </c>
       <c r="K256" t="s">
-        <v>44</v>
+        <v>570</v>
       </c>
       <c r="L256" t="s">
-        <v>570</v>
+        <v>34</v>
       </c>
       <c r="M256" t="s">
         <v>537</v>
@@ -16401,28 +16404,28 @@
         <v>34</v>
       </c>
       <c r="E258" t="s">
-        <v>144</v>
+        <v>568</v>
       </c>
       <c r="F258" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G258" t="s">
         <v>41</v>
       </c>
       <c r="H258" t="s">
-        <v>351</v>
+        <v>573</v>
       </c>
       <c r="I258" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J258" t="s">
-        <v>574</v>
+        <v>138</v>
       </c>
       <c r="K258" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="L258" t="s">
-        <v>575</v>
+        <v>34</v>
       </c>
       <c r="M258" t="s">
         <v>537</v>
@@ -16434,7 +16437,7 @@
         <v>140</v>
       </c>
       <c r="P258" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Q258" t="s">
         <v>45</v>
@@ -16457,28 +16460,28 @@
         <v>34</v>
       </c>
       <c r="E259" t="s">
-        <v>559</v>
+        <v>144</v>
       </c>
       <c r="F259" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="G259" t="s">
         <v>41</v>
       </c>
       <c r="H259" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="I259" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="J259" t="s">
-        <v>177</v>
+        <v>575</v>
       </c>
       <c r="K259" t="s">
+        <v>44</v>
+      </c>
+      <c r="L259" t="s">
         <v>576</v>
-      </c>
-      <c r="L259" t="s">
-        <v>34</v>
       </c>
       <c r="M259" t="s">
         <v>537</v>
@@ -16490,7 +16493,7 @@
         <v>140</v>
       </c>
       <c r="P259" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="Q259" t="s">
         <v>45</v>
@@ -17763,7 +17766,7 @@
         <v>511</v>
       </c>
       <c r="K282" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="L282" t="s">
         <v>641</v>
@@ -18152,10 +18155,10 @@
         <v>658</v>
       </c>
       <c r="J289" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="K289" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="L289" t="s">
         <v>34</v>
@@ -18323,7 +18326,7 @@
         <v>250</v>
       </c>
       <c r="K292" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="L292" t="s">
         <v>669</v>
@@ -20097,10 +20100,10 @@
         <v>33</v>
       </c>
       <c r="E324" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="F324" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="G324" t="s">
         <v>41</v>
@@ -20112,10 +20115,10 @@
         <v>778</v>
       </c>
       <c r="J324" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="K324" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="L324" t="s">
         <v>779</v>
@@ -20127,13 +20130,13 @@
         <v>45</v>
       </c>
       <c r="O324" t="s">
-        <v>34</v>
+        <v>305</v>
       </c>
       <c r="P324" t="s">
-        <v>34</v>
+        <v>778</v>
       </c>
       <c r="Q324" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R324" t="s">
         <v>34</v>
@@ -20153,25 +20156,25 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>348</v>
+        <v>194</v>
       </c>
       <c r="F325" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="G325" t="s">
         <v>41</v>
       </c>
       <c r="H325" t="s">
+        <v>777</v>
+      </c>
+      <c r="I325" t="s">
         <v>780</v>
       </c>
-      <c r="I325" t="s">
-        <v>781</v>
-      </c>
       <c r="J325" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="K325" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="L325" t="s">
         <v>779</v>
@@ -20183,13 +20186,13 @@
         <v>45</v>
       </c>
       <c r="O325" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P325" t="s">
-        <v>34</v>
+        <v>780</v>
       </c>
       <c r="Q325" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R325" t="s">
         <v>34</v>
@@ -20209,10 +20212,10 @@
         <v>34</v>
       </c>
       <c r="E326" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F326" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="G326" t="s">
         <v>41</v>
@@ -20221,13 +20224,13 @@
         <v>777</v>
       </c>
       <c r="I326" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="J326" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="K326" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="L326" t="s">
         <v>779</v>
@@ -20239,13 +20242,13 @@
         <v>45</v>
       </c>
       <c r="O326" t="s">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="P326" t="s">
-        <v>34</v>
+        <v>781</v>
       </c>
       <c r="Q326" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R326" t="s">
         <v>34</v>
@@ -20265,10 +20268,10 @@
         <v>34</v>
       </c>
       <c r="E327" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F327" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="G327" t="s">
         <v>41</v>
@@ -20277,13 +20280,13 @@
         <v>777</v>
       </c>
       <c r="I327" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="J327" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="K327" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="L327" t="s">
         <v>779</v>
@@ -20295,13 +20298,13 @@
         <v>45</v>
       </c>
       <c r="O327" t="s">
-        <v>34</v>
+        <v>121</v>
       </c>
       <c r="P327" t="s">
-        <v>34</v>
+        <v>782</v>
       </c>
       <c r="Q327" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R327" t="s">
         <v>34</v>
@@ -20324,7 +20327,7 @@
         <v>107</v>
       </c>
       <c r="F328" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="G328" t="s">
         <v>41</v>
@@ -20333,7 +20336,7 @@
         <v>777</v>
       </c>
       <c r="I328" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="J328" t="s">
         <v>110</v>
@@ -20351,13 +20354,13 @@
         <v>45</v>
       </c>
       <c r="O328" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="P328" t="s">
-        <v>34</v>
+        <v>783</v>
       </c>
       <c r="Q328" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R328" t="s">
         <v>34</v>
@@ -20377,10 +20380,10 @@
         <v>34</v>
       </c>
       <c r="E329" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="F329" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="G329" t="s">
         <v>41</v>
@@ -20389,13 +20392,13 @@
         <v>777</v>
       </c>
       <c r="I329" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="J329" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="K329" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="L329" t="s">
         <v>779</v>
@@ -20407,13 +20410,13 @@
         <v>45</v>
       </c>
       <c r="O329" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="P329" t="s">
-        <v>34</v>
+        <v>784</v>
       </c>
       <c r="Q329" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R329" t="s">
         <v>34</v>
@@ -20433,7 +20436,7 @@
         <v>34</v>
       </c>
       <c r="E330" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F330" t="s">
         <v>190</v>
@@ -20445,13 +20448,13 @@
         <v>777</v>
       </c>
       <c r="I330" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="J330" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K330" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="L330" t="s">
         <v>779</v>
@@ -20463,10 +20466,10 @@
         <v>45</v>
       </c>
       <c r="O330" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="P330" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="Q330" t="s">
         <v>45</v>
@@ -20489,10 +20492,10 @@
         <v>34</v>
       </c>
       <c r="E331" t="s">
-        <v>361</v>
+        <v>200</v>
       </c>
       <c r="F331" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="G331" t="s">
         <v>41</v>
@@ -20501,13 +20504,13 @@
         <v>777</v>
       </c>
       <c r="I331" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="J331" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="K331" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="L331" t="s">
         <v>779</v>
@@ -20519,13 +20522,13 @@
         <v>45</v>
       </c>
       <c r="O331" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="P331" t="s">
-        <v>34</v>
+        <v>786</v>
       </c>
       <c r="Q331" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R331" t="s">
         <v>34</v>
@@ -20545,10 +20548,10 @@
         <v>34</v>
       </c>
       <c r="E332" t="s">
-        <v>202</v>
+        <v>404</v>
       </c>
       <c r="F332" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="G332" t="s">
         <v>41</v>
@@ -20557,13 +20560,13 @@
         <v>777</v>
       </c>
       <c r="I332" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="J332" t="s">
-        <v>98</v>
+        <v>414</v>
       </c>
       <c r="K332" t="s">
-        <v>98</v>
+        <v>414</v>
       </c>
       <c r="L332" t="s">
         <v>779</v>
@@ -20575,13 +20578,13 @@
         <v>45</v>
       </c>
       <c r="O332" t="s">
-        <v>34</v>
+        <v>788</v>
       </c>
       <c r="P332" t="s">
-        <v>34</v>
+        <v>787</v>
       </c>
       <c r="Q332" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R332" t="s">
         <v>34</v>
@@ -20601,10 +20604,10 @@
         <v>34</v>
       </c>
       <c r="E333" t="s">
-        <v>207</v>
+        <v>361</v>
       </c>
       <c r="F333" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="G333" t="s">
         <v>41</v>
@@ -20616,10 +20619,10 @@
         <v>789</v>
       </c>
       <c r="J333" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="K333" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="L333" t="s">
         <v>779</v>
@@ -20631,13 +20634,13 @@
         <v>45</v>
       </c>
       <c r="O333" t="s">
-        <v>34</v>
+        <v>363</v>
       </c>
       <c r="P333" t="s">
-        <v>34</v>
+        <v>789</v>
       </c>
       <c r="Q333" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R333" t="s">
         <v>34</v>
@@ -20657,25 +20660,25 @@
         <v>34</v>
       </c>
       <c r="E334" t="s">
-        <v>186</v>
+        <v>348</v>
       </c>
       <c r="F334" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="G334" t="s">
         <v>41</v>
       </c>
       <c r="H334" t="s">
-        <v>777</v>
+        <v>790</v>
       </c>
       <c r="I334" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="J334" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="K334" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="L334" t="s">
         <v>779</v>
@@ -20687,13 +20690,13 @@
         <v>45</v>
       </c>
       <c r="O334" t="s">
-        <v>34</v>
+        <v>321</v>
       </c>
       <c r="P334" t="s">
-        <v>34</v>
+        <v>791</v>
       </c>
       <c r="Q334" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R334" t="s">
         <v>34</v>
@@ -20713,10 +20716,10 @@
         <v>34</v>
       </c>
       <c r="E335" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="F335" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="G335" t="s">
         <v>41</v>
@@ -20725,13 +20728,13 @@
         <v>777</v>
       </c>
       <c r="I335" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="J335" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="K335" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="L335" t="s">
         <v>779</v>
@@ -20743,13 +20746,13 @@
         <v>45</v>
       </c>
       <c r="O335" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="P335" t="s">
-        <v>34</v>
+        <v>792</v>
       </c>
       <c r="Q335" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R335" t="s">
         <v>34</v>
@@ -20769,10 +20772,10 @@
         <v>34</v>
       </c>
       <c r="E336" t="s">
-        <v>413</v>
+        <v>196</v>
       </c>
       <c r="F336" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="G336" t="s">
         <v>41</v>
@@ -20781,13 +20784,13 @@
         <v>777</v>
       </c>
       <c r="I336" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="J336" t="s">
-        <v>409</v>
+        <v>91</v>
       </c>
       <c r="K336" t="s">
-        <v>409</v>
+        <v>91</v>
       </c>
       <c r="L336" t="s">
         <v>779</v>
@@ -20799,13 +20802,13 @@
         <v>45</v>
       </c>
       <c r="O336" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="P336" t="s">
-        <v>34</v>
+        <v>793</v>
       </c>
       <c r="Q336" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R336" t="s">
         <v>34</v>
@@ -20813,7 +20816,7 @@
     </row>
     <row r="337">
       <c r="A337" t="s" s="1">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B337" t="s" s="1">
         <v>32</v>
@@ -20869,7 +20872,7 @@
     </row>
     <row r="338">
       <c r="A338" t="s" s="1">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B338" t="s" s="1">
         <v>32</v>
@@ -20925,7 +20928,7 @@
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B339" t="s">
         <v>32</v>
@@ -20981,7 +20984,7 @@
     </row>
     <row r="340">
       <c r="A340" t="s" s="1">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B340" t="s" s="1">
         <v>157</v>
@@ -21037,7 +21040,7 @@
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B341" t="s">
         <v>157</v>
@@ -21093,13 +21096,13 @@
     </row>
     <row r="342">
       <c r="A342" t="s" s="1">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B342" t="s" s="1">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C342" t="s" s="1">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D342" t="s" s="1">
         <v>33</v>
@@ -21149,7 +21152,7 @@
     </row>
     <row r="343">
       <c r="A343" t="s" s="1">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B343" t="s" s="1">
         <v>180</v>
@@ -21205,7 +21208,7 @@
     </row>
     <row r="344">
       <c r="A344" t="s" s="1">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B344" t="s" s="1">
         <v>182</v>
@@ -21261,7 +21264,7 @@
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B345" t="s">
         <v>182</v>
@@ -21317,7 +21320,7 @@
     </row>
     <row r="346">
       <c r="A346" t="s" s="1">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B346" t="s" s="1">
         <v>272</v>
@@ -21373,7 +21376,7 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B347" t="s">
         <v>272</v>
@@ -21429,13 +21432,13 @@
     </row>
     <row r="348">
       <c r="A348" t="s" s="1">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B348" t="s" s="1">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C348" t="s" s="1">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D348" t="s" s="1">
         <v>33</v>
@@ -21485,13 +21488,13 @@
     </row>
     <row r="349">
       <c r="A349" t="s" s="1">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B349" t="s" s="1">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C349" t="s" s="1">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D349" t="s" s="1">
         <v>33</v>
@@ -21541,7 +21544,7 @@
     </row>
     <row r="350">
       <c r="A350" t="s" s="1">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B350" t="s" s="1">
         <v>327</v>
@@ -21597,7 +21600,7 @@
     </row>
     <row r="351">
       <c r="A351" t="s" s="1">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B351" t="s" s="1">
         <v>329</v>
@@ -21653,7 +21656,7 @@
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B352" t="s">
         <v>329</v>
@@ -21709,7 +21712,7 @@
     </row>
     <row r="353">
       <c r="A353" t="s" s="1">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B353" t="s" s="1">
         <v>444</v>
@@ -21765,7 +21768,7 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B354" t="s">
         <v>444</v>
@@ -21821,7 +21824,7 @@
     </row>
     <row r="355">
       <c r="A355" t="s" s="1">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B355" t="s" s="1">
         <v>450</v>
@@ -21877,7 +21880,7 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B356" t="s">
         <v>452</v>
@@ -21933,7 +21936,7 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B357" t="s">
         <v>499</v>
@@ -21989,7 +21992,7 @@
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B358" t="s">
         <v>506</v>
@@ -22045,7 +22048,7 @@
     </row>
     <row r="359">
       <c r="A359" t="s" s="1">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B359" t="s" s="1">
         <v>525</v>
@@ -22101,7 +22104,7 @@
     </row>
     <row r="360">
       <c r="A360" t="s" s="1">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B360" t="s" s="1">
         <v>527</v>
@@ -22157,7 +22160,7 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B361" t="s">
         <v>529</v>
@@ -22213,7 +22216,7 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B362" t="s">
         <v>534</v>
@@ -22269,7 +22272,7 @@
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B363" t="s">
         <v>586</v>
@@ -22325,7 +22328,7 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B364" t="s">
         <v>592</v>
@@ -22381,7 +22384,7 @@
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B365" t="s">
         <v>596</v>
@@ -22437,7 +22440,7 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="1">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B366" t="s" s="1">
         <v>603</v>
@@ -22493,7 +22496,7 @@
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B367" t="s">
         <v>605</v>
@@ -22549,7 +22552,7 @@
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B368" t="s">
         <v>617</v>
@@ -22605,7 +22608,7 @@
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B369" t="s">
         <v>625</v>
@@ -22661,7 +22664,7 @@
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B370" t="s">
         <v>631</v>
@@ -22717,7 +22720,7 @@
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B371" t="s">
         <v>643</v>
@@ -22773,7 +22776,7 @@
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B372" t="s">
         <v>660</v>
@@ -22829,7 +22832,7 @@
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B373" t="s">
         <v>671</v>
@@ -22885,7 +22888,7 @@
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B374" t="s">
         <v>689</v>
@@ -22941,7 +22944,7 @@
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B375" t="s">
         <v>715</v>
@@ -22997,7 +23000,7 @@
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B376" t="s">
         <v>721</v>
@@ -23053,7 +23056,7 @@
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B377" t="s">
         <v>740</v>
@@ -23109,13 +23112,13 @@
     </row>
     <row r="378">
       <c r="A378" t="s" s="1">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B378" t="s" s="1">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C378" t="s" s="1">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D378" t="s" s="1">
         <v>33</v>
@@ -23165,13 +23168,13 @@
     </row>
     <row r="379">
       <c r="A379" t="s" s="1">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B379" t="s" s="1">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C379" t="s" s="1">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D379" t="s" s="1">
         <v>33</v>
@@ -23221,7 +23224,7 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="1">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B380" t="s" s="1">
         <v>765</v>
@@ -23277,7 +23280,7 @@
     </row>
     <row r="381">
       <c r="A381" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B381" t="s">
         <v>765</v>
@@ -23333,7 +23336,7 @@
     </row>
     <row r="382">
       <c r="A382" t="s" s="1">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B382" t="s" s="1">
         <v>773</v>
@@ -23389,7 +23392,7 @@
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B383" t="s">
         <v>773</v>
@@ -23445,13 +23448,13 @@
     </row>
     <row r="384">
       <c r="A384" t="s" s="1">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B384" t="s" s="1">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C384" t="s" s="1">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D384" t="s" s="1">
         <v>33</v>
@@ -23501,13 +23504,13 @@
     </row>
     <row r="385">
       <c r="A385" t="s" s="1">
+        <v>848</v>
+      </c>
+      <c r="B385" t="s" s="1">
         <v>847</v>
       </c>
-      <c r="B385" t="s" s="1">
-        <v>846</v>
-      </c>
       <c r="C385" t="s" s="1">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D385" t="s" s="1">
         <v>33</v>
@@ -23557,13 +23560,13 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="1">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B386" t="s" s="1">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C386" t="s" s="1">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D386" t="s" s="1">
         <v>33</v>
@@ -23613,7 +23616,7 @@
     </row>
     <row r="387">
       <c r="A387" t="s" s="1">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B387" t="s" s="1">
         <v>32</v>
@@ -23669,13 +23672,13 @@
     </row>
     <row r="388">
       <c r="A388" t="s" s="1">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B388" t="s" s="1">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C388" t="s" s="1">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D388" t="s" s="1">
         <v>33</v>
@@ -23725,7 +23728,7 @@
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B389" t="s">
         <v>157</v>
@@ -23781,7 +23784,7 @@
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B390" t="s">
         <v>180</v>
@@ -23837,7 +23840,7 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B391" t="s">
         <v>327</v>
@@ -23893,7 +23896,7 @@
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B392" t="s">
         <v>773</v>
@@ -23949,13 +23952,13 @@
     </row>
     <row r="393">
       <c r="A393" t="s" s="1">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B393" t="s" s="1">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C393" t="s" s="1">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D393" t="s" s="1">
         <v>33</v>
@@ -24005,7 +24008,7 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B394" t="s">
         <v>525</v>
@@ -24061,7 +24064,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B395" t="s">
         <v>765</v>
@@ -24117,7 +24120,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B396" t="s">
         <v>32</v>
@@ -24173,13 +24176,13 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B397" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C397" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D397" t="s">
         <v>33</v>
@@ -24229,13 +24232,13 @@
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B398" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C398" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D398" t="s">
         <v>33</v>
@@ -24285,7 +24288,7 @@
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B399" t="s">
         <v>182</v>
@@ -24341,7 +24344,7 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B400" t="s">
         <v>329</v>
@@ -24397,7 +24400,7 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B401" t="s">
         <v>527</v>
@@ -24453,7 +24456,7 @@
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B402" t="s">
         <v>605</v>
@@ -24509,7 +24512,7 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B403" t="s">
         <v>157</v>
@@ -24565,13 +24568,13 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B404" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C404" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D404" t="s">
         <v>33</v>
@@ -24621,13 +24624,13 @@
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B405" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C405" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D405" t="s">
         <v>33</v>
@@ -24677,13 +24680,13 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="1">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B406" t="s" s="1">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C406" t="s" s="1">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D406" t="s" s="1">
         <v>33</v>
@@ -24733,16 +24736,16 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="1">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B407" t="s" s="1">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C407" t="s" s="1">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D407" t="s" s="1">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E407" t="s" s="1">
         <v>34</v>
@@ -24789,16 +24792,16 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="1">
+        <v>878</v>
+      </c>
+      <c r="B408" t="s" s="1">
+        <v>879</v>
+      </c>
+      <c r="C408" t="s" s="1">
+        <v>879</v>
+      </c>
+      <c r="D408" t="s" s="1">
         <v>877</v>
-      </c>
-      <c r="B408" t="s" s="1">
-        <v>878</v>
-      </c>
-      <c r="C408" t="s" s="1">
-        <v>878</v>
-      </c>
-      <c r="D408" t="s" s="1">
-        <v>876</v>
       </c>
       <c r="E408" t="s" s="1">
         <v>34</v>
@@ -24845,16 +24848,16 @@
     </row>
     <row r="409">
       <c r="A409" t="s" s="1">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B409" t="s" s="1">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C409" t="s" s="1">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D409" t="s" s="1">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E409" t="s" s="1">
         <v>34</v>
